--- a/Master Updates.xlsx
+++ b/Master Updates.xlsx
@@ -6985,8 +6985,10 @@
       <c r="AX2" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY2" s="2" t="s">
-        <v>1090</v>
+      <c r="AY2" s="2" t="inlineStr">
+        <is>
+          <t>Overpayment identified / Refund sent</t>
+        </is>
       </c>
       <c r="AZ2" s="2" t="s">
         <v>1090</v>
@@ -7130,8 +7132,10 @@
       <c r="AX3" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY3" s="2" t="s">
-        <v>1090</v>
+      <c r="AY3" s="2" t="inlineStr">
+        <is>
+          <t>Waiting on payer</t>
+        </is>
       </c>
       <c r="AZ3" s="2" t="s">
         <v>1090</v>
@@ -8048,8 +8052,10 @@
       <c r="AX9" s="8">
         <v>93925</v>
       </c>
-      <c r="AY9" s="2" t="s">
-        <v>1090</v>
+      <c r="AY9" s="2" t="inlineStr">
+        <is>
+          <t>Checking with internal team</t>
+        </is>
       </c>
       <c r="AZ9" s="2" t="s">
         <v>1090</v>
@@ -8204,8 +8210,10 @@
       <c r="AX10" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="AY10" s="2" t="s">
-        <v>1459</v>
+      <c r="AY10" s="2" t="inlineStr">
+        <is>
+          <t>Waiting on recoupment</t>
+        </is>
       </c>
       <c r="AZ10" s="2" t="s">
         <v>1090</v>
@@ -9126,8 +9134,10 @@
       <c r="AX16" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="AY16" s="2" t="s">
-        <v>1090</v>
+      <c r="AY16" s="2" t="inlineStr">
+        <is>
+          <t>Waiting on recoupment</t>
+        </is>
       </c>
       <c r="AZ16" s="2" t="s">
         <v>1090</v>
@@ -9286,8 +9296,10 @@
       <c r="AX17" s="8" t="s">
         <v>1469</v>
       </c>
-      <c r="AY17" s="2" t="s">
-        <v>1090</v>
+      <c r="AY17" s="2" t="inlineStr">
+        <is>
+          <t>Checking with internal team</t>
+        </is>
       </c>
       <c r="AZ17" s="2" t="s">
         <v>1090</v>
@@ -9446,8 +9458,10 @@
       <c r="AX18" s="8" t="s">
         <v>1469</v>
       </c>
-      <c r="AY18" s="2" t="s">
-        <v>1090</v>
+      <c r="AY18" s="2" t="inlineStr">
+        <is>
+          <t>Checking with internal team</t>
+        </is>
       </c>
       <c r="AZ18" s="2" t="s">
         <v>1090</v>
@@ -9606,8 +9620,10 @@
       <c r="AX19" s="8" t="s">
         <v>1469</v>
       </c>
-      <c r="AY19" s="2" t="s">
-        <v>1090</v>
+      <c r="AY19" s="2" t="inlineStr">
+        <is>
+          <t>Checking with internal team</t>
+        </is>
       </c>
       <c r="AZ19" s="2" t="s">
         <v>1090</v>
@@ -9766,8 +9782,10 @@
       <c r="AX20" s="8" t="s">
         <v>1469</v>
       </c>
-      <c r="AY20" s="2" t="s">
-        <v>1090</v>
+      <c r="AY20" s="2" t="inlineStr">
+        <is>
+          <t>Checking with internal team</t>
+        </is>
       </c>
       <c r="AZ20" s="2" t="s">
         <v>1090</v>
@@ -9920,8 +9938,10 @@
       <c r="AX21" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY21" s="2" t="s">
-        <v>1090</v>
+      <c r="AY21" s="2" t="inlineStr">
+        <is>
+          <t>Overpayment identified / Refund sent</t>
+        </is>
       </c>
       <c r="AZ21" s="2" t="s">
         <v>1090</v>
@@ -10078,8 +10098,10 @@
       <c r="AX22" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY22" s="2" t="s">
-        <v>1090</v>
+      <c r="AY22" s="2" t="inlineStr">
+        <is>
+          <t>Overpayment identified / Refund sent</t>
+        </is>
       </c>
       <c r="AZ22" s="2" t="s">
         <v>1090</v>
@@ -10546,8 +10568,10 @@
       <c r="AX25" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="AY25" s="2" t="s">
-        <v>1443</v>
+      <c r="AY25" s="2" t="inlineStr">
+        <is>
+          <t>Billed secondary / Crossed over to secondary</t>
+        </is>
       </c>
       <c r="AZ25" s="2" t="s">
         <v>1090</v>
@@ -10852,8 +10876,10 @@
       <c r="AX27" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY27" s="2" t="s">
-        <v>1090</v>
+      <c r="AY27" s="2" t="inlineStr">
+        <is>
+          <t>Contacted payer</t>
+        </is>
       </c>
       <c r="AZ27" s="2" t="s">
         <v>1090</v>
@@ -11004,8 +11030,10 @@
       <c r="AX28" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="AY28" s="2" t="s">
-        <v>1090</v>
+      <c r="AY28" s="2" t="inlineStr">
+        <is>
+          <t>Overpayment identified / Refund sent</t>
+        </is>
       </c>
       <c r="AZ28" s="2" t="s">
         <v>1090</v>
@@ -11612,8 +11640,10 @@
       <c r="AX32" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="AY32" s="2" t="s">
-        <v>1090</v>
+      <c r="AY32" s="2" t="inlineStr">
+        <is>
+          <t>Overpayment identified / Refund sent</t>
+        </is>
       </c>
       <c r="AZ32" s="2" t="s">
         <v>1090</v>
@@ -12226,8 +12256,10 @@
       <c r="AX36" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="AY36" s="2" t="s">
-        <v>1443</v>
+      <c r="AY36" s="2" t="inlineStr">
+        <is>
+          <t>Billed secondary / Crossed over to secondary</t>
+        </is>
       </c>
       <c r="AZ36" s="2" t="s">
         <v>1090</v>
@@ -12998,8 +13030,10 @@
       <c r="AX41" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY41" s="2" t="s">
-        <v>1090</v>
+      <c r="AY41" s="2" t="inlineStr">
+        <is>
+          <t>Contacted patient</t>
+        </is>
       </c>
       <c r="AZ41" s="2" t="s">
         <v>1505</v>
@@ -13616,8 +13650,10 @@
       <c r="AX45" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY45" s="2" t="s">
-        <v>1090</v>
+      <c r="AY45" s="2" t="inlineStr">
+        <is>
+          <t>Checking with internal team</t>
+        </is>
       </c>
       <c r="AZ45" s="2" t="s">
         <v>1090</v>
@@ -18565,8 +18601,10 @@
       <c r="AX77" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY77" s="2" t="s">
-        <v>1090</v>
+      <c r="AY77" s="2" t="inlineStr">
+        <is>
+          <t>Checking with internal team</t>
+        </is>
       </c>
       <c r="AZ77" s="2" t="s">
         <v>1090</v>
@@ -18719,8 +18757,10 @@
       <c r="AX78" s="8" t="s">
         <v>1449</v>
       </c>
-      <c r="AY78" s="2" t="s">
-        <v>1090</v>
+      <c r="AY78" s="2" t="inlineStr">
+        <is>
+          <t>Checking with internal team</t>
+        </is>
       </c>
       <c r="AZ78" s="2" t="s">
         <v>1090</v>
@@ -20587,8 +20627,10 @@
       <c r="AX90" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY90" s="2" t="s">
-        <v>1090</v>
+      <c r="AY90" s="2" t="inlineStr">
+        <is>
+          <t>Contacted payer</t>
+        </is>
       </c>
       <c r="AZ90" s="2" t="s">
         <v>1090</v>
@@ -21675,8 +21717,10 @@
       <c r="AX97" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY97" s="2" t="s">
-        <v>1090</v>
+      <c r="AY97" s="2" t="inlineStr">
+        <is>
+          <t>Checking with internal team</t>
+        </is>
       </c>
       <c r="AZ97" s="2" t="s">
         <v>1090</v>
@@ -21841,8 +21885,10 @@
       <c r="AX98" s="8" t="s">
         <v>1557</v>
       </c>
-      <c r="AY98" s="2" t="s">
-        <v>1090</v>
+      <c r="AY98" s="2" t="inlineStr">
+        <is>
+          <t>Contacted payer</t>
+        </is>
       </c>
       <c r="AZ98" s="2" t="s">
         <v>1090</v>
@@ -22773,8 +22819,10 @@
       <c r="AX104" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY104" s="2" t="s">
-        <v>1090</v>
+      <c r="AY104" s="2" t="inlineStr">
+        <is>
+          <t>Checking with internal team</t>
+        </is>
       </c>
       <c r="AZ104" s="2" t="s">
         <v>1090</v>
@@ -23075,8 +23123,10 @@
       <c r="AX106" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY106" s="2" t="s">
-        <v>1090</v>
+      <c r="AY106" s="2" t="inlineStr">
+        <is>
+          <t>Checking with internal team</t>
+        </is>
       </c>
       <c r="AZ106" s="2" t="s">
         <v>1090</v>
@@ -23251,8 +23301,10 @@
       <c r="AX107" s="8" t="s">
         <v>1565</v>
       </c>
-      <c r="AY107" s="2" t="s">
-        <v>1443</v>
+      <c r="AY107" s="2" t="inlineStr">
+        <is>
+          <t>Billed secondary / Crossed over to secondary</t>
+        </is>
       </c>
       <c r="AZ107" s="2" t="s">
         <v>1090</v>
@@ -23879,8 +23931,10 @@
       <c r="AX111" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY111" s="2" t="s">
-        <v>1090</v>
+      <c r="AY111" s="2" t="inlineStr">
+        <is>
+          <t>Checking with internal team</t>
+        </is>
       </c>
       <c r="AZ111" s="2" t="s">
         <v>1090</v>
@@ -24033,8 +24087,10 @@
       <c r="AX112" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY112" s="2" t="s">
-        <v>1090</v>
+      <c r="AY112" s="2" t="inlineStr">
+        <is>
+          <t>Contacted payer</t>
+        </is>
       </c>
       <c r="AZ112" s="2" t="s">
         <v>1090</v>
@@ -25256,8 +25312,10 @@
       <c r="AX120" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="AY120" s="2" t="s">
-        <v>1090</v>
+      <c r="AY120" s="2" t="inlineStr">
+        <is>
+          <t>Billed secondary / Crossed over to secondary</t>
+        </is>
       </c>
       <c r="AZ120" s="2" t="s">
         <v>1090</v>
@@ -25890,8 +25948,10 @@
       <c r="AX124" s="8" t="s">
         <v>1574</v>
       </c>
-      <c r="AY124" s="2" t="s">
-        <v>1477</v>
+      <c r="AY124" s="2" t="inlineStr">
+        <is>
+          <t>Reprocessing requested</t>
+        </is>
       </c>
       <c r="AZ124" s="2" t="s">
         <v>1090</v>
@@ -26045,8 +26105,10 @@
       <c r="AX125" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY125" s="2" t="s">
-        <v>1090</v>
+      <c r="AY125" s="2" t="inlineStr">
+        <is>
+          <t>Checking with internal team</t>
+        </is>
       </c>
       <c r="AZ125" s="2" t="s">
         <v>1090</v>
@@ -29469,8 +29531,10 @@
       <c r="AX147" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY147" s="2" t="s">
-        <v>1090</v>
+      <c r="AY147" s="2" t="inlineStr">
+        <is>
+          <t>Checking with internal team</t>
+        </is>
       </c>
       <c r="AZ147" s="2" t="s">
         <v>1090</v>
@@ -33348,8 +33412,10 @@
       <c r="AX172" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="AY172" s="2" t="s">
-        <v>1090</v>
+      <c r="AY172" s="2" t="inlineStr">
+        <is>
+          <t>Checking with internal team</t>
+        </is>
       </c>
       <c r="AZ172" s="2" t="s">
         <v>1090</v>
@@ -34660,8 +34726,10 @@
       <c r="AX180" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY180" s="2" t="s">
-        <v>1090</v>
+      <c r="AY180" s="2" t="inlineStr">
+        <is>
+          <t>Contacted payer</t>
+        </is>
       </c>
       <c r="AZ180" s="2" t="s">
         <v>1090</v>
@@ -35582,8 +35650,10 @@
       <c r="AX186" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY186" s="2" t="s">
-        <v>1090</v>
+      <c r="AY186" s="2" t="inlineStr">
+        <is>
+          <t>Contacted payer</t>
+        </is>
       </c>
       <c r="AZ186" s="2" t="s">
         <v>1090</v>
@@ -35888,8 +35958,10 @@
       <c r="AX188" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="AY188" s="2" t="s">
-        <v>1090</v>
+      <c r="AY188" s="2" t="inlineStr">
+        <is>
+          <t>Waiting on payer</t>
+        </is>
       </c>
       <c r="AZ188" s="2" t="s">
         <v>1111</v>
@@ -36344,8 +36416,10 @@
       <c r="AX191" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY191" s="2" t="s">
-        <v>1090</v>
+      <c r="AY191" s="2" t="inlineStr">
+        <is>
+          <t>Contacted payer</t>
+        </is>
       </c>
       <c r="AZ191" s="2" t="s">
         <v>1090</v>
@@ -36500,8 +36574,10 @@
       <c r="AX192" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="AY192" s="2" t="s">
-        <v>1090</v>
+      <c r="AY192" s="2" t="inlineStr">
+        <is>
+          <t>Contacted payer</t>
+        </is>
       </c>
       <c r="AZ192" s="2" t="s">
         <v>1090</v>
@@ -39622,8 +39698,10 @@
       <c r="AX212" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY212" s="2" t="s">
-        <v>1090</v>
+      <c r="AY212" s="2" t="inlineStr">
+        <is>
+          <t>Contacted patient</t>
+        </is>
       </c>
       <c r="AZ212" s="2" t="s">
         <v>1090</v>
@@ -40572,8 +40650,10 @@
       <c r="AX218" s="8" t="s">
         <v>1677</v>
       </c>
-      <c r="AY218" s="2" t="s">
-        <v>1090</v>
+      <c r="AY218" s="2" t="inlineStr">
+        <is>
+          <t>Billed secondary / Crossed over to secondary</t>
+        </is>
       </c>
       <c r="AZ218" s="2" t="s">
         <v>1090</v>
@@ -41976,8 +42056,10 @@
       <c r="AX227" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY227" s="2" t="s">
-        <v>1090</v>
+      <c r="AY227" s="2" t="inlineStr">
+        <is>
+          <t>Contacted payer</t>
+        </is>
       </c>
       <c r="AZ227" s="2" t="s">
         <v>1090</v>
@@ -42282,8 +42364,10 @@
       <c r="AX229" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY229" s="2" t="s">
-        <v>1090</v>
+      <c r="AY229" s="2" t="inlineStr">
+        <is>
+          <t>Overpayment identified / Refund sent</t>
+        </is>
       </c>
       <c r="AZ229" s="2" t="s">
         <v>1090</v>
@@ -43716,8 +43800,10 @@
       <c r="AX238" s="8" t="s">
         <v>1688</v>
       </c>
-      <c r="AY238" s="2" t="s">
-        <v>1090</v>
+      <c r="AY238" s="2" t="inlineStr">
+        <is>
+          <t>Overpayment identified / Refund sent</t>
+        </is>
       </c>
       <c r="AZ238" s="2" t="s">
         <v>1090</v>
@@ -44028,8 +44114,10 @@
       <c r="AX240" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="AY240" s="2" t="s">
-        <v>1459</v>
+      <c r="AY240" s="2" t="inlineStr">
+        <is>
+          <t>Reprocessing requested</t>
+        </is>
       </c>
       <c r="AZ240" s="2" t="s">
         <v>1090</v>
@@ -45142,8 +45230,10 @@
       <c r="AX247" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="AY247" s="2" t="s">
-        <v>1090</v>
+      <c r="AY247" s="2" t="inlineStr">
+        <is>
+          <t>Billed secondary / Crossed over to secondary</t>
+        </is>
       </c>
       <c r="AZ247" s="2" t="s">
         <v>1090</v>
@@ -45918,8 +46008,10 @@
       <c r="AX252" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY252" s="2" t="s">
-        <v>1090</v>
+      <c r="AY252" s="2" t="inlineStr">
+        <is>
+          <t>Billed correct payer</t>
+        </is>
       </c>
       <c r="AZ252" s="2" t="s">
         <v>1090</v>
@@ -46398,8 +46490,10 @@
       <c r="AX255" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY255" s="2" t="s">
-        <v>1443</v>
+      <c r="AY255" s="2" t="inlineStr">
+        <is>
+          <t>Reprocessing requested</t>
+        </is>
       </c>
       <c r="AZ255" s="2" t="s">
         <v>1090</v>
@@ -47024,8 +47118,10 @@
       <c r="AX259" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY259" s="2" t="s">
-        <v>1443</v>
+      <c r="AY259" s="2" t="inlineStr">
+        <is>
+          <t>Reprocessing requested</t>
+        </is>
       </c>
       <c r="AZ259" s="2" t="s">
         <v>1090</v>
@@ -49032,8 +49128,10 @@
       <c r="AX272" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="AY272" s="2" t="s">
-        <v>1090</v>
+      <c r="AY272" s="2" t="inlineStr">
+        <is>
+          <t>Billed secondary / Crossed over to secondary</t>
+        </is>
       </c>
       <c r="AZ272" s="2" t="s">
         <v>1090</v>
@@ -49820,8 +49918,10 @@
       <c r="AX277" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="AY277" s="2" t="s">
-        <v>1443</v>
+      <c r="AY277" s="2" t="inlineStr">
+        <is>
+          <t>Billed secondary / Crossed over to secondary</t>
+        </is>
       </c>
       <c r="AZ277" s="2" t="s">
         <v>1090</v>
@@ -50136,8 +50236,10 @@
       <c r="AX279" s="8" t="s">
         <v>1664</v>
       </c>
-      <c r="AY279" s="2" t="s">
-        <v>1443</v>
+      <c r="AY279" s="2" t="inlineStr">
+        <is>
+          <t>Billed secondary / Crossed over to secondary</t>
+        </is>
       </c>
       <c r="AZ279" s="2" t="s">
         <v>1090</v>
@@ -51380,8 +51482,10 @@
       <c r="AX287" s="8" t="s">
         <v>381</v>
       </c>
-      <c r="AY287" s="2" t="s">
-        <v>1443</v>
+      <c r="AY287" s="2" t="inlineStr">
+        <is>
+          <t>Billed secondary / Crossed over to secondary</t>
+        </is>
       </c>
       <c r="AZ287" s="2" t="s">
         <v>1090</v>
@@ -56390,8 +56494,10 @@
       <c r="AX319" s="8" t="s">
         <v>1729</v>
       </c>
-      <c r="AY319" s="2" t="s">
-        <v>1090</v>
+      <c r="AY319" s="2" t="inlineStr">
+        <is>
+          <t>Contacted patient</t>
+        </is>
       </c>
       <c r="AZ319" s="2" t="s">
         <v>1090</v>
@@ -58244,8 +58350,10 @@
       <c r="AX331" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY331" s="2" t="s">
-        <v>1090</v>
+      <c r="AY331" s="2" t="inlineStr">
+        <is>
+          <t>Contacted patient</t>
+        </is>
       </c>
       <c r="AZ331" s="2" t="s">
         <v>1090</v>
@@ -61059,8 +61167,10 @@
       <c r="AX350" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY350" s="2" t="s">
-        <v>1090</v>
+      <c r="AY350" s="2" t="inlineStr">
+        <is>
+          <t>Waiting on payer</t>
+        </is>
       </c>
       <c r="AZ350" s="2" t="s">
         <v>1090</v>
@@ -69711,8 +69821,10 @@
       <c r="AX408" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY408" s="2" t="s">
-        <v>1090</v>
+      <c r="AY408" s="2" t="inlineStr">
+        <is>
+          <t>Adjusted balance</t>
+        </is>
       </c>
       <c r="AZ408" s="2" t="s">
         <v>1090</v>
@@ -74566,8 +74678,10 @@
       <c r="AX440" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="AY440" s="2" t="s">
-        <v>1090</v>
+      <c r="AY440" s="2" t="inlineStr">
+        <is>
+          <t>Adjusted balance</t>
+        </is>
       </c>
       <c r="AZ440" s="2" t="s">
         <v>1090</v>
@@ -84817,6 +84931,11 @@
       <c r="B13" t="s">
         <v>1831</v>
       </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Billed secondary / Crossed over to secondary</t>
+        </is>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -84825,6 +84944,11 @@
       <c r="B14" t="s">
         <v>1832</v>
       </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Billed correct payer</t>
+        </is>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
@@ -84833,6 +84957,11 @@
       <c r="B15" t="s">
         <v>1833</v>
       </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Contacted patient</t>
+        </is>
+      </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -84841,6 +84970,11 @@
       <c r="B16" t="s">
         <v>1834</v>
       </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Reprocessing requested</t>
+        </is>
+      </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -84849,6 +84983,11 @@
       <c r="B17" t="s">
         <v>1835</v>
       </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Checking with internal team</t>
+        </is>
+      </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
@@ -84857,6 +84996,11 @@
       <c r="B18" t="s">
         <v>1836</v>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Overpayment identified / Refund sent</t>
+        </is>
+      </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -84864,6 +85008,11 @@
       </c>
       <c r="B19" t="s">
         <v>1837</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Waiting on recoupment</t>
+        </is>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">

--- a/Master Updates.xlsx
+++ b/Master Updates.xlsx
@@ -7134,7 +7134,7 @@
       </c>
       <c r="AY3" s="2" t="inlineStr">
         <is>
-          <t>Waiting on payer</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ3" s="2" t="s">
@@ -8054,7 +8054,7 @@
       </c>
       <c r="AY9" s="2" t="inlineStr">
         <is>
-          <t>Checking with internal team</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ9" s="2" t="s">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="AY20" s="2" t="inlineStr">
         <is>
-          <t>Checking with internal team</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ20" s="2" t="s">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="AY27" s="2" t="inlineStr">
         <is>
-          <t>Contacted payer</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ27" s="2" t="s">
@@ -12251,7 +12251,7 @@
         <v>1090</v>
       </c>
       <c r="AW36" s="8" t="s">
-        <v>141</v>
+        <v>1090</v>
       </c>
       <c r="AX36" s="8" t="s">
         <v>141</v>
@@ -12410,8 +12410,10 @@
       <c r="AX37" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY37" s="2" t="s">
-        <v>1477</v>
+      <c r="AY37" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ37" s="2" t="s">
         <v>1498</v>
@@ -13803,7 +13805,7 @@
         <v>1090</v>
       </c>
       <c r="AW46" s="8" t="s">
-        <v>1455</v>
+        <v>1090</v>
       </c>
       <c r="AX46" s="8" t="s">
         <v>1455</v>
@@ -14440,11 +14442,15 @@
       <c r="AX50" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY50" s="2" t="s">
-        <v>1443</v>
-      </c>
-      <c r="AZ50" s="2" t="s">
-        <v>1090</v>
+      <c r="AY50" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="AZ50" s="2" t="inlineStr">
+        <is>
+          <t>Resubmitted</t>
+        </is>
       </c>
       <c r="BA50" s="2" t="s">
         <v>1499</v>
@@ -15043,8 +15049,10 @@
       <c r="AU54" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AV54" s="8" t="s">
-        <v>122</v>
+      <c r="AV54" s="8" t="inlineStr">
+        <is>
+          <t>99492, 99493</t>
+        </is>
       </c>
       <c r="AW54" s="8" t="s">
         <v>1090</v>
@@ -15191,8 +15199,10 @@
       <c r="AU55" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AV55" s="8" t="s">
-        <v>122</v>
+      <c r="AV55" s="8" t="inlineStr">
+        <is>
+          <t>99492, 99493</t>
+        </is>
       </c>
       <c r="AW55" s="8" t="s">
         <v>1090</v>
@@ -15219,8 +15229,10 @@
       <c r="BE55" s="2"/>
     </row>
     <row r="56" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>1114</v>
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Denied</t>
+        </is>
       </c>
       <c r="B56" s="2" t="s">
         <v>1907</v>
@@ -15350,8 +15362,10 @@
       <c r="AX56" s="8">
         <v>63047</v>
       </c>
-      <c r="AY56" s="2" t="s">
-        <v>1490</v>
+      <c r="AY56" s="2" t="inlineStr">
+        <is>
+          <t>Resubmitted</t>
+        </is>
       </c>
       <c r="AZ56" s="2" t="s">
         <v>1443</v>
@@ -16125,8 +16139,10 @@
       <c r="AU61" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AV61" s="8" t="s">
-        <v>1449</v>
+      <c r="AV61" s="8" t="inlineStr">
+        <is>
+          <t>99492, 99494, 99493</t>
+        </is>
       </c>
       <c r="AW61" s="8" t="s">
         <v>1090</v>
@@ -18603,7 +18619,7 @@
       </c>
       <c r="AY77" s="2" t="inlineStr">
         <is>
-          <t>Checking with internal team</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ77" s="2" t="s">
@@ -18913,11 +18929,15 @@
       <c r="AX79" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY79" s="2" t="s">
-        <v>1477</v>
-      </c>
-      <c r="AZ79" s="2" t="s">
-        <v>1090</v>
+      <c r="AY79" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="AZ79" s="2" t="inlineStr">
+        <is>
+          <t>Contacted payer</t>
+        </is>
       </c>
       <c r="BA79" s="2" t="s">
         <v>1483</v>
@@ -19220,7 +19240,7 @@
         <v>1090</v>
       </c>
       <c r="AW81" s="8" t="s">
-        <v>381</v>
+        <v>1090</v>
       </c>
       <c r="AX81" s="8" t="s">
         <v>381</v>
@@ -20473,11 +20493,15 @@
       <c r="AX89" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="AY89" s="2" t="s">
-        <v>1329</v>
-      </c>
-      <c r="AZ89" s="2" t="s">
-        <v>1090</v>
+      <c r="AY89" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="AZ89" s="2" t="inlineStr">
+        <is>
+          <t>Adjusted balance</t>
+        </is>
       </c>
       <c r="BA89" s="2" t="s">
         <v>1513</v>
@@ -20629,7 +20653,7 @@
       </c>
       <c r="AY90" s="2" t="inlineStr">
         <is>
-          <t>Contacted payer</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ90" s="2" t="s">
@@ -21253,8 +21277,10 @@
       <c r="AX94" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="AY94" s="2" t="s">
-        <v>1090</v>
+      <c r="AY94" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ94" s="2" t="s">
         <v>1090</v>
@@ -21407,8 +21433,10 @@
       <c r="AX95" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="AY95" s="2" t="s">
-        <v>1090</v>
+      <c r="AY95" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ95" s="2" t="s">
         <v>1090</v>
@@ -21719,11 +21747,13 @@
       </c>
       <c r="AY97" s="2" t="inlineStr">
         <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="AZ97" s="2" t="inlineStr">
+        <is>
           <t>Checking with internal team</t>
         </is>
-      </c>
-      <c r="AZ97" s="2" t="s">
-        <v>1090</v>
       </c>
       <c r="BA97" s="2" t="s">
         <v>1447</v>
@@ -21887,7 +21917,7 @@
       </c>
       <c r="AY98" s="2" t="inlineStr">
         <is>
-          <t>Contacted payer</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ98" s="2" t="s">
@@ -22511,8 +22541,10 @@
       <c r="AX102" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="AY102" s="2" t="s">
-        <v>1090</v>
+      <c r="AY102" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ102" s="2" t="s">
         <v>1090</v>
@@ -23459,8 +23491,10 @@
       <c r="AX108" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="AY108" s="2" t="s">
-        <v>1090</v>
+      <c r="AY108" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ108" s="2" t="s">
         <v>1090</v>
@@ -24089,7 +24123,7 @@
       </c>
       <c r="AY112" s="2" t="inlineStr">
         <is>
-          <t>Contacted payer</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ112" s="2" t="s">
@@ -25314,7 +25348,7 @@
       </c>
       <c r="AY120" s="2" t="inlineStr">
         <is>
-          <t>Billed secondary / Crossed over to secondary</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ120" s="2" t="s">
@@ -25470,8 +25504,10 @@
       <c r="AX121" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="AY121" s="2" t="s">
-        <v>1090</v>
+      <c r="AY121" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ121" s="2" t="s">
         <v>1090</v>
@@ -25628,11 +25664,15 @@
       <c r="AX122" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY122" s="2" t="s">
-        <v>1111</v>
-      </c>
-      <c r="AZ122" s="2" t="s">
-        <v>1090</v>
+      <c r="AY122" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="AZ122" s="2" t="inlineStr">
+        <is>
+          <t>Uploaded MR</t>
+        </is>
       </c>
       <c r="BA122" s="2" t="s">
         <v>1452</v>
@@ -26107,7 +26147,7 @@
       </c>
       <c r="AY125" s="2" t="inlineStr">
         <is>
-          <t>Checking with internal team</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ125" s="2" t="s">
@@ -26263,8 +26303,10 @@
       <c r="AX126" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY126" s="2" t="s">
-        <v>1459</v>
+      <c r="AY126" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ126" s="2" t="s">
         <v>1090</v>
@@ -27838,8 +27880,10 @@
       <c r="BE136" s="2"/>
     </row>
     <row r="137" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A137" s="2" t="s">
-        <v>1114</v>
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Denied</t>
+        </is>
       </c>
       <c r="B137" s="2" t="s">
         <v>1202</v>
@@ -29048,11 +29092,15 @@
       <c r="AQ144" s="6">
         <v>46160</v>
       </c>
-      <c r="AR144" s="8" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AS144" s="8" t="s">
-        <v>1090</v>
+      <c r="AR144" s="8" t="inlineStr">
+        <is>
+          <t>63047</t>
+        </is>
+      </c>
+      <c r="AS144" s="8" t="inlineStr">
+        <is>
+          <t>CO_150 - Payer deems the information submitted does not support this level of service</t>
+        </is>
       </c>
       <c r="AT144" s="8" t="s">
         <v>1090</v>
@@ -29225,11 +29273,15 @@
       <c r="AX145" s="8" t="s">
         <v>1595</v>
       </c>
-      <c r="AY145" s="2" t="s">
-        <v>1443</v>
-      </c>
-      <c r="AZ145" s="2" t="s">
-        <v>1090</v>
+      <c r="AY145" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
+      </c>
+      <c r="AZ145" s="2" t="inlineStr">
+        <is>
+          <t>Resubmitted</t>
+        </is>
       </c>
       <c r="BA145" s="2" t="s">
         <v>1452</v>
@@ -30144,8 +30196,10 @@
       <c r="AU151" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AV151" s="8" t="s">
-        <v>122</v>
+      <c r="AV151" s="8" t="inlineStr">
+        <is>
+          <t>99492, 99494</t>
+        </is>
       </c>
       <c r="AW151" s="8" t="s">
         <v>1090</v>
@@ -31197,11 +31251,15 @@
       <c r="AS158" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AT158" s="8" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AU158" s="8" t="s">
-        <v>1090</v>
+      <c r="AT158" s="8" t="inlineStr">
+        <is>
+          <t>93923</t>
+        </is>
+      </c>
+      <c r="AU158" s="8" t="inlineStr">
+        <is>
+          <t>CO_146 - Diagnosis was invalid for the date(s) of service reported</t>
+        </is>
       </c>
       <c r="AV158" s="8" t="s">
         <v>132</v>
@@ -31665,8 +31723,10 @@
       <c r="AU161" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AV161" s="8" t="s">
-        <v>1090</v>
+      <c r="AV161" s="8" t="inlineStr">
+        <is>
+          <t>99493, 99494</t>
+        </is>
       </c>
       <c r="AW161" s="8" t="s">
         <v>1090</v>
@@ -31674,11 +31734,15 @@
       <c r="AX161" s="8" t="s">
         <v>1455</v>
       </c>
-      <c r="AY161" s="2" t="s">
-        <v>1443</v>
-      </c>
-      <c r="AZ161" s="2" t="s">
-        <v>1090</v>
+      <c r="AY161" s="2" t="inlineStr">
+        <is>
+          <t>Payment posted</t>
+        </is>
+      </c>
+      <c r="AZ161" s="2" t="inlineStr">
+        <is>
+          <t>Resubmitted</t>
+        </is>
       </c>
       <c r="BA161" s="2" t="s">
         <v>1492</v>
@@ -33414,7 +33478,7 @@
       </c>
       <c r="AY172" s="2" t="inlineStr">
         <is>
-          <t>Checking with internal team</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ172" s="2" t="s">
@@ -34728,7 +34792,7 @@
       </c>
       <c r="AY180" s="2" t="inlineStr">
         <is>
-          <t>Contacted payer</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ180" s="2" t="s">
@@ -35652,7 +35716,7 @@
       </c>
       <c r="AY186" s="2" t="inlineStr">
         <is>
-          <t>Contacted payer</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ186" s="2" t="s">
@@ -35960,7 +36024,7 @@
       </c>
       <c r="AY188" s="2" t="inlineStr">
         <is>
-          <t>Waiting on payer</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ188" s="2" t="s">
@@ -36418,7 +36482,7 @@
       </c>
       <c r="AY191" s="2" t="inlineStr">
         <is>
-          <t>Contacted payer</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ191" s="2" t="s">
@@ -36576,7 +36640,7 @@
       </c>
       <c r="AY192" s="2" t="inlineStr">
         <is>
-          <t>Contacted payer</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ192" s="2" t="s">
@@ -37840,8 +37904,10 @@
       <c r="AX200" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="AY200" s="2" t="s">
-        <v>1090</v>
+      <c r="AY200" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ200" s="2" t="s">
         <v>1090</v>
@@ -38610,8 +38676,10 @@
       <c r="AX205" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="AY205" s="2" t="s">
-        <v>1090</v>
+      <c r="AY205" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ205" s="2" t="s">
         <v>1090</v>
@@ -39700,7 +39768,7 @@
       </c>
       <c r="AY212" s="2" t="inlineStr">
         <is>
-          <t>Contacted patient</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ212" s="2" t="s">
@@ -42058,7 +42126,7 @@
       </c>
       <c r="AY227" s="2" t="inlineStr">
         <is>
-          <t>Contacted payer</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ227" s="2" t="s">
@@ -46010,7 +46078,7 @@
       </c>
       <c r="AY252" s="2" t="inlineStr">
         <is>
-          <t>Billed correct payer</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ252" s="2" t="s">
@@ -48042,8 +48110,10 @@
       <c r="AX265" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY265" s="2" t="s">
-        <v>1490</v>
+      <c r="AY265" s="2" t="inlineStr">
+        <is>
+          <t>Adjusted balance</t>
+        </is>
       </c>
       <c r="AZ265" s="2" t="s">
         <v>1443</v>
@@ -56496,7 +56566,7 @@
       </c>
       <c r="AY319" s="2" t="inlineStr">
         <is>
-          <t>Contacted patient</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ319" s="2" t="s">
@@ -58196,8 +58266,10 @@
       <c r="AX330" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="AY330" s="2" t="s">
-        <v>1459</v>
+      <c r="AY330" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ330" s="2" t="s">
         <v>1090</v>
@@ -58352,7 +58424,7 @@
       </c>
       <c r="AY331" s="2" t="inlineStr">
         <is>
-          <t>Contacted patient</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ331" s="2" t="s">
@@ -59265,7 +59337,7 @@
         <v>1090</v>
       </c>
       <c r="AW337" s="8" t="s">
-        <v>1744</v>
+        <v>1090</v>
       </c>
       <c r="AX337" s="8" t="s">
         <v>1744</v>
@@ -60889,8 +60961,10 @@
       <c r="AX348" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY348" s="2" t="s">
-        <v>1459</v>
+      <c r="AY348" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ348" s="2" t="s">
         <v>1090</v>
@@ -61169,7 +61243,7 @@
       </c>
       <c r="AY350" s="2" t="inlineStr">
         <is>
-          <t>Waiting on payer</t>
+          <t>Under Review</t>
         </is>
       </c>
       <c r="AZ350" s="2" t="s">
@@ -61302,8 +61376,10 @@
       <c r="AX351" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY351" s="2" t="s">
-        <v>1459</v>
+      <c r="AY351" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ351" s="2" t="s">
         <v>1090</v>
@@ -61578,8 +61654,10 @@
       <c r="AX353" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY353" s="2" t="s">
-        <v>1459</v>
+      <c r="AY353" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ353" s="2" t="s">
         <v>1090</v>
@@ -61713,8 +61791,10 @@
       <c r="AX354" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY354" s="2" t="s">
-        <v>1459</v>
+      <c r="AY354" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ354" s="2" t="s">
         <v>1090</v>
@@ -61992,8 +62072,10 @@
       <c r="AX356" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY356" s="2" t="s">
-        <v>1459</v>
+      <c r="AY356" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ356" s="2" t="s">
         <v>1090</v>
@@ -62260,8 +62342,10 @@
       <c r="AX358" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY358" s="2" t="s">
-        <v>1459</v>
+      <c r="AY358" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ358" s="2" t="s">
         <v>1090</v>
@@ -62415,8 +62499,10 @@
       <c r="AX359" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY359" s="2" t="s">
-        <v>1459</v>
+      <c r="AY359" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ359" s="2" t="s">
         <v>1090</v>
@@ -62548,8 +62634,10 @@
       <c r="AX360" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY360" s="2" t="s">
-        <v>1459</v>
+      <c r="AY360" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ360" s="2" t="s">
         <v>1090</v>
@@ -62841,8 +62929,10 @@
       <c r="AX362" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY362" s="2" t="s">
-        <v>1459</v>
+      <c r="AY362" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ362" s="2" t="s">
         <v>1090</v>
@@ -63124,8 +63214,10 @@
       <c r="AX364" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY364" s="2" t="s">
-        <v>1459</v>
+      <c r="AY364" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ364" s="2" t="s">
         <v>1090</v>
@@ -63259,8 +63351,10 @@
       <c r="AX365" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY365" s="2" t="s">
-        <v>1459</v>
+      <c r="AY365" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ365" s="2" t="s">
         <v>1090</v>
@@ -63817,8 +63911,10 @@
       <c r="AX369" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY369" s="2" t="s">
-        <v>1459</v>
+      <c r="AY369" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ369" s="2" t="s">
         <v>1090</v>
@@ -63954,8 +64050,10 @@
       <c r="AX370" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AY370" s="2" t="s">
-        <v>1459</v>
+      <c r="AY370" s="2" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
       <c r="AZ370" s="2" t="s">
         <v>1090</v>
@@ -64980,11 +65078,15 @@
       <c r="AS377" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AT377" s="8" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AU377" s="8" t="s">
-        <v>1090</v>
+      <c r="AT377" s="8" t="inlineStr">
+        <is>
+          <t>63047</t>
+        </is>
+      </c>
+      <c r="AU377" s="8" t="inlineStr">
+        <is>
+          <t>CO_197 - Precertification/authorization/notification/pre-treatment absent</t>
+        </is>
       </c>
       <c r="AV377" s="8" t="s">
         <v>1090</v>
@@ -65426,11 +65528,15 @@
       <c r="AQ380" s="6">
         <v>46049</v>
       </c>
-      <c r="AR380" s="8" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AS380" s="8" t="s">
-        <v>1090</v>
+      <c r="AR380" s="8" t="inlineStr">
+        <is>
+          <t>27279</t>
+        </is>
+      </c>
+      <c r="AS380" s="8" t="inlineStr">
+        <is>
+          <t>PR_1 - Patient Responsibility - Deductible Amount</t>
+        </is>
       </c>
       <c r="AT380" s="8" t="s">
         <v>1090</v>
@@ -67206,11 +67312,15 @@
       <c r="AQ391" s="6">
         <v>46211</v>
       </c>
-      <c r="AR391" s="8" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AS391" s="8" t="s">
-        <v>1090</v>
+      <c r="AR391" s="8" t="inlineStr">
+        <is>
+          <t>A6023</t>
+        </is>
+      </c>
+      <c r="AS391" s="8" t="inlineStr">
+        <is>
+          <t>M2 - Not paid separately when the patient is an inpatient</t>
+        </is>
       </c>
       <c r="AT391" s="8" t="s">
         <v>1090</v>
@@ -68272,11 +68382,15 @@
       <c r="AQ398" s="6">
         <v>46204</v>
       </c>
-      <c r="AR398" s="8" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AS398" s="8" t="s">
-        <v>1090</v>
+      <c r="AR398" s="8" t="inlineStr">
+        <is>
+          <t>L0650</t>
+        </is>
+      </c>
+      <c r="AS398" s="8" t="inlineStr">
+        <is>
+          <t>M3 - Equipment is the same or similar to equipment already being used</t>
+        </is>
       </c>
       <c r="AT398" s="8" t="s">
         <v>1090</v>
@@ -69206,8 +69320,10 @@
       <c r="AU404" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AV404" s="8" t="s">
-        <v>141</v>
+      <c r="AV404" s="8" t="inlineStr">
+        <is>
+          <t>99493, 99494</t>
+        </is>
       </c>
       <c r="AW404" s="8" t="s">
         <v>1090</v>
@@ -72228,11 +72344,15 @@
       <c r="AQ424" s="6">
         <v>46180</v>
       </c>
-      <c r="AR424" s="8" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AS424" s="8" t="s">
-        <v>1090</v>
+      <c r="AR424" s="8" t="inlineStr">
+        <is>
+          <t>99492, 99494</t>
+        </is>
+      </c>
+      <c r="AS424" s="8" t="inlineStr">
+        <is>
+          <t>PR_1 - Patient Responsibility - Deductible Amount</t>
+        </is>
       </c>
       <c r="AT424" s="8" t="s">
         <v>1090</v>
@@ -73148,11 +73268,15 @@
       <c r="AS430" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AT430" s="8" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AU430" s="8" t="s">
-        <v>1090</v>
+      <c r="AT430" s="8" t="inlineStr">
+        <is>
+          <t>93923, 93925</t>
+        </is>
+      </c>
+      <c r="AU430" s="8" t="inlineStr">
+        <is>
+          <t>CO_146 - Diagnosis was invalid for the date(s) of service reported</t>
+        </is>
       </c>
       <c r="AV430" s="8" t="s">
         <v>1090</v>
@@ -74657,11 +74781,15 @@
       <c r="AQ440" s="6">
         <v>46182</v>
       </c>
-      <c r="AR440" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="AS440" s="8" t="s">
-        <v>1549</v>
+      <c r="AR440" s="8" t="inlineStr">
+        <is>
+          <t>36248, 37242</t>
+        </is>
+      </c>
+      <c r="AS440" s="8" t="inlineStr">
+        <is>
+          <t>CO_B15 (36248) - This service/procedure requires that a qualifying service/procedure be received and covered; CO_55 (37242) - Procedure/treatment/drug is deemed experimental/investigational by the payer</t>
+        </is>
       </c>
       <c r="AT440" s="8" t="s">
         <v>1090</v>
@@ -75577,11 +75705,15 @@
       <c r="AS446" s="8" t="s">
         <v>1090</v>
       </c>
-      <c r="AT446" s="8" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AU446" s="8" t="s">
-        <v>1090</v>
+      <c r="AT446" s="8" t="inlineStr">
+        <is>
+          <t>64708, 63047</t>
+        </is>
+      </c>
+      <c r="AU446" s="8" t="inlineStr">
+        <is>
+          <t>PR_96 - Non-covered charge(s)</t>
+        </is>
       </c>
       <c r="AV446" s="8" t="s">
         <v>1090</v>
@@ -75721,11 +75853,15 @@
       <c r="AQ447" s="6">
         <v>46161</v>
       </c>
-      <c r="AR447" s="8" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AS447" s="8" t="s">
-        <v>1090</v>
+      <c r="AR447" s="8" t="inlineStr">
+        <is>
+          <t>63047</t>
+        </is>
+      </c>
+      <c r="AS447" s="8" t="inlineStr">
+        <is>
+          <t>CO_96 - Non-covered charge(s)</t>
+        </is>
       </c>
       <c r="AT447" s="8" t="s">
         <v>1090</v>
@@ -79859,11 +79995,15 @@
       <c r="AQ474" s="6">
         <v>46093</v>
       </c>
-      <c r="AR474" s="8" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AS474" s="8" t="s">
-        <v>1090</v>
+      <c r="AR474" s="8" t="inlineStr">
+        <is>
+          <t>L0650</t>
+        </is>
+      </c>
+      <c r="AS474" s="8" t="inlineStr">
+        <is>
+          <t>M3 - Equipment is the same or similar to equipment already being used</t>
+        </is>
       </c>
       <c r="AT474" s="8" t="s">
         <v>1090</v>
@@ -81075,11 +81215,15 @@
       <c r="AQ482" s="6">
         <v>46118</v>
       </c>
-      <c r="AR482" s="8" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AS482" s="8" t="s">
-        <v>1090</v>
+      <c r="AR482" s="8" t="inlineStr">
+        <is>
+          <t>L0650</t>
+        </is>
+      </c>
+      <c r="AS482" s="8" t="inlineStr">
+        <is>
+          <t>M3 - Equipment is the same or similar to equipment already being used</t>
+        </is>
       </c>
       <c r="AT482" s="8" t="s">
         <v>1090</v>
@@ -81375,11 +81519,15 @@
       <c r="AQ484" s="6">
         <v>46133</v>
       </c>
-      <c r="AR484" s="8" t="s">
-        <v>1090</v>
-      </c>
-      <c r="AS484" s="8" t="s">
-        <v>1090</v>
+      <c r="AR484" s="8" t="inlineStr">
+        <is>
+          <t>L0650</t>
+        </is>
+      </c>
+      <c r="AS484" s="8" t="inlineStr">
+        <is>
+          <t>M3 - Equipment is the same or similar to equipment already being used</t>
+        </is>
       </c>
       <c r="AT484" s="8" t="s">
         <v>1090</v>
@@ -85021,6 +85169,11 @@
       </c>
       <c r="B20" t="s">
         <v>1838</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Under Review</t>
+        </is>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">

--- a/Master Updates.xlsx
+++ b/Master Updates.xlsx
@@ -15677,7 +15677,7 @@
         <v>132</v>
       </c>
       <c r="AW58" s="8" t="s">
-        <v>325</v>
+        <v>1090</v>
       </c>
       <c r="AX58" s="8" t="s">
         <v>1519</v>

--- a/Master Updates.xlsx
+++ b/Master Updates.xlsx
@@ -7630,8 +7630,10 @@
       <c r="A7" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>1096</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uploaded MR on portal - Case ID# 18151</t>
+        </is>
       </c>
       <c r="C7" s="3">
         <v>568271516</v>
@@ -7772,8 +7774,10 @@
       <c r="A8" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>1097</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added mod 24, and resubmitted - Denied: 99493 is included in the global period of 64635 on Claim ID RC2772466500 Line ID 1, DOS 03/24/2026</t>
+        </is>
       </c>
       <c r="C8" s="3">
         <v>554160244</v>
@@ -7926,8 +7930,10 @@
       <c r="A9" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>1098</v>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MR needed - Requesting from Juan</t>
+        </is>
       </c>
       <c r="C9" s="3">
         <v>568316185</v>
@@ -8238,8 +8244,10 @@
       <c r="A11" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>1100</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uploaded MR on portal - Case ID# 18149</t>
+        </is>
       </c>
       <c r="C11" s="3">
         <v>568312031</v>
@@ -8536,8 +8544,10 @@
       <c r="A13" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>1102</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected claim, and resubmitted - by Tina - Filed recon with MR - PIQ-89945925</t>
+        </is>
       </c>
       <c r="C13" s="3">
         <v>573339755</v>
@@ -8692,8 +8702,10 @@
       <c r="A14" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>1103</v>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted - Renee Oroc credentialing issue - Remark MA130: multiple submission/billing errors, unable to adjudicate claim as submitted</t>
+        </is>
       </c>
       <c r="C14" s="3">
         <v>557506616</v>
@@ -8848,8 +8860,10 @@
       <c r="A15" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>1104</v>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected referring provider, and resubmitted</t>
+        </is>
       </c>
       <c r="C15" s="3">
         <v>568470154</v>
@@ -9486,8 +9500,10 @@
       <c r="A19" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>1817</v>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Checking with D - Adjust, or ask scribe to correct notes</t>
+        </is>
       </c>
       <c r="C19" s="3">
         <v>570821252</v>
@@ -9648,8 +9664,10 @@
       <c r="A20" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>1106</v>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Checking with D - Adjust 99204 or change the encounter notes</t>
+        </is>
       </c>
       <c r="C20" s="3">
         <v>560610028</v>
@@ -9810,8 +9828,10 @@
       <c r="A21" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>1088</v>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OP - BCBS - Refund needed</t>
+        </is>
       </c>
       <c r="C21" s="3">
         <v>562125174</v>
@@ -9966,8 +9986,10 @@
       <c r="A22" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>1088</v>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OP - BCBS - Refund needed</t>
+        </is>
       </c>
       <c r="C22" s="3">
         <v>563181415</v>
@@ -10126,8 +10148,10 @@
       <c r="A23" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>1107</v>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moved mod 25 from 62323 to 99204, and resubmitted</t>
+        </is>
       </c>
       <c r="C23" s="3">
         <v>563596494</v>
@@ -10280,8 +10304,10 @@
       <c r="A24" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>1108</v>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Called AZ Priority Care and BCBS - Rep MousamK - Call ref # 12696890 - Clarification requested and escalated to confirm the payer - by Tina - Resubmitted to APCP - Rep Heather: member is assigned to an affiliated network (Arizona Priority Care)</t>
+        </is>
       </c>
       <c r="C24" s="3">
         <v>569646388</v>
@@ -10434,8 +10460,10 @@
       <c r="A25" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>1110</v>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Corrected adjustments, and resubmitted</t>
+        </is>
       </c>
       <c r="C25" s="3">
         <v>546184427</v>
@@ -10904,8 +10932,10 @@
       <c r="A28" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>1088</v>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OP - Void original claim 547459229</t>
+        </is>
       </c>
       <c r="C28" s="3">
         <v>555109108</v>
@@ -11058,8 +11088,10 @@
       <c r="A29" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>1112</v>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed recon with MR - by Jess - Optum letter ref # 70293624: 99492 denied because MR shows POS 11 (office) but the claim was billed POS 10 (telehealth in patient's home), so the claim can't be verified</t>
+        </is>
       </c>
       <c r="C29" s="3">
         <v>545748574</v>
@@ -11212,8 +11244,10 @@
       <c r="A30" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>1113</v>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed recon with MR - Recon # BOT3951067 - No waiver for 63047: Carrum A0 exclusion lists fusion, but 63047 is decompression (no fusion billed) - Asked payer to reprocess or provide the plan language for the denial</t>
+        </is>
       </c>
       <c r="C30" s="3">
         <v>545934422</v>
@@ -11514,8 +11548,10 @@
       <c r="A32" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>1088</v>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OP - Void original claim 547855520</t>
+        </is>
       </c>
       <c r="C32" s="3">
         <v>548717876</v>
@@ -11820,8 +11856,10 @@
       <c r="A34" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>1116</v>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professional claim, no revenue code needed - Filed recon with duplex report - Uploaded MR</t>
+        </is>
       </c>
       <c r="C34" s="3">
         <v>547465291</v>
@@ -11974,8 +12012,10 @@
       <c r="A35" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>1117</v>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Called payer - Rep Muthamma - Call ref # 10605826 - TAT 15 days</t>
+        </is>
       </c>
       <c r="C35" s="3">
         <v>548015539</v>
@@ -12128,8 +12168,10 @@
       <c r="A36" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>1118</v>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Resubmitted to AmeTrust</t>
+        </is>
       </c>
       <c r="C36" s="3">
         <v>547442681</v>
@@ -12284,8 +12326,10 @@
       <c r="A37" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>1119</v>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Handled by Deanne - Called BCBS AZ - Rep Heather: per the provider's contract the allowed amount is $0.00 (contractual adjustment = billed charges minus the non-covered/denied allowed amount, not a payable allowance) - Case # 10628911 - Rep Mage E: payer canceled the appeal, claim was forwarded to Anthem with zero price and no allowed amount - Pricing issue with local plan - Filed appeal - Request APP-COMM-6695304</t>
+        </is>
       </c>
       <c r="C37" s="3">
         <v>547576017</v>
@@ -12438,8 +12482,10 @@
       <c r="A38" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>1120</v>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Corrected charges for A6219, and resubmitted</t>
+        </is>
       </c>
       <c r="C38" s="3">
         <v>557162806</v>
@@ -12752,8 +12798,10 @@
       <c r="A40" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>1123</v>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Changed 99493 to 99492, and resubmitted - Filed recon - Claim 26A635462200 DOS 01/27/26: 99493 denied, no prior CoCM in 6 months; prior 99493 DOS 12/16/25 paid on claim 26A070631100 under old ID 2062477 - Requested reprocess, PRA attached - Added Date of Current Illness, claim note, and resubmitted</t>
+        </is>
       </c>
       <c r="C40" s="3">
         <v>573875345</v>
@@ -12906,8 +12954,10 @@
       <c r="A41" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>1124</v>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not shifting to PT - Working on it - Shifted to PT earlier - Payer didn't receive PT's update</t>
+        </is>
       </c>
       <c r="C41" s="3">
         <v>547976909</v>
@@ -13060,8 +13110,10 @@
       <c r="A42" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>1125</v>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed recon with MR - PIQ-92451492 - 93970 denial: sent signed report showing bilateral compression/augmentation - by Jess</t>
+        </is>
       </c>
       <c r="C42" s="3">
         <v>548573158</v>
@@ -13216,8 +13268,10 @@
       <c r="A43" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>1126</v>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Called payer - Rep Briana - Call ref # 11216220 - Dr. Leathem is not contracted with member's Focus Network</t>
+        </is>
       </c>
       <c r="C43" s="3">
         <v>548676737</v>
@@ -13370,8 +13424,10 @@
       <c r="A44" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>1127</v>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deanne reviewing - Called payer - Rep Jessie - Claim has a non-anesthesia service but payer lists the rendering provider as an anesthesiologist</t>
+        </is>
       </c>
       <c r="C44" s="3">
         <v>555677002</v>
@@ -13680,8 +13736,10 @@
       <c r="A46" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>1118</v>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Resubmitted to AmeTrust</t>
+        </is>
       </c>
       <c r="C46" s="3">
         <v>549765437</v>
@@ -13836,8 +13894,10 @@
       <c r="A47" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>1128</v>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected dx to G894, added auth #, and resubmitted - VA doesn't cover BH - Rejected: invalid dx - ASAP Deer Valley NPI missing - Resubmitted</t>
+        </is>
       </c>
       <c r="C47" s="3">
         <v>574453982</v>
@@ -14142,8 +14202,10 @@
       <c r="A49" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>1129</v>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provider active - Resubmitted</t>
+        </is>
       </c>
       <c r="C49" s="3">
         <v>557784595</v>
@@ -14312,8 +14374,10 @@
       <c r="A50" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>1130</v>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auth issue - Resubmitted - by Bri - Provider Tax ID/NPI combination not on file with BCBS AZ</t>
+        </is>
       </c>
       <c r="C50" s="3">
         <v>565140993</v>
@@ -14472,8 +14536,10 @@
       <c r="A51" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>1131</v>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99492 paid on DOS 01/27/2026 - Resubmitted - Waiting on claim #556349314 (DOS 01/27/2026) before reprocessing - 99493 denied: non-payable code for required reporting only - Added Date of Current Illness, claim note, and resubmitted</t>
+        </is>
       </c>
       <c r="C51" s="3">
         <v>557794882</v>
@@ -14626,8 +14692,10 @@
       <c r="A52" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>1132</v>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Called payer - Rep Muthamma - Call ref # 11253575</t>
+        </is>
       </c>
       <c r="C52" s="3">
         <v>550288006</v>
@@ -14780,8 +14848,10 @@
       <c r="A53" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>1133</v>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - No auth on file - Checking whether auth is needed on Curo portal # 19801266</t>
+        </is>
       </c>
       <c r="C53" s="3">
         <v>550530483</v>
@@ -14932,8 +15002,10 @@
       <c r="A54" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>1134</v>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Changed 99493 to 99492, and resubmitted</t>
+        </is>
       </c>
       <c r="C54" s="3">
         <v>557794229</v>
@@ -15082,8 +15154,10 @@
       <c r="A55" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>1135</v>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Changed 99493 to 99492, and resubmitted - Recon not available on portal because the claim was already adjusted - 99493 paid on claim 26A074466600, DOS 12/12/2025, under prior member ID 1718676 - Current claim billed with active member ID 906162197 - Added Date of Current Illness, claim note, and resubmitted</t>
+        </is>
       </c>
       <c r="C55" s="3">
         <v>557793858</v>
@@ -15234,8 +15308,10 @@
           <t>Denied</t>
         </is>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>1907</v>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claim 568613230 was paid - Removed mod 58, and resubmitted - Added mod 58, and resubmitted</t>
+        </is>
       </c>
       <c r="C56" s="3">
         <v>562083380</v>
@@ -15548,8 +15624,10 @@
       <c r="A58" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>1137</v>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected dx order, and resubmitted</t>
+        </is>
       </c>
       <c r="C58" s="3">
         <v>571606836</v>
@@ -15708,8 +15786,10 @@
       <c r="A59" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>1138</v>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected rendering provider to Timothy Baugher (was Jarrett Leathem), and resubmitted - by Jess</t>
+        </is>
       </c>
       <c r="C59" s="3">
         <v>566722180</v>
@@ -15862,8 +15942,10 @@
       <c r="A60" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>1139</v>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed recon by fax (615-401-4642) - by Christian J</t>
+        </is>
       </c>
       <c r="C60" s="3">
         <v>552284225</v>
@@ -16020,8 +16102,10 @@
       <c r="A61" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>1140</v>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Optum had no record of 99492 (billed to UHC, not Optum) - Resubmitted with 99492</t>
+        </is>
       </c>
       <c r="C61" s="3">
         <v>551769931</v>
@@ -16322,8 +16406,10 @@
       <c r="A63" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>1142</v>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - OP by secondary - Called payer - Rep Gloria C - Payer started the refund request and sent the claim back for reprocessing - Ticket # SF20260903906271400 - TAT 30 business days</t>
+        </is>
       </c>
       <c r="C63" s="3">
         <v>551830492</v>
@@ -16626,8 +16712,10 @@
       <c r="A65" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>1144</v>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed appeal on portal with op note - Appeal # Z264AZW09999 - Basis: 63048 is an add-on to auth'd/paid 63047, intraop findings - Medicaid auth tool shows add-on 63048 requires auth - Auth # OP4987640976 didn't include 63048</t>
+        </is>
       </c>
       <c r="C65" s="3">
         <v>564578362</v>
@@ -16940,8 +17028,10 @@
       <c r="A67" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>1145</v>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted to Alignment - Active on DOS</t>
+        </is>
       </c>
       <c r="C67" s="3">
         <v>569488863</v>
@@ -17075,8 +17165,10 @@
       <c r="A68" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>1146</v>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted on 08/31/2026 - by Jess</t>
+        </is>
       </c>
       <c r="C68" s="3">
         <v>570400502</v>
@@ -17235,8 +17327,10 @@
       <c r="A69" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>1147</v>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uploaded MR (op notes 03/12/2026 to 03/15/2026) - by Jess</t>
+        </is>
       </c>
       <c r="C69" s="3">
         <v>553656838</v>
@@ -17547,8 +17641,10 @@
       <c r="A71" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>1148</v>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Updated insured's info, and resubmitted</t>
+        </is>
       </c>
       <c r="C71" s="3">
         <v>570820956</v>
@@ -17857,8 +17953,10 @@
       <c r="A73" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>1150</v>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected CPT codes, added code 7, and resubmitted</t>
+        </is>
       </c>
       <c r="C73" s="3">
         <v>571612561</v>
@@ -18173,8 +18271,10 @@
       <c r="A75" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>1151</v>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed recon with MR (02/27/2026 order notes for BHE prior to SCS trial + March 2026 Monthly Review Summary) - by Jess</t>
+        </is>
       </c>
       <c r="C75" s="3">
         <v>553133483</v>
@@ -18327,8 +18427,10 @@
       <c r="A76" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>1153</v>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Resubmitted to Tricare for Life - Claim not found on portal (sent to Tricare West, can't locate it on Availity)</t>
+        </is>
       </c>
       <c r="C76" s="3">
         <v>553857983</v>
@@ -18645,8 +18747,10 @@
       <c r="A78" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>1154</v>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OP (possible) - Optum - Duplicate payment: checks VP3502669763 and 5533489 - VP3502669763 not found in NGO or Optum - Posting team notified to review</t>
+        </is>
       </c>
       <c r="C78" s="3">
         <v>553362911</v>
@@ -18801,8 +18905,10 @@
       <c r="A79" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B79" s="2" t="s">
-        <v>1155</v>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Emailed AZ Blue for details - Active coverage on DOS</t>
+        </is>
       </c>
       <c r="C79" s="3">
         <v>571907149</v>
@@ -19271,8 +19377,10 @@
       <c r="A82" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>1157</v>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Bundled with Claim ID 26F500108500 Line ID 1, DOS 03/24/2026, CPT 64640</t>
+        </is>
       </c>
       <c r="C82" s="3">
         <v>563362114</v>
@@ -19423,8 +19531,10 @@
       <c r="A83" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>1158</v>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99492 paid - Resubmitted - Reprocess when claim 570543000 is paid</t>
+        </is>
       </c>
       <c r="C83" s="3">
         <v>554088972</v>
@@ -19577,8 +19687,10 @@
       <c r="A84" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>1159</v>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted - by Jess</t>
+        </is>
       </c>
       <c r="C84" s="3">
         <v>566720408</v>
@@ -19889,8 +20001,10 @@
       <c r="A86" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>1160</v>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uploaded MR per payer request - PIQ-91107053</t>
+        </is>
       </c>
       <c r="C86" s="3">
         <v>558304247</v>
@@ -20047,8 +20161,10 @@
       <c r="A87" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>1161</v>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Corrected dx codes, and resubmitted</t>
+        </is>
       </c>
       <c r="C87" s="3">
         <v>553787632</v>
@@ -20199,8 +20315,10 @@
       <c r="A88" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B88" s="2" t="s">
-        <v>1162</v>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Appeal form completed with MR - Sent to April to fax to payer (855-699-8985)</t>
+        </is>
       </c>
       <c r="C88" s="3">
         <v>555586629</v>
@@ -20353,8 +20471,10 @@
       <c r="A89" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>1163</v>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - 36246 not included in auth - 36248 add-on requires payment of the primary code - 99153 can't be billed with POS 24</t>
+        </is>
       </c>
       <c r="C89" s="3">
         <v>558554119</v>
@@ -20523,8 +20643,10 @@
       <c r="A90" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>1164</v>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denied as bundled - Auth on file</t>
+        </is>
       </c>
       <c r="C90" s="3">
         <v>559115526</v>
@@ -20837,8 +20959,10 @@
       <c r="A92" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>1166</v>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denied for timely filing, but this was a resubmission - Resubmitted - Changed 93970 to 93971, and resubmitted</t>
+        </is>
       </c>
       <c r="C92" s="3">
         <v>558308311</v>
@@ -21147,8 +21271,10 @@
       <c r="A94" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>1167</v>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denied - Preferred Homecare is the delegated vendor (800-636-2123)</t>
+        </is>
       </c>
       <c r="C94" s="3">
         <v>556770603</v>
@@ -21305,8 +21431,10 @@
       <c r="A95" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>1167</v>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denied - Preferred Homecare is the delegated vendor (800-636-2123)</t>
+        </is>
       </c>
       <c r="C95" s="3">
         <v>556772233</v>
@@ -21461,8 +21589,10 @@
       <c r="A96" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>1168</v>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed - Rep Mark confirmed Integra is the delegated DME vendor for this PT - Provider OON with Devoted</t>
+        </is>
       </c>
       <c r="C96" s="3">
         <v>559115746</v>
@@ -22093,8 +22223,10 @@
       <c r="A100" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>1170</v>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uploaded MR - Removed line 20936, and resubmitted</t>
+        </is>
       </c>
       <c r="C100" s="3">
         <v>569505824</v>
@@ -22257,8 +22389,10 @@
       <c r="A101" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>1171</v>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uploaded missing MR - PIQ-85007180 - Uploaded POD - by Jess</t>
+        </is>
       </c>
       <c r="C101" s="3">
         <v>561043971</v>
@@ -22411,8 +22545,10 @@
       <c r="A102" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>1167</v>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denied - Preferred Homecare is the delegated vendor (800-636-2123)</t>
+        </is>
       </c>
       <c r="C102" s="3">
         <v>565388312</v>
@@ -22569,8 +22705,10 @@
       <c r="A103" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>1172</v>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Submitted to BCBS (BCBS primary, Banner Aetna secondary) - Removed mod 79, added mod 24, and resubmitted - Payer edits only allow 79/78/58 on surgical/procedural codes; 99492 is an E/M - Resubmitted with mod 79 - by Jess</t>
+        </is>
       </c>
       <c r="C103" s="3">
         <v>573878565</v>
@@ -22723,8 +22861,10 @@
       <c r="A104" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>1173</v>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asked Linda W. to fax MR to 480-499-8744 - MR due 08/18/2026</t>
+        </is>
       </c>
       <c r="C104" s="3">
         <v>559861642</v>
@@ -22879,8 +23019,10 @@
       <c r="A105" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>1174</v>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid</t>
+        </is>
       </c>
       <c r="C105" s="3">
         <v>553378154</v>
@@ -23027,8 +23169,10 @@
       <c r="A106" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B106" s="2" t="s">
-        <v>1175</v>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Checking with credentialing team - Dr. Sarkar OON</t>
+        </is>
       </c>
       <c r="C106" s="3">
         <v>556564886</v>
@@ -23183,8 +23327,10 @@
       <c r="A107" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>1176</v>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Added COB info, and resubmitted</t>
+        </is>
       </c>
       <c r="C107" s="3">
         <v>558686710</v>
@@ -23361,8 +23507,10 @@
       <c r="A108" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>1167</v>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denied - Preferred Homecare is the delegated vendor (800-636-2123)</t>
+        </is>
       </c>
       <c r="C108" s="3">
         <v>556833981</v>
@@ -23675,8 +23823,10 @@
       <c r="A110" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>1177</v>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uploaded MR per payer request - Request ID 35635409 - All CPT codes denied as not covered</t>
+        </is>
       </c>
       <c r="C110" s="3">
         <v>563133469</v>
@@ -23837,8 +23987,10 @@
       <c r="A111" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>1178</v>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Checking PT eligibility on DOS - by Tina</t>
+        </is>
       </c>
       <c r="C111" s="3">
         <v>570556425</v>
@@ -23993,8 +24145,10 @@
       <c r="A112" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B112" s="2" t="s">
-        <v>1179</v>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MR under PIQ review - Status pending</t>
+        </is>
       </c>
       <c r="C112" s="3">
         <v>565376983</v>
@@ -24299,8 +24453,10 @@
       <c r="A114" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>1181</v>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed recon - Decision ID # D600552039 shows NAR</t>
+        </is>
       </c>
       <c r="C114" s="3">
         <v>558377934</v>
@@ -24457,8 +24613,10 @@
       <c r="A115" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>1182</v>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per Medicare guidelines, mod NU is not typical for L1851 - Resubmitted with mods KX+RT - Medicare Advantage plan - Resubmitted with mod NU only - by Jess</t>
+        </is>
       </c>
       <c r="C115" s="3">
         <v>572320097</v>
@@ -24748,8 +24906,10 @@
       <c r="A117" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>1184</v>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed line 20930 and dx M542 on portal (action required) - Dx M542 and M5030 can't be reported together - 20930 is inclusive to other services reported - Claim downloaded</t>
+        </is>
       </c>
       <c r="C117" s="3">
         <v>558405759</v>
@@ -24914,8 +25074,10 @@
       <c r="A118" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>1185</v>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Added SCS referral #, and resubmitted - Not expected to pay: VA doesn't cover BH and we don't have an RFS</t>
+        </is>
       </c>
       <c r="C118" s="3">
         <v>554404221</v>
@@ -25218,8 +25380,10 @@
       <c r="A120" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B120" s="2" t="s">
-        <v>1187</v>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - 1A95CU0TY97</t>
+        </is>
       </c>
       <c r="C120" s="3">
         <v>558643419</v>
@@ -25374,8 +25538,10 @@
       <c r="A121" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>1167</v>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denied - Preferred Homecare is the delegated vendor (800-636-2123)</t>
+        </is>
       </c>
       <c r="C121" s="3">
         <v>558739471</v>
@@ -25532,8 +25698,10 @@
       <c r="A122" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>1188</v>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uploaded MR (fax, with barcode letter) - by Jess - Confirming receipt with Anthem</t>
+        </is>
       </c>
       <c r="C122" s="3">
         <v>562340666</v>
@@ -25694,8 +25862,10 @@
       <c r="A123" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>1189</v>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted - Aisha reviewed Dr. Adler's status on the AHCCCS portal: active since 2012 - Rendering OON with Medicaid AHCCCS - Confirming with Bri - DOS worked: 05/01/2026</t>
+        </is>
       </c>
       <c r="C123" s="3">
         <v>573882260</v>
@@ -25848,8 +26018,10 @@
       <c r="A124" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>1190</v>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Called payer - Rep Harold C - Call ref # 372182510 - Claim didn't price to the market fee schedule in effect on DOS - Claim sent back for reprocessing - TAT 30 days - ERA shows no allowed amount; payer moved the full billed charge to PT</t>
+        </is>
       </c>
       <c r="C124" s="3">
         <v>556732851</v>
@@ -26173,8 +26345,10 @@
       <c r="A126" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>1191</v>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Still processing - Payer received claim on 07/20/2026</t>
+        </is>
       </c>
       <c r="C126" s="3">
         <v>559374682</v>
@@ -26331,8 +26505,10 @@
       <c r="A127" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>1192</v>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed dispute with MR - Dispute ID PDX7G8WCG9</t>
+        </is>
       </c>
       <c r="C127" s="3">
         <v>565099868</v>
@@ -26505,8 +26681,10 @@
       <c r="A128" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>1193</v>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - No auth on file - Retro auth not available - Submitted claim on portal with MR</t>
+        </is>
       </c>
       <c r="C128" s="3">
         <v>556762240</v>
@@ -26657,8 +26835,10 @@
       <c r="A129" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>1194</v>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Requested auth on portal - Status: Not certified - NAR received was for 62330, which doesn't require auth per Availity portal</t>
+        </is>
       </c>
       <c r="C129" s="3">
         <v>554827888</v>
@@ -26809,8 +26989,10 @@
       <c r="A130" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B130" s="2" t="s">
-        <v>1195</v>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Corrected mod, and resubmitted</t>
+        </is>
       </c>
       <c r="C130" s="3">
         <v>559005954</v>
@@ -27115,8 +27297,10 @@
       <c r="A132" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>1197</v>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted - Denied for timely filing - Removed line 80307, and resubmitted corrected claim - by Tina</t>
+        </is>
       </c>
       <c r="C132" s="3">
         <v>558351506</v>
@@ -27419,8 +27603,10 @@
       <c r="A134" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B134" s="2" t="s">
-        <v>1199</v>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Changed 93923 to 93922, and resubmitted - 93923 requires 3 levels; report shows only ankle + toe (2 levels) - Resubmitted by mail - by April - Uploaded MR - by DMinker30A</t>
+        </is>
       </c>
       <c r="C134" s="3">
         <v>569778058</v>
@@ -27581,8 +27767,10 @@
       <c r="A135" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>1200</v>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Corrected rendering provider, and resubmitted</t>
+        </is>
       </c>
       <c r="C135" s="3">
         <v>559736857</v>
@@ -27733,8 +27921,10 @@
       <c r="A136" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>1201</v>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Added active referral for DOS, and resubmitted - VA doesn't cover BH; separate RFS approval needed for BH coverage</t>
+        </is>
       </c>
       <c r="C136" s="3">
         <v>555379100</v>
@@ -28209,8 +28399,10 @@
       <c r="A139" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>1204</v>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Corrected claim, and resubmitted on 08/03/2026 - by DMinker30A</t>
+        </is>
       </c>
       <c r="C139" s="3">
         <v>567453889</v>
@@ -28361,8 +28553,10 @@
       <c r="A140" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B140" s="2" t="s">
-        <v>1205</v>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed line 20936, and resubmitted</t>
+        </is>
       </c>
       <c r="C140" s="3">
         <v>568203238</v>
@@ -29139,8 +29333,10 @@
       <c r="A145" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B145" s="2" t="s">
-        <v>1207</v>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MR requested - Removed line A6219, and resubmitted</t>
+        </is>
       </c>
       <c r="C145" s="3">
         <v>568211905</v>
@@ -29767,8 +29963,10 @@
       <c r="A149" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B149" s="2" t="s">
-        <v>1211</v>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed recon with MR and WC denied auth #910943907 - Unchecked employment box, restored dx order, and resubmitted - Rejected again - Changed employment dx to primary, added dx Y990 and claim note, and resubmitted</t>
+        </is>
       </c>
       <c r="C149" s="3">
         <v>568526020</v>
@@ -29925,8 +30123,10 @@
       <c r="A150" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>1212</v>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Changed service line 1 to 99492, and resubmitted - Processed date 06/16/2026</t>
+        </is>
       </c>
       <c r="C150" s="3">
         <v>559931934</v>
@@ -30077,8 +30277,10 @@
       <c r="A151" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B151" s="2" t="s">
-        <v>1213</v>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Changed service line 1 to 99492, and resubmitted - Processed date 06/10/2026</t>
+        </is>
       </c>
       <c r="C151" s="3">
         <v>560175340</v>
@@ -30826,8 +31028,10 @@
       <c r="A156" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B156" s="2" t="s">
-        <v>1215</v>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Corrected dx for 93970, and resubmitted</t>
+        </is>
       </c>
       <c r="C156" s="3">
         <v>560711490</v>
@@ -30978,8 +31182,10 @@
       <c r="A157" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>1216</v>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Filed recon - Decision ID # D606429361</t>
+        </is>
       </c>
       <c r="C157" s="3">
         <v>563202144</v>
@@ -31132,8 +31338,10 @@
       <c r="A158" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>1217</v>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Corrected dx for 93970, removed line 93923, and resubmitted</t>
+        </is>
       </c>
       <c r="C158" s="3">
         <v>560713422</v>
@@ -31292,8 +31500,10 @@
       <c r="A159" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>1218</v>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uploaded MR - Dispute ID PDXEFY2R66 - Rep Ria U said MR was needed</t>
+        </is>
       </c>
       <c r="C159" s="3">
         <v>564111540</v>
@@ -31604,8 +31814,10 @@
       <c r="A161" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>1220</v>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99492 paid on DOS 02/20/2026 - Resubmitted</t>
+        </is>
       </c>
       <c r="C161" s="3">
         <v>560664762</v>
@@ -31914,8 +32126,10 @@
       <c r="A163" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B163" s="2" t="s">
-        <v>1222</v>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Billed 93923 separately on portal</t>
+        </is>
       </c>
       <c r="C163" s="3">
         <v>558643526</v>
@@ -32064,8 +32278,10 @@
       <c r="A164" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B164" s="2" t="s">
-        <v>1223</v>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Changed POS from 11 to 24 and location to ASAP Surgery Centers North Valley, and resubmitted</t>
+        </is>
       </c>
       <c r="C164" s="3">
         <v>561591684</v>
@@ -32388,8 +32604,10 @@
       <c r="A166" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B166" s="2" t="s">
-        <v>1224</v>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed recon with MR for 76937 - by Jess</t>
+        </is>
       </c>
       <c r="C166" s="3">
         <v>565100484</v>
@@ -32722,8 +32940,10 @@
       <c r="A168" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B168" s="2" t="s">
-        <v>1225</v>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected dx codes for 93970 (added I83893, R600), and resubmitted</t>
+        </is>
       </c>
       <c r="C168" s="3">
         <v>570988442</v>
@@ -32876,8 +33096,10 @@
       <c r="A169" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B169" s="2" t="s">
-        <v>1226</v>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Waiting on secondary payment</t>
+        </is>
       </c>
       <c r="C169" s="3">
         <v>561646092</v>
@@ -33836,8 +34058,10 @@
       <c r="A175" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B175" s="2" t="s">
-        <v>1228</v>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed line 20936, and resubmitted</t>
+        </is>
       </c>
       <c r="C175" s="3">
         <v>570979198</v>
@@ -34338,8 +34562,10 @@
       <c r="A178" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B178" s="2" t="s">
-        <v>1229</v>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added mod RT to 36245, corrected dx order, and resubmitted</t>
+        </is>
       </c>
       <c r="C178" s="3">
         <v>570979060</v>
@@ -34508,8 +34734,10 @@
       <c r="A179" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B179" s="2" t="s">
-        <v>1230</v>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT</t>
+        </is>
       </c>
       <c r="C179" s="3">
         <v>562623275</v>
@@ -34658,8 +34886,10 @@
       <c r="A180" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B180" s="2" t="s">
-        <v>1231</v>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denied - Need bar code letter and denial details from payer</t>
+        </is>
       </c>
       <c r="C180" s="3">
         <v>562573309</v>
@@ -34968,8 +35198,10 @@
       <c r="A182" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B182" s="2" t="s">
-        <v>1233</v>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Filed recon with MR</t>
+        </is>
       </c>
       <c r="C182" s="3">
         <v>562698907</v>
@@ -35432,8 +35664,10 @@
       <c r="A185" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B185" s="2" t="s">
-        <v>1235</v>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed appeal by fax (602-544-5601) - by April - Incorrectly sent - Filed appeal by fax (602-544-5601) - by Linda W - Prior auth required per Carelon Medical Benefits Management review (Doc ID: RBM08-1125.1-UC0126, Vascular Imaging Clinical Appropriateness Guidelines) - Carelon is the delegated UM vendor for PT's home plan CDHP Georgia Health Savings Account, Anthem - GA</t>
+        </is>
       </c>
       <c r="C185" s="3">
         <v>563063291</v>
@@ -35586,8 +35820,10 @@
       <c r="A186" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B186" s="2" t="s">
-        <v>1231</v>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denied - Need bar code letter and denial details from payer</t>
+        </is>
       </c>
       <c r="C186" s="3">
         <v>562086355</v>
@@ -35894,8 +36130,10 @@
       <c r="A188" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B188" s="2" t="s">
-        <v>1237</v>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uploaded MR (fax) - by Jess</t>
+        </is>
       </c>
       <c r="C188" s="3">
         <v>562572005</v>
@@ -36050,8 +36288,10 @@
       <c r="A189" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B189" s="2" t="s">
-        <v>1238</v>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claim not found on portal - Resubmitted - Asked April to print</t>
+        </is>
       </c>
       <c r="C189" s="3">
         <v>568765283</v>
@@ -36202,8 +36442,10 @@
       <c r="A190" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B190" s="2" t="s">
-        <v>1239</v>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Uploaded MR - by Jess</t>
+        </is>
       </c>
       <c r="C190" s="3">
         <v>562534504</v>
@@ -36666,8 +36908,10 @@
       <c r="A193" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="B193" s="2" t="s">
-        <v>1238</v>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claim not found on portal - Resubmitted - Asked April to print</t>
+        </is>
       </c>
       <c r="C193" s="3">
         <v>568970208</v>
@@ -36822,8 +37066,10 @@
       <c r="A194" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B194" s="2" t="s">
-        <v>1240</v>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed - No coverage - Policy MP.009.35</t>
+        </is>
       </c>
       <c r="C194" s="3">
         <v>563172458</v>
@@ -36972,8 +37218,10 @@
       <c r="A195" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B195" s="2" t="s">
-        <v>1241</v>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Expected to be denied (not covered) - Resubmitted to BCBS AZ - Group corrected to MAY001 for BCBS AZ (53589) per BCBS AZ portal; A0021 is the Medica-side group only</t>
+        </is>
       </c>
       <c r="C195" s="3">
         <v>570556322</v>
@@ -37276,8 +37524,10 @@
       <c r="A197" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B197" s="2" t="s">
-        <v>1243</v>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed line 20930, and resubmitted</t>
+        </is>
       </c>
       <c r="C197" s="3">
         <v>571013418</v>
@@ -38392,8 +38642,10 @@
       <c r="A204" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B204" s="2" t="s">
-        <v>1245</v>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sent claims inquiry message on portal - ICN 100015364807</t>
+        </is>
       </c>
       <c r="C204" s="3">
         <v>565362589</v>
@@ -38704,8 +38956,10 @@
       <c r="A206" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B206" s="2" t="s">
-        <v>1246</v>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Removed dx M5416, and resubmitted</t>
+        </is>
       </c>
       <c r="C206" s="3">
         <v>561859042</v>
@@ -39170,8 +39424,10 @@
       <c r="A209" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B209" s="2" t="s">
-        <v>1247</v>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed referring provider, and resubmitted - Rejected for invalid EDI. reasons 1. invalid id dataelement text (2), see entity type qualifier at position 2, nmi, nm1dn2insurancexx1356950653</t>
+        </is>
       </c>
       <c r="C209" s="3">
         <v>572208778</v>
@@ -39328,8 +39584,10 @@
       <c r="A210" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B210" s="2" t="s">
-        <v>1248</v>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed recon - PIQ-91152640</t>
+        </is>
       </c>
       <c r="C210" s="3">
         <v>563854100</v>
@@ -39640,8 +39898,10 @@
       <c r="A212" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B212" s="2" t="s">
-        <v>1250</v>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aetna termed 03/31/2026</t>
+        </is>
       </c>
       <c r="C212" s="3">
         <v>560450629</v>
@@ -39794,8 +40054,10 @@
       <c r="A213" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B213" s="2" t="s">
-        <v>1251</v>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - OP (possible)</t>
+        </is>
       </c>
       <c r="C213" s="3">
         <v>563716478</v>
@@ -40256,8 +40518,10 @@
       <c r="A216" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B216" s="2" t="s">
-        <v>1254</v>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uploaded MR on portal - by Jess</t>
+        </is>
       </c>
       <c r="C216" s="3">
         <v>565098609</v>
@@ -40584,8 +40848,10 @@
       <c r="A218" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B218" s="2" t="s">
-        <v>1226</v>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Waiting on secondary payment</t>
+        </is>
       </c>
       <c r="C218" s="3">
         <v>564070165</v>
@@ -40746,8 +41012,10 @@
       <c r="A219" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B219" s="2" t="s">
-        <v>1255</v>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uploaded MR - by Jess</t>
+        </is>
       </c>
       <c r="C219" s="3">
         <v>564121445</v>
@@ -40900,8 +41168,10 @@
       <c r="A220" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B220" s="2" t="s">
-        <v>1256</v>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added auth, and resubmitted - by Tina</t>
+        </is>
       </c>
       <c r="C220" s="3">
         <v>572245401</v>
@@ -41054,8 +41324,10 @@
       <c r="A221" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="B221" s="2" t="s">
-        <v>1257</v>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Removed duplicate PR line, and resubmitted - Rejected: duplicate line-level COB adjustment reason code (PR) not allowed within the same service line (1) adjustment group for insurance sequence (1). X12 Info- 2430-CAS</t>
+        </is>
       </c>
       <c r="C221" s="3">
         <v>561704073</v>
@@ -41210,8 +41482,10 @@
       <c r="A222" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="B222" s="2" t="s">
-        <v>1258</v>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed referring provider, added ordering provider, and resubmitted - Referring provider first and last name invalid or missing</t>
+        </is>
       </c>
       <c r="C222" s="3">
         <v>573841574</v>
@@ -41520,8 +41794,10 @@
       <c r="A224" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B224" s="2" t="s">
-        <v>1260</v>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Added COB info, and sent claim to print</t>
+        </is>
       </c>
       <c r="C224" s="3">
         <v>563158507</v>
@@ -41676,8 +41952,10 @@
       <c r="A225" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B225" s="2" t="s">
-        <v>1261</v>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID (payment approved) - Submitted claim on portal with dx M4802 only - Added auth # OP5257461084 - Rejected: invalid diagnosis pointer</t>
+        </is>
       </c>
       <c r="C225" s="3">
         <v>563845926</v>
@@ -41836,8 +42114,10 @@
       <c r="A226" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B226" s="2" t="s">
-        <v>1262</v>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Changed mods to NU+A2, and resubmitted - Changed mod A2 to KX, and resubmitted</t>
+        </is>
       </c>
       <c r="C226" s="3">
         <v>574469147</v>
@@ -41994,8 +42274,10 @@
       <c r="A227" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B227" s="2" t="s">
-        <v>1263</v>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denied - MUE issue</t>
+        </is>
       </c>
       <c r="C227" s="3">
         <v>561880706</v>
@@ -42152,8 +42434,10 @@
       <c r="A228" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B228" s="2" t="s">
-        <v>1264</v>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Removed dx M5116, and resubmitted - Dx M5116 and M5416 can't be billed together</t>
+        </is>
       </c>
       <c r="C228" s="3">
         <v>561866854</v>
@@ -42776,8 +43060,10 @@
       <c r="A232" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B232" s="2" t="s">
-        <v>1267</v>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted to BCBS (primary on DOS)</t>
+        </is>
       </c>
       <c r="C232" s="3">
         <v>574466702</v>
@@ -42938,8 +43224,10 @@
       <c r="A233" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B233" s="2" t="s">
-        <v>1268</v>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Changed mods to NU+A2, and resubmitted</t>
+        </is>
       </c>
       <c r="C233" s="3">
         <v>574469266</v>
@@ -43100,8 +43388,10 @@
       <c r="A234" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B234" s="2" t="s">
-        <v>1269</v>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Waiting on secondary payment</t>
+        </is>
       </c>
       <c r="C234" s="3">
         <v>545752977</v>
@@ -43256,8 +43546,10 @@
       <c r="A235" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B235" s="2" t="s">
-        <v>1270</v>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted - Aisha confirmed Peoria is active from Jan 2026 - Claim sent back for reprocessing - Confirmation # 26119900211</t>
+        </is>
       </c>
       <c r="C235" s="3">
         <v>573887856</v>
@@ -43412,8 +43704,10 @@
       <c r="A236" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="B236" s="2" t="s">
-        <v>1271</v>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Added COB info, and resubmitted electronically - Claim not found on portal</t>
+        </is>
       </c>
       <c r="C236" s="3">
         <v>547309790</v>
@@ -43566,8 +43860,10 @@
       <c r="A237" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B237" s="2" t="s">
-        <v>1272</v>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted to Humana - Active plan in Jan</t>
+        </is>
       </c>
       <c r="C237" s="3">
         <v>574455004</v>
@@ -43720,8 +44016,10 @@
       <c r="A238" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B238" s="2" t="s">
-        <v>1273</v>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OP - Secondary - $211.63 - Secondary paid twice; refund to secondary</t>
+        </is>
       </c>
       <c r="C238" s="3">
         <v>548917446</v>
@@ -43896,8 +44194,10 @@
       <c r="A239" s="2" t="s">
         <v>1152</v>
       </c>
-      <c r="B239" s="2" t="s">
-        <v>1274</v>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Added COB info, and resubmitted - Claim not found on portal</t>
+        </is>
       </c>
       <c r="C239" s="3">
         <v>547756234</v>
@@ -44050,8 +44350,10 @@
       <c r="A240" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B240" s="2" t="s">
-        <v>1275</v>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claim sent back for reprocessing</t>
+        </is>
       </c>
       <c r="C240" s="3">
         <v>561884409</v>
@@ -44380,8 +44682,10 @@
       <c r="A242" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B242" s="2" t="s">
-        <v>1276</v>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Corrected referring provider, and resubmitted</t>
+        </is>
       </c>
       <c r="C242" s="3">
         <v>563152890</v>
@@ -44540,8 +44844,10 @@
       <c r="A243" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B243" s="2" t="s">
-        <v>1277</v>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected units from 3 to 2 on portal - Confirmation # 4726236494120 - Medicare MUE for 76937 is 2 per DOS</t>
+        </is>
       </c>
       <c r="C243" s="3">
         <v>549219539</v>
@@ -44696,8 +45002,10 @@
       <c r="A244" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B244" s="2" t="s">
-        <v>1278</v>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid</t>
+        </is>
       </c>
       <c r="C244" s="3">
         <v>553137846</v>
@@ -44852,8 +45160,10 @@
       <c r="A245" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B245" s="2" t="s">
-        <v>1276</v>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Corrected referring provider, and resubmitted</t>
+        </is>
       </c>
       <c r="C245" s="3">
         <v>563153622</v>
@@ -45004,8 +45314,10 @@
       <c r="A246" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B246" s="2" t="s">
-        <v>1279</v>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid (Medicare) - Added primary claim ID, and submitted electronically - Resubmitted to Medicare</t>
+        </is>
       </c>
       <c r="C246" s="3">
         <v>563161793</v>
@@ -45164,8 +45476,10 @@
       <c r="A247" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B247" s="2" t="s">
-        <v>1278</v>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid</t>
+        </is>
       </c>
       <c r="C247" s="3">
         <v>550531610</v>
@@ -45492,8 +45806,10 @@
       <c r="A249" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B249" s="2" t="s">
-        <v>1276</v>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Corrected referring provider, and resubmitted</t>
+        </is>
       </c>
       <c r="C249" s="3">
         <v>563152081</v>
@@ -45642,8 +45958,10 @@
       <c r="A250" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B250" s="2" t="s">
-        <v>1276</v>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Corrected referring provider, and resubmitted</t>
+        </is>
       </c>
       <c r="C250" s="3">
         <v>563152473</v>
@@ -45796,8 +46114,10 @@
       <c r="A251" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B251" s="2" t="s">
-        <v>1280</v>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Added primary claim ID, and submitted electronically</t>
+        </is>
       </c>
       <c r="C251" s="3">
         <v>550306697</v>
@@ -45946,8 +46266,10 @@
       <c r="A252" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B252" s="2" t="s">
-        <v>1281</v>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DME jurisdiction issue</t>
+        </is>
       </c>
       <c r="C252" s="3">
         <v>557715576</v>
@@ -46424,8 +46746,10 @@
       <c r="A255" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B255" s="2" t="s">
-        <v>1284</v>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claim sent back for reprocessing - Confirmation # 4726257491890 - Rendering provider McCunniff</t>
+        </is>
       </c>
       <c r="C255" s="3">
         <v>552282896</v>
@@ -46742,8 +47066,10 @@
       <c r="A257" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B257" s="2" t="s">
-        <v>1286</v>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Updated supplemental insurance info, and resubmitted</t>
+        </is>
       </c>
       <c r="C257" s="3">
         <v>570792439</v>
@@ -46898,8 +47224,10 @@
       <c r="A258" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B258" s="2" t="s">
-        <v>1287</v>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Updated dx to M5416, and resubmitted - by Felipe</t>
+        </is>
       </c>
       <c r="C258" s="3">
         <v>553223068</v>
@@ -47048,8 +47376,10 @@
       <c r="A259" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B259" s="2" t="s">
-        <v>1288</v>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claim sent back for reprocessing - Confirmation # 4726257492330 - Rendering provider McCunniff</t>
+        </is>
       </c>
       <c r="C259" s="3">
         <v>555372244</v>
@@ -47372,8 +47702,10 @@
       <c r="A261" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B261" s="2" t="s">
-        <v>1290</v>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Added COB info, and crossed over electronically</t>
+        </is>
       </c>
       <c r="C261" s="3">
         <v>553825634</v>
@@ -47522,8 +47854,10 @@
       <c r="A262" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B262" s="2" t="s">
-        <v>1291</v>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Added COB info, and resubmitted - Secondary denied for timely filing - Corrected rendering and referring provider, and resubmitted - Invalid rendering provider NPI</t>
+        </is>
       </c>
       <c r="C262" s="3">
         <v>569308800</v>
@@ -47678,8 +48012,10 @@
       <c r="A263" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B263" s="2" t="s">
-        <v>1292</v>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Medicare didn't cross over to Mercy Care - Submitted electronically</t>
+        </is>
       </c>
       <c r="C263" s="3">
         <v>554160609</v>
@@ -47830,8 +48166,10 @@
       <c r="A264" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B264" s="2" t="s">
-        <v>1290</v>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Added COB info, and crossed over electronically</t>
+        </is>
       </c>
       <c r="C264" s="3">
         <v>554186385</v>
@@ -48442,8 +48780,10 @@
       <c r="A268" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B268" s="2" t="s">
-        <v>1295</v>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed appeal on portal with MR - Confirmation # 148586224 - L1851 requires auth; none obtained</t>
+        </is>
       </c>
       <c r="C268" s="3">
         <v>555436823</v>
@@ -48754,8 +49094,10 @@
       <c r="A270" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B270" s="2" t="s">
-        <v>1297</v>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Filed auth on Zyter - Details Overview - OPFOEY0914142230 - No auth request found for 63655</t>
+        </is>
       </c>
       <c r="C270" s="3">
         <v>556661876</v>
@@ -49068,8 +49410,10 @@
       <c r="A272" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B272" s="2" t="s">
-        <v>1174</v>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid</t>
+        </is>
       </c>
       <c r="C272" s="3">
         <v>556803684</v>
@@ -49708,8 +50052,10 @@
       <c r="A276" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B276" s="2" t="s">
-        <v>1300</v>
+      <c r="B276" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Primary paid - Removed mod RT, and resubmitted - by Deanne</t>
+        </is>
       </c>
       <c r="C276" s="3">
         <v>556710044</v>
@@ -49858,8 +50204,10 @@
       <c r="A277" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B277" s="2" t="s">
-        <v>1301</v>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Corrected COB info, and resubmitted</t>
+        </is>
       </c>
       <c r="C277" s="3">
         <v>556808178</v>
@@ -50016,8 +50364,10 @@
       <c r="A278" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B278" s="2" t="s">
-        <v>1302</v>
+      <c r="B278" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBI updated on chart, and resubmitted</t>
+        </is>
       </c>
       <c r="C278" s="3">
         <v>572266830</v>
@@ -50170,8 +50520,10 @@
       <c r="A279" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B279" s="2" t="s">
-        <v>1303</v>
+      <c r="B279" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Crossed over to secondary</t>
+        </is>
       </c>
       <c r="C279" s="3">
         <v>558642115</v>
@@ -50334,8 +50686,10 @@
       <c r="A280" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B280" s="2" t="s">
-        <v>1304</v>
+      <c r="B280" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Sent on 06/08/2026 - None of the secondary claims are paid</t>
+        </is>
       </c>
       <c r="C280" s="3">
         <v>556872696</v>
@@ -50490,8 +50844,10 @@
       <c r="A281" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B281" s="2" t="s">
-        <v>1303</v>
+      <c r="B281" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Crossed over to secondary</t>
+        </is>
       </c>
       <c r="C281" s="3">
         <v>557577339</v>
@@ -51420,8 +51776,10 @@
       <c r="A287" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B287" s="2" t="s">
-        <v>1307</v>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Added rendering NPI 1518261023 to box 24J and COB info, and resubmitted</t>
+        </is>
       </c>
       <c r="C287" s="3">
         <v>557798679</v>
@@ -51580,8 +51938,10 @@
       <c r="A288" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B288" s="2" t="s">
-        <v>1308</v>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Removed mod, and resubmitted - by Deanne</t>
+        </is>
       </c>
       <c r="C288" s="3">
         <v>558809263</v>
@@ -51880,8 +52240,10 @@
       <c r="A290" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="B290" s="2" t="s">
-        <v>1310</v>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Added adjustments, and resubmitted to secondary after rejection - Resubmitted 63663 with 1 unit instead of 2 - by Tina - Denied for frequency - MBI updated on chart, and resubmitted</t>
+        </is>
       </c>
       <c r="C290" s="3">
         <v>569308141</v>
@@ -52038,8 +52400,10 @@
       <c r="A291" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B291" s="2" t="s">
-        <v>1269</v>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Waiting on secondary payment</t>
+        </is>
       </c>
       <c r="C291" s="3">
         <v>558264882</v>
@@ -52194,8 +52558,10 @@
       <c r="A292" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B292" s="2" t="s">
-        <v>1311</v>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBI updated on chart, and resubmitted - MBI End Date 04/14/2026</t>
+        </is>
       </c>
       <c r="C292" s="3">
         <v>569306039</v>
@@ -52348,8 +52714,10 @@
       <c r="A293" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B293" s="2" t="s">
-        <v>1104</v>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected referring provider, and resubmitted</t>
+        </is>
       </c>
       <c r="C293" s="3">
         <v>569482322</v>
@@ -52510,8 +52878,10 @@
       <c r="A294" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B294" s="2" t="s">
-        <v>1312</v>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Pending posting</t>
+        </is>
       </c>
       <c r="C294" s="3">
         <v>559009959</v>
@@ -52666,8 +53036,10 @@
       <c r="A295" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B295" s="2" t="s">
-        <v>1313</v>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - MBI updated on chart, and resubmitted - MBI End Date 04/14/2026</t>
+        </is>
       </c>
       <c r="C295" s="3">
         <v>558588714</v>
@@ -52816,8 +53188,10 @@
       <c r="A296" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B296" s="2" t="s">
-        <v>1314</v>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBI updated on chart, and resubmitted - MBI End Date 04/14/2026</t>
+        </is>
       </c>
       <c r="C296" s="3">
         <v>569307969</v>
@@ -52976,8 +53350,10 @@
       <c r="A297" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B297" s="2" t="s">
-        <v>1269</v>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Waiting on secondary payment</t>
+        </is>
       </c>
       <c r="C297" s="3">
         <v>559008757</v>
@@ -53134,8 +53510,10 @@
       <c r="A298" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B298" s="2" t="s">
-        <v>1315</v>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - MBI updated on chart (typo corrected), and resubmitted</t>
+        </is>
       </c>
       <c r="C298" s="3">
         <v>561727580</v>
@@ -53304,8 +53682,10 @@
       <c r="A299" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B299" s="2" t="s">
-        <v>1316</v>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed appeal for 63685 - Confirmation # 2686931212 - TAT 60 days - Filed auth on Zyter - No auth found</t>
+        </is>
       </c>
       <c r="C299" s="3">
         <v>559152944</v>
@@ -53456,8 +53836,10 @@
       <c r="A300" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B300" s="2" t="s">
-        <v>1317</v>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Corrected service line 1 on portal: billed 93970 instead of 93923, and reopened claim - Confirmation # 4726237493100 - 93923 was billed on 2 separate lines and 93970 was missed</t>
+        </is>
       </c>
       <c r="C300" s="3">
         <v>560069379</v>
@@ -53604,8 +53986,10 @@
       <c r="A301" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B301" s="2" t="s">
-        <v>1269</v>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Waiting on secondary payment</t>
+        </is>
       </c>
       <c r="C301" s="3">
         <v>559107561</v>
@@ -53760,8 +54144,10 @@
       <c r="A302" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B302" s="2" t="s">
-        <v>1318</v>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added mod 79 on portal, and reopened claim - Confirmation # 4726237491810</t>
+        </is>
       </c>
       <c r="C302" s="3">
         <v>559435670</v>
@@ -53910,8 +54296,10 @@
       <c r="A303" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B303" s="2" t="s">
-        <v>1319</v>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed - Requested void of claim 569311834 per Medicare recoup - Home Health Scottsdale is the delegated DME vendor on DOS</t>
+        </is>
       </c>
       <c r="C303" s="3">
         <v>559783560</v>
@@ -54068,8 +54456,10 @@
       <c r="A304" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B304" s="2" t="s">
-        <v>1269</v>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Waiting on secondary payment</t>
+        </is>
       </c>
       <c r="C304" s="3">
         <v>559368713</v>
@@ -54554,8 +54944,10 @@
       <c r="A307" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B307" s="2" t="s">
-        <v>1320</v>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Corrected referring provider, and resubmitted</t>
+        </is>
       </c>
       <c r="C307" s="3">
         <v>560703801</v>
@@ -54710,8 +55102,10 @@
       <c r="A308" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B308" s="2" t="s">
-        <v>1321</v>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Corrected referring and ordering providers, and resubmitted</t>
+        </is>
       </c>
       <c r="C308" s="3">
         <v>560707683</v>
@@ -54858,8 +55252,10 @@
       <c r="A309" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B309" s="2" t="s">
-        <v>1322</v>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID</t>
+        </is>
       </c>
       <c r="C309" s="3">
         <v>561853521</v>
@@ -55010,8 +55406,10 @@
       <c r="A310" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B310" s="2" t="s">
-        <v>1312</v>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Pending posting</t>
+        </is>
       </c>
       <c r="C310" s="3">
         <v>561856360</v>
@@ -55166,8 +55564,10 @@
       <c r="A311" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B311" s="2" t="s">
-        <v>1269</v>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - Waiting on secondary payment</t>
+        </is>
       </c>
       <c r="C311" s="3">
         <v>560682170</v>
@@ -55320,8 +55720,10 @@
       <c r="A312" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B312" s="2" t="s">
-        <v>1323</v>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added dx M25562 (only knee dx on order encounter notes), and resubmitted</t>
+        </is>
       </c>
       <c r="C312" s="3">
         <v>569389326</v>
@@ -55482,8 +55884,10 @@
       <c r="A313" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B313" s="2" t="s">
-        <v>1324</v>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Added Medicare ICN, and crossed over electronically</t>
+        </is>
       </c>
       <c r="C313" s="3">
         <v>560691343</v>
@@ -55808,8 +56212,10 @@
       <c r="A315" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B315" s="2" t="s">
-        <v>1325</v>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBI updated on chart, and resubmitted - by QRobertson30</t>
+        </is>
       </c>
       <c r="C315" s="3">
         <v>574432540</v>
@@ -56120,8 +56526,10 @@
       <c r="A317" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B317" s="2" t="s">
-        <v>1327</v>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Pending posting</t>
+        </is>
       </c>
       <c r="C317" s="3">
         <v>572497474</v>
@@ -56592,8 +57000,10 @@
       <c r="A320" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B320" s="2" t="s">
-        <v>1328</v>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Resubmitted with Medicare COB claim info - Secondary payment appears to have been recouped due to a duplicate error</t>
+        </is>
       </c>
       <c r="C320" s="3">
         <v>562140958</v>
@@ -58136,8 +58546,10 @@
       <c r="A330" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B330" s="2" t="s">
-        <v>1332</v>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crossover status unclear - Only a rejection on file</t>
+        </is>
       </c>
       <c r="C330" s="3">
         <v>564112414</v>
@@ -58606,8 +59018,10 @@
       <c r="A333" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B333" s="2" t="s">
-        <v>1334</v>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed appeal for 75774 - Confirmation # 2718022455 - TAT 60 days</t>
+        </is>
       </c>
       <c r="C333" s="3">
         <v>566102944</v>
@@ -58915,8 +59329,10 @@
       <c r="A335" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B335" s="2" t="s">
-        <v>1335</v>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed auth appeal by mail (PO Box 64, Huntingdon Valley, PA 19006) - Auth # 20260114-002504 denied</t>
+        </is>
       </c>
       <c r="C335" s="3">
         <v>552275426</v>
@@ -59057,8 +59473,10 @@
       <c r="A336" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B336" s="2" t="s">
-        <v>1336</v>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Checking tax code on UMR records - Waiting on email response</t>
+        </is>
       </c>
       <c r="C336" s="3">
         <v>555069563</v>
@@ -59368,8 +59786,10 @@
       <c r="A338" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B338" s="2" t="s">
-        <v>1337</v>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Called payer - Rep Keran - Call ref # REQ0679770 - Claim escalated - TAT 30 days</t>
+        </is>
       </c>
       <c r="C338" s="3">
         <v>553079628</v>
@@ -59505,8 +59925,10 @@
       <c r="A339" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B339" s="2" t="s">
-        <v>1338</v>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Called payer - Rep Keran - Call ref # REQ0679770 - Charges issue under review on claim 553079628</t>
+        </is>
       </c>
       <c r="C339" s="3">
         <v>559748258</v>
@@ -59640,8 +60062,10 @@
       <c r="A340" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B340" s="2" t="s">
-        <v>1338</v>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Called payer - Rep Keran - Call ref # REQ0679770 - Charges issue under review on claim 553079628</t>
+        </is>
       </c>
       <c r="C340" s="3">
         <v>559795824</v>
@@ -59777,8 +60201,10 @@
       <c r="A341" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="B341" s="2" t="s">
-        <v>1339</v>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network) - Call ref # 0800645 - Rejected: Member not found (X12 2010BA-NM1)</t>
+        </is>
       </c>
       <c r="C341" s="3">
         <v>569036930</v>
@@ -59931,8 +60357,10 @@
       <c r="A342" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="B342" s="2" t="s">
-        <v>1340</v>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network) - Call ref # 0800645</t>
+        </is>
       </c>
       <c r="C342" s="3">
         <v>569036426</v>
@@ -60085,8 +60513,10 @@
       <c r="A343" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="B343" s="2" t="s">
-        <v>1341</v>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network) - Call ref # 0800645 - Rejected: Member not found (X12 2010BA-NM1)</t>
+        </is>
       </c>
       <c r="C343" s="3">
         <v>569035837</v>
@@ -60241,8 +60671,10 @@
       <c r="A344" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="B344" s="2" t="s">
-        <v>1340</v>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network) - Call ref # 0800645</t>
+        </is>
       </c>
       <c r="C344" s="3">
         <v>569034695</v>
@@ -60395,8 +60827,10 @@
       <c r="A345" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="B345" s="2" t="s">
-        <v>1341</v>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network) - Call ref # 0800645 - Rejected: Member not found (X12 2010BA-NM1)</t>
+        </is>
       </c>
       <c r="C345" s="3">
         <v>570895731</v>
@@ -60549,8 +60983,10 @@
       <c r="A346" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B346" s="2" t="s">
-        <v>1342</v>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Adjusted allowed amount per secondary EOB</t>
+        </is>
       </c>
       <c r="C346" s="3">
         <v>553577987</v>
@@ -60686,8 +61122,10 @@
       <c r="A347" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B347" s="2" t="s">
-        <v>1343</v>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uploaded MR (Message Center) - Payer: no MR received - Uploaded MR on PCH portal - AA0019803260980101003 - MR was requested</t>
+        </is>
       </c>
       <c r="C347" s="3">
         <v>548926996</v>
@@ -60989,8 +61427,10 @@
       <c r="A349" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B349" s="2" t="s">
-        <v>1344</v>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted with MR - by Tina - Uploaded MR on portal</t>
+        </is>
       </c>
       <c r="C349" s="3">
         <v>571716115</v>
@@ -61124,8 +61564,10 @@
       <c r="A350" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B350" s="2" t="s">
-        <v>1345</v>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Requested EOB access with Imperial</t>
+        </is>
       </c>
       <c r="C350" s="3">
         <v>556696226</v>
@@ -61819,8 +62261,10 @@
       <c r="A355" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B355" s="2" t="s">
-        <v>1346</v>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uploaded MR on portal - Case ID# 18150</t>
+        </is>
       </c>
       <c r="C355" s="3">
         <v>557575573</v>
@@ -62820,8 +63264,10 @@
       <c r="A362" s="2" t="s">
         <v>1089</v>
       </c>
-      <c r="B362" s="2" t="s">
-        <v>1348</v>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denied - Payer says they are secondary</t>
+        </is>
       </c>
       <c r="C362" s="3">
         <v>561219063</v>
@@ -62957,8 +63403,10 @@
       <c r="A363" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B363" s="2" t="s">
-        <v>1349</v>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep Arvin-CFR replied: MR under review - Document review # 208075035 - TAT 30 days - Uploaded MR (Message Center)</t>
+        </is>
       </c>
       <c r="C363" s="3">
         <v>563009396</v>
@@ -63379,8 +63827,10 @@
       <c r="A366" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B366" s="2" t="s">
-        <v>1350</v>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uploaded MR on portal - Case ID# 17527</t>
+        </is>
       </c>
       <c r="C366" s="3">
         <v>569719928</v>
@@ -63519,8 +63969,10 @@
       <c r="A367" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B367" s="2" t="s">
-        <v>1351</v>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rep Vin M: MR under review - Document handle # 208203095 - Open inquiry on portal Message Center</t>
+        </is>
       </c>
       <c r="C367" s="3">
         <v>562862986</v>
@@ -63661,8 +64113,10 @@
       <c r="A368" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B368" s="2" t="s">
-        <v>1352</v>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network) - Call ref # 0800645</t>
+        </is>
       </c>
       <c r="C368" s="3">
         <v>562903580</v>
@@ -64078,8 +64532,10 @@
       <c r="A371" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="B371" s="2" t="s">
-        <v>1353</v>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted for printing - Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network) - Call ref # 0800645</t>
+        </is>
       </c>
       <c r="C371" s="3">
         <v>563421228</v>
@@ -64213,8 +64669,10 @@
       <c r="A372" s="2" t="s">
         <v>1093</v>
       </c>
-      <c r="B372" s="2" t="s">
-        <v>1354</v>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Member ID updated on chart, and resubmitted - Rejected: Member not found on payer member table. X12 Info- 2010BA-NM109A3-21. Claim rejected as unprocessable: missing or invalid information - member not found</t>
+        </is>
       </c>
       <c r="C372" s="3">
         <v>563470580</v>
@@ -64348,8 +64806,10 @@
       <c r="A373" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B373" s="2" t="s">
-        <v>1355</v>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Pending posting</t>
+        </is>
       </c>
       <c r="C373" s="3">
         <v>564560469</v>
@@ -64489,8 +64949,10 @@
       <c r="A374" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B374" s="2" t="s">
-        <v>1356</v>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - Humana considers GAE experimental or not medically necessary for chronic pain - Humana Medicare Advantage Medical Coverage Policy: Injections for Chronic Pain Conditions - Uploaded MR - by DMinker30A</t>
+        </is>
       </c>
       <c r="C374" s="3">
         <v>548877808</v>
@@ -64651,8 +65113,10 @@
       <c r="A375" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B375" s="2" t="s">
-        <v>1356</v>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - Humana considers GAE experimental or not medically necessary for chronic pain - Humana Medicare Advantage Medical Coverage Policy: Injections for Chronic Pain Conditions - Uploaded MR - by DMinker30A</t>
+        </is>
       </c>
       <c r="C375" s="3">
         <v>554116779</v>
@@ -64813,8 +65277,10 @@
       <c r="A376" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B376" s="2" t="s">
-        <v>1357</v>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humana denied for timely filing - Resubmitted to Humana - Active only in Jan 2026 - Claim not found on portal - Plan not active on DOS</t>
+        </is>
       </c>
       <c r="C376" s="3">
         <v>557356991</v>
@@ -65119,8 +65585,10 @@
       <c r="A378" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B378" s="2" t="s">
-        <v>1359</v>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - Called payer - Rep Heather - Case # 12323141 - Provider wasn't participating with this plan until 04/01/2026 - Dr. Mayuran is INN for commercial lines but OON for Medicare</t>
+        </is>
       </c>
       <c r="C378" s="3">
         <v>548591390</v>
@@ -65575,8 +66043,10 @@
       <c r="A381" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B381" s="2" t="s">
-        <v>1356</v>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - Humana considers GAE experimental or not medically necessary for chronic pain - Humana Medicare Advantage Medical Coverage Policy: Injections for Chronic Pain Conditions - Uploaded MR - by DMinker30A</t>
+        </is>
       </c>
       <c r="C381" s="3">
         <v>552170540</v>
@@ -65737,8 +66207,10 @@
       <c r="A382" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B382" s="2" t="s">
-        <v>1360</v>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - GAE (37242) experimental per Aetna policy 0856 (Embolization: Selected Procedures)</t>
+        </is>
       </c>
       <c r="C382" s="3">
         <v>555373347</v>
@@ -65897,8 +66369,10 @@
       <c r="A383" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B383" s="2" t="s">
-        <v>1361</v>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provider Tax ID/NPI combination not on file with BCBS AZ</t>
+        </is>
       </c>
       <c r="C383" s="3">
         <v>563274947</v>
@@ -66051,8 +66525,10 @@
       <c r="A384" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B384" s="2" t="s">
-        <v>1362</v>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - Filed recon - Request ID TT2646380 - Auth 19816932 denied</t>
+        </is>
       </c>
       <c r="C384" s="3">
         <v>567785138</v>
@@ -66871,8 +67347,10 @@
       <c r="A389" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B389" s="2" t="s">
-        <v>1363</v>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - 37242-53 not supported: embolization discontinued, procedure stopped at arterial access - Resubmitted with 37242 - by QNavarro30</t>
+        </is>
       </c>
       <c r="C389" s="3">
         <v>552345092</v>
@@ -68125,8 +68603,10 @@
       <c r="A397" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B397" s="2" t="s">
-        <v>1366</v>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Shifted to PT - Plan termed 04/30/2026</t>
+        </is>
       </c>
       <c r="C397" s="3">
         <v>563651212</v>
@@ -68275,8 +68755,10 @@
       <c r="A398" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B398" s="2" t="s">
-        <v>1367</v>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed for $400.00 - Bundled with L0637 claim on DOS 12/04/2023 - Supplier SonoSpine Arizona LLC - Member ID updated on chart, and resubmitted - by Bri</t>
+        </is>
       </c>
       <c r="C398" s="3">
         <v>565309736</v>
@@ -68743,8 +69225,10 @@
       <c r="A401" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B401" s="2" t="s">
-        <v>1368</v>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - Dr. Krause OON - Approved by Optum Medicare Advantage on 04/08/2026</t>
+        </is>
       </c>
       <c r="C401" s="3">
         <v>555728365</v>
@@ -68895,8 +69379,10 @@
       <c r="A402" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B402" s="2" t="s">
-        <v>1369</v>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed mod 79, added mod 24, and resubmitted - Added mod 79, and resubmitted</t>
+        </is>
       </c>
       <c r="C402" s="3">
         <v>563362999</v>
@@ -69047,8 +69533,10 @@
       <c r="A403" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B403" s="2" t="s">
-        <v>1370</v>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - by Amanda</t>
+        </is>
       </c>
       <c r="C403" s="3">
         <v>552871981</v>
@@ -69201,8 +69689,10 @@
       <c r="A404" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B404" s="2" t="s">
-        <v>1371</v>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected claim back to 99214 - Posted adjustments per payment</t>
+        </is>
       </c>
       <c r="C404" s="3">
         <v>555169750</v>
@@ -69353,8 +69843,10 @@
       <c r="A405" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B405" s="2" t="s">
-        <v>1372</v>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Payer approved correction - Corrected dx order (I83811 as primary), and resubmitted</t>
+        </is>
       </c>
       <c r="C405" s="3">
         <v>569508762</v>
@@ -69505,8 +69997,10 @@
       <c r="A406" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B406" s="2" t="s">
-        <v>1373</v>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ChampVA doesn't cover BH</t>
+        </is>
       </c>
       <c r="C406" s="3">
         <v>554246495</v>
@@ -69655,8 +70149,10 @@
       <c r="A407" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B407" s="2" t="s">
-        <v>1374</v>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - Removed dx M5416, and resubmitted on portal - Dx M5116 and M5416 can't be reported together - Claim downloaded</t>
+        </is>
       </c>
       <c r="C407" s="3">
         <v>556735438</v>
@@ -69809,8 +70305,10 @@
       <c r="A408" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B408" s="2" t="s">
-        <v>1375</v>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - No auth on file (required for 63047)</t>
+        </is>
       </c>
       <c r="C408" s="3">
         <v>565388227</v>
@@ -70259,8 +70757,10 @@
       <c r="A411" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B411" s="2" t="s">
-        <v>1377</v>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - No auth on file - Collagen dressings</t>
+        </is>
       </c>
       <c r="C411" s="3">
         <v>556802417</v>
@@ -70411,8 +70911,10 @@
       <c r="A412" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B412" s="2" t="s">
-        <v>1377</v>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - No auth on file - Collagen dressings</t>
+        </is>
       </c>
       <c r="C412" s="3">
         <v>556804689</v>
@@ -70563,8 +71065,10 @@
       <c r="A413" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B413" s="2" t="s">
-        <v>1377</v>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - No auth on file - Collagen dressings</t>
+        </is>
       </c>
       <c r="C413" s="3">
         <v>556801421</v>
@@ -70715,8 +71219,10 @@
       <c r="A414" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B414" s="2" t="s">
-        <v>1378</v>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - Auth only included 63045</t>
+        </is>
       </c>
       <c r="C414" s="3">
         <v>558964326</v>
@@ -70865,8 +71371,10 @@
       <c r="A415" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B415" s="2" t="s">
-        <v>1379</v>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ChampVA doesn't cover BH</t>
+        </is>
       </c>
       <c r="C415" s="3">
         <v>557054917</v>
@@ -71015,8 +71523,10 @@
       <c r="A416" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B416" s="2" t="s">
-        <v>1380</v>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed - No coverage - Policy MP.009.35</t>
+        </is>
       </c>
       <c r="C416" s="3">
         <v>558609820</v>
@@ -71167,8 +71677,10 @@
       <c r="A417" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B417" s="2" t="s">
-        <v>1380</v>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed - No coverage - Policy MP.009.35</t>
+        </is>
       </c>
       <c r="C417" s="3">
         <v>557507395</v>
@@ -71621,8 +72133,10 @@
       <c r="A420" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B420" s="2" t="s">
-        <v>1381</v>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed - PCP is the delegated DME vendor</t>
+        </is>
       </c>
       <c r="C420" s="3">
         <v>559761030</v>
@@ -71927,8 +72441,10 @@
       <c r="A422" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B422" s="2" t="s">
-        <v>1383</v>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed - No auth on file</t>
+        </is>
       </c>
       <c r="C422" s="3">
         <v>559775347</v>
@@ -72237,8 +72753,10 @@
       <c r="A424" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B424" s="2" t="s">
-        <v>1385</v>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - Adjusted insurance balance - Provider OON - Audit # WY03MQKV - Provider inquiry</t>
+        </is>
       </c>
       <c r="C424" s="3">
         <v>559340053</v>
@@ -72391,8 +72909,10 @@
       <c r="A425" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B425" s="2" t="s">
-        <v>1386</v>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed line 93923 (bundled), and resubmitted - 93923 billed on claim 568263929</t>
+        </is>
       </c>
       <c r="C425" s="3">
         <v>568262814</v>
@@ -72549,8 +73069,10 @@
       <c r="A426" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B426" s="2" t="s">
-        <v>1387</v>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - 93923 bundled with 93925 and 93970 - 93923 billed on claim 568254615</t>
+        </is>
       </c>
       <c r="C426" s="3">
         <v>568254615</v>
@@ -72701,8 +73223,10 @@
       <c r="A427" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B427" s="2" t="s">
-        <v>1388</v>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted to Devoted - by Bri</t>
+        </is>
       </c>
       <c r="C427" s="3">
         <v>565931559</v>
@@ -72851,8 +73375,10 @@
       <c r="A428" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B428" s="2" t="s">
-        <v>1389</v>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - Auth only included 63650 (63685 adjusted)</t>
+        </is>
       </c>
       <c r="C428" s="3">
         <v>559340087</v>
@@ -73003,8 +73529,10 @@
       <c r="A429" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B429" s="2" t="s">
-        <v>1390</v>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed (charges per ABN)</t>
+        </is>
       </c>
       <c r="C429" s="3">
         <v>561237046</v>
@@ -73155,8 +73683,10 @@
       <c r="A430" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B430" s="2" t="s">
-        <v>1391</v>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - Ordering provider Dr. Krause notified of the dx issue</t>
+        </is>
       </c>
       <c r="C430" s="3">
         <v>560709048</v>
@@ -73309,8 +73839,10 @@
       <c r="A431" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B431" s="2" t="s">
-        <v>1392</v>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - No auth on file</t>
+        </is>
       </c>
       <c r="C431" s="3">
         <v>561851402</v>
@@ -73461,8 +73993,10 @@
       <c r="A432" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B432" s="2" t="s">
-        <v>1393</v>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Member ID updated on chart, and resubmitted - by Jess</t>
+        </is>
       </c>
       <c r="C432" s="3">
         <v>565698268</v>
@@ -73611,8 +74145,10 @@
       <c r="A433" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B433" s="2" t="s">
-        <v>1394</v>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed - No coverage</t>
+        </is>
       </c>
       <c r="C433" s="3">
         <v>561860576</v>
@@ -73765,8 +74301,10 @@
       <c r="A434" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B434" s="2" t="s">
-        <v>1395</v>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Jess asked our team to post payment</t>
+        </is>
       </c>
       <c r="C434" s="3">
         <v>560711027</v>
@@ -73917,8 +74455,10 @@
       <c r="A435" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B435" s="2" t="s">
-        <v>1396</v>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - A-codes not included in auth/referral</t>
+        </is>
       </c>
       <c r="C435" s="3">
         <v>558742342</v>
@@ -74221,8 +74761,10 @@
       <c r="A437" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B437" s="2" t="s">
-        <v>1398</v>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - No auth on file</t>
+        </is>
       </c>
       <c r="C437" s="3">
         <v>563985783</v>
@@ -74373,8 +74915,10 @@
       <c r="A438" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B438" s="2" t="s">
-        <v>1399</v>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - A-codes not covered under BCBS M2K plan</t>
+        </is>
       </c>
       <c r="C438" s="3">
         <v>562140119</v>
@@ -74525,8 +75069,10 @@
       <c r="A439" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B439" s="2" t="s">
-        <v>1400</v>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed - No auth on file</t>
+        </is>
       </c>
       <c r="C439" s="3">
         <v>559770046</v>
@@ -74668,8 +75214,10 @@
       <c r="A440" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B440" s="2" t="s">
-        <v>1401</v>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - GAE (37242) experimental per Aetna for knee pain</t>
+        </is>
       </c>
       <c r="C440" s="3">
         <v>561650229</v>
@@ -75130,8 +75678,10 @@
       <c r="A443" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B443" s="2" t="s">
-        <v>1403</v>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Primary paid - VA doesn't cover BH</t>
+        </is>
       </c>
       <c r="C443" s="3">
         <v>561646907</v>
@@ -75280,8 +75830,10 @@
       <c r="A444" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B444" s="2" t="s">
-        <v>1404</v>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted to Optum - Denied as misrouted (first submitted to SCAN Health Plan)</t>
+        </is>
       </c>
       <c r="C444" s="3">
         <v>571160597</v>
@@ -75588,8 +76140,10 @@
       <c r="A446" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B446" s="2" t="s">
-        <v>1148</v>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Updated insured's info, and resubmitted</t>
+        </is>
       </c>
       <c r="C446" s="3">
         <v>570992620</v>
@@ -75746,8 +76300,10 @@
       <c r="A447" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B447" s="2" t="s">
-        <v>1406</v>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT per EOB</t>
+        </is>
       </c>
       <c r="C447" s="3">
         <v>559655054</v>
@@ -75900,8 +76456,10 @@
       <c r="A448" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B448" s="2" t="s">
-        <v>1407</v>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - Should have been billed to Optum; past the 90-day filing limit</t>
+        </is>
       </c>
       <c r="C448" s="3">
         <v>555140726</v>
@@ -76050,8 +76608,10 @@
       <c r="A449" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B449" s="2" t="s">
-        <v>1408</v>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed - A-codes not covered</t>
+        </is>
       </c>
       <c r="C449" s="3">
         <v>562729752</v>
@@ -76200,8 +76760,10 @@
       <c r="A450" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B450" s="2" t="s">
-        <v>1409</v>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Resubmitted to Optum - First submitted to SCAN Health Plan and denied</t>
+        </is>
       </c>
       <c r="C450" s="3">
         <v>562803163</v>
@@ -76352,8 +76914,10 @@
       <c r="A451" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B451" s="2" t="s">
-        <v>1410</v>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed dx I872, and resubmitted</t>
+        </is>
       </c>
       <c r="C451" s="3">
         <v>570990107</v>
@@ -76502,8 +77066,10 @@
       <c r="A452" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B452" s="2" t="s">
-        <v>1411</v>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Updated insured's info, and resubmitted</t>
+        </is>
       </c>
       <c r="C452" s="3">
         <v>571030818</v>
@@ -76652,8 +77218,10 @@
       <c r="A453" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B453" s="2" t="s">
-        <v>1412</v>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed - No coverage - Policy MP.009.35</t>
+        </is>
       </c>
       <c r="C453" s="3">
         <v>563159449</v>
@@ -76806,8 +77374,10 @@
       <c r="A454" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B454" s="2" t="s">
-        <v>1413</v>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - No auth on file</t>
+        </is>
       </c>
       <c r="C454" s="3">
         <v>563166125</v>
@@ -76958,8 +77528,10 @@
       <c r="A455" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B455" s="2" t="s">
-        <v>1414</v>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - A-codes not covered under BCBS M2K plan</t>
+        </is>
       </c>
       <c r="C455" s="3">
         <v>563202959</v>
@@ -77108,8 +77680,10 @@
       <c r="A456" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B456" s="2" t="s">
-        <v>1415</v>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - Emailed provider - The 3-year clock follows the provider relationship - Dr. Wilson doesn't want to change the CPT code</t>
+        </is>
       </c>
       <c r="C456" s="3">
         <v>563023433</v>
@@ -77258,8 +77832,10 @@
       <c r="A457" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B457" s="2" t="s">
-        <v>1414</v>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - A-codes not covered under BCBS M2K plan</t>
+        </is>
       </c>
       <c r="C457" s="3">
         <v>564106567</v>
@@ -77566,8 +78142,10 @@
       <c r="A459" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B459" s="2" t="s">
-        <v>1412</v>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed - No coverage - Policy MP.009.35</t>
+        </is>
       </c>
       <c r="C459" s="3">
         <v>564118055</v>
@@ -77716,8 +78294,10 @@
       <c r="A460" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B460" s="2" t="s">
-        <v>1417</v>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed - Removed referring provider, and resubmitted - Rejected: invalid EDI</t>
+        </is>
       </c>
       <c r="C460" s="3">
         <v>572251311</v>
@@ -77866,8 +78446,10 @@
       <c r="A461" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B461" s="2" t="s">
-        <v>1418</v>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - VA doesn't cover BH</t>
+        </is>
       </c>
       <c r="C461" s="3">
         <v>561204793</v>
@@ -78016,8 +78598,10 @@
       <c r="A462" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B462" s="2" t="s">
-        <v>1419</v>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - GAE (37242) experimental per Aetna policy 0856 (Embolization: Selected Procedures) - If 37242 doesn't pay, neither does 36245 - 99153 not covered due to POS</t>
+        </is>
       </c>
       <c r="C462" s="3">
         <v>565101339</v>
@@ -78186,8 +78770,10 @@
       <c r="A463" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B463" s="2" t="s">
-        <v>1419</v>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - GAE (37242) experimental per Aetna policy 0856 (Embolization: Selected Procedures) - If 37242 doesn't pay, neither does 36245 - 99153 not covered due to POS</t>
+        </is>
       </c>
       <c r="C463" s="3">
         <v>565104933</v>
@@ -78504,8 +79090,10 @@
       <c r="A465" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B465" s="2" t="s">
-        <v>1420</v>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - 75710, 75774, 36245</t>
+        </is>
       </c>
       <c r="C465" s="3">
         <v>558686908</v>
@@ -78816,8 +79404,10 @@
       <c r="A467" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B467" s="2" t="s">
-        <v>1419</v>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - GAE (37242) experimental per Aetna policy 0856 (Embolization: Selected Procedures) - If 37242 doesn't pay, neither does 36245 - 99153 not covered due to POS</t>
+        </is>
       </c>
       <c r="C467" s="3">
         <v>565098145</v>
@@ -78982,8 +79572,10 @@
       <c r="A468" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B468" s="2" t="s">
-        <v>1421</v>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - Auth only included 63650 - Auth # A273499577</t>
+        </is>
       </c>
       <c r="C468" s="3">
         <v>559248529</v>
@@ -79734,8 +80326,10 @@
       <c r="A473" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B473" s="2" t="s">
-        <v>1423</v>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PAID - Payment on hold</t>
+        </is>
       </c>
       <c r="C473" s="3">
         <v>553095408</v>
@@ -79888,8 +80482,10 @@
       <c r="A474" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B474" s="2" t="s">
-        <v>1424</v>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed - Same/similar: L0637 dispensed 01/16/2023 by Arizona Spine and Pain Specialists LLC</t>
+        </is>
       </c>
       <c r="C474" s="3">
         <v>550127169</v>
@@ -80194,8 +80790,10 @@
       <c r="A476" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B476" s="2" t="s">
-        <v>1426</v>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - No auth on file</t>
+        </is>
       </c>
       <c r="C476" s="3">
         <v>551735634</v>
@@ -80648,8 +81246,10 @@
       <c r="A479" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B479" s="2" t="s">
-        <v>1373</v>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ChampVA doesn't cover BH</t>
+        </is>
       </c>
       <c r="C479" s="3">
         <v>552857208</v>
@@ -80800,8 +81400,10 @@
       <c r="A480" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B480" s="2" t="s">
-        <v>1426</v>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - No auth on file</t>
+        </is>
       </c>
       <c r="C480" s="3">
         <v>553103783</v>
@@ -81104,8 +81706,10 @@
       <c r="A482" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B482" s="2" t="s">
-        <v>1428</v>
+      <c r="B482" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed - Same/similar: another L0650 dispensed in the last 5 years</t>
+        </is>
       </c>
       <c r="C482" s="3">
         <v>554941943</v>
@@ -81412,8 +82016,10 @@
       <c r="A484" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B484" s="2" t="s">
-        <v>1430</v>
+      <c r="B484" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed - Same/similar: another L0650 dispensed 04/25/2022 by SonoSpine Arizona LLC</t>
+        </is>
       </c>
       <c r="C484" s="3">
         <v>556764690</v>
@@ -81566,8 +82172,10 @@
       <c r="A485" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B485" s="2" t="s">
-        <v>1431</v>
+      <c r="B485" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - No ABN signed - Same/similar: another L0650 dispensed 04/25/2022 by SonoSpine Arizona LLC</t>
+        </is>
       </c>
       <c r="C485" s="3">
         <v>557840581</v>
@@ -81716,8 +82324,10 @@
       <c r="A486" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B486" s="2" t="s">
-        <v>1432</v>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected rendering and referring provider, and resubmitted</t>
+        </is>
       </c>
       <c r="C486" s="3">
         <v>563732700</v>
@@ -81866,8 +82476,10 @@
       <c r="A487" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B487" s="2" t="s">
-        <v>1433</v>
+      <c r="B487" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Added COB info, and crossed over electronically</t>
+        </is>
       </c>
       <c r="C487" s="3">
         <v>558645693</v>
@@ -82018,8 +82630,10 @@
       <c r="A488" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B488" s="2" t="s">
-        <v>1434</v>
+      <c r="B488" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - Adjusted balance - Plan termed 04/30/2026</t>
+        </is>
       </c>
       <c r="C488" s="3">
         <v>558777279</v>
@@ -82170,8 +82784,10 @@
       <c r="A489" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B489" s="2" t="s">
-        <v>1269</v>
+      <c r="B489" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary - PAID</t>
+        </is>
       </c>
       <c r="C489" s="3">
         <v>560072534</v>
@@ -82324,8 +82940,10 @@
       <c r="A490" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B490" s="2" t="s">
-        <v>1435</v>
+      <c r="B490" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to PT - ABN signed - No auth on file</t>
+        </is>
       </c>
       <c r="C490" s="3">
         <v>564572924</v>
@@ -82480,8 +83098,10 @@
       <c r="A491" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B491" s="2" t="s">
-        <v>1436</v>
+      <c r="B491" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - No auth on file</t>
+        </is>
       </c>
       <c r="C491" s="3">
         <v>559739970</v>
@@ -82630,8 +83250,10 @@
       <c r="A492" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B492" s="2" t="s">
-        <v>1437</v>
+      <c r="B492" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance - No auth on file</t>
+        </is>
       </c>
       <c r="C492" s="3">
         <v>559735530</v>
@@ -82784,8 +83406,10 @@
       <c r="A493" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B493" s="2" t="s">
-        <v>1438</v>
+      <c r="B493" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected ordering provider, and resubmitted</t>
+        </is>
       </c>
       <c r="C493" s="3">
         <v>561864733</v>
@@ -82940,8 +83564,10 @@
       <c r="A494" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B494" s="2" t="s">
-        <v>1439</v>
+      <c r="B494" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted on 08/05/2026 - by Bri</t>
+        </is>
       </c>
       <c r="C494" s="3">
         <v>567670697</v>

--- a/Master Updates.xlsx
+++ b/Master Updates.xlsx
@@ -6854,7 +6854,7 @@
         <v>1087</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="C2" s="3">
         <v>546185672</v>
@@ -7160,8 +7160,10 @@
       <c r="A4" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>1092</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added anatomical modifiers</t>
+        </is>
       </c>
       <c r="C4" s="3">
         <v>555920273</v>
@@ -7630,10 +7632,8 @@
       <c r="A7" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Uploaded MR on portal - Case ID# 18151</t>
-        </is>
+      <c r="B7" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C7" s="3">
         <v>568271516</v>
@@ -7776,7 +7776,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added mod 24, and resubmitted - Denied: 99493 is included in the global period of 64635 on Claim ID RC2772466500 Line ID 1, DOS 03/24/2026</t>
+          <t xml:space="preserve">Added mod 24 - Denied: 99493 is included in the global period of 64635 on Claim ID RC2772466500 Line ID 1, DOS 03/24/2026</t>
         </is>
       </c>
       <c r="C8" s="3">
@@ -8244,10 +8244,8 @@
       <c r="A11" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Uploaded MR on portal - Case ID# 18149</t>
-        </is>
+      <c r="B11" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C11" s="3">
         <v>568312031</v>
@@ -8391,7 +8389,7 @@
         <v>1091</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>1101</v>
+        <v>1090</v>
       </c>
       <c r="C12" s="3">
         <v>556730319</v>
@@ -8546,7 +8544,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrected claim, and resubmitted - by Tina - Filed recon with MR - PIQ-89945925</t>
+          <t xml:space="preserve">Corrected claim - by Tina - Filed recon with MR</t>
         </is>
       </c>
       <c r="C13" s="3">
@@ -8688,8 +8686,10 @@
       <c r="BB13" s="2" t="s">
         <v>1464</v>
       </c>
-      <c r="BC13" s="2" t="s">
-        <v>1090</v>
+      <c r="BC13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PIQ-89945925</t>
+        </is>
       </c>
       <c r="BD13" s="4" t="s">
         <v>1090</v>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resubmitted - Renee Oroc credentialing issue - Remark MA130: multiple submission/billing errors, unable to adjudicate claim as submitted</t>
+          <t xml:space="preserve">Renee Oroc credentialing issue - Remark MA130: multiple submission/billing errors, unable to adjudicate claim as submitted</t>
         </is>
       </c>
       <c r="C14" s="3">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrected referring provider, and resubmitted</t>
+          <t xml:space="preserve">Corrected referring provider</t>
         </is>
       </c>
       <c r="C15" s="3">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OP - BCBS - Refund needed</t>
+          <t xml:space="preserve">Refund needed to BCBS</t>
         </is>
       </c>
       <c r="C21" s="3">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OP - BCBS - Refund needed</t>
+          <t xml:space="preserve">Refund needed to BCBS</t>
         </is>
       </c>
       <c r="C22" s="3">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moved mod 25 from 62323 to 99204, and resubmitted</t>
+          <t xml:space="preserve">Moved mod 25 from 62323 to 99204</t>
         </is>
       </c>
       <c r="C23" s="3">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Called AZ Priority Care and BCBS - Rep MousamK - Call ref # 12696890 - Clarification requested and escalated to confirm the payer - by Tina - Resubmitted to APCP - Rep Heather: member is assigned to an affiliated network (Arizona Priority Care)</t>
+          <t xml:space="preserve">Called AZ Priority Care and BCBS - Rep MousamK - Clarification requested and escalated to confirm the payer - by Tina - Resubmitted to APCP - Rep Heather: member is assigned to an affiliated network (Arizona Priority Care)</t>
         </is>
       </c>
       <c r="C24" s="3">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Corrected adjustments, and resubmitted</t>
+          <t xml:space="preserve">Corrected adjustments</t>
         </is>
       </c>
       <c r="C25" s="3">
@@ -10625,7 +10625,7 @@
         <v>1091</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C26" s="3">
         <v>545332485</v>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OP - Void original claim 547459229</t>
+          <t xml:space="preserve">Void original claim 547459229</t>
         </is>
       </c>
       <c r="C28" s="3">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filed recon with MR - by Jess - Optum letter ref # 70293624: 99492 denied because MR shows POS 11 (office) but the claim was billed POS 10 (telehealth in patient's home), so the claim can't be verified</t>
+          <t xml:space="preserve">Filed recon with MR by Jess - Optum letter ref # 70293624: 99492 denied because MR shows POS 11 (office) but the claim was billed POS 10 (telehealth in patient's home), so the claim can't be verified</t>
         </is>
       </c>
       <c r="C29" s="3">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filed recon with MR - Recon # BOT3951067 - No waiver for 63047: Carrum A0 exclusion lists fusion, but 63047 is decompression (no fusion billed) - Asked payer to reprocess or provide the plan language for the denial</t>
+          <t xml:space="preserve">No waiver for 63047: Carrum A0 exclusion lists fusion, but 63047 is decompression (no fusion billed) - Asked payer to reprocess or provide the plan language for the denial</t>
         </is>
       </c>
       <c r="C30" s="3">
@@ -11399,7 +11399,7 @@
         <v>1114</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="C31" s="3">
         <v>545934840</v>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OP - Void original claim 547855520</t>
+          <t xml:space="preserve">Void original claim 547855520</t>
         </is>
       </c>
       <c r="C32" s="3">
@@ -11704,8 +11704,10 @@
       <c r="A33" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>1115</v>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added Date of Current Illness, claim note</t>
+        </is>
       </c>
       <c r="C33" s="3">
         <v>556348109</v>
@@ -11858,7 +11860,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professional claim, no revenue code needed - Filed recon with duplex report - Uploaded MR</t>
+          <t xml:space="preserve">Professional claim, no revenue code needed - Filed recon with duplex report</t>
         </is>
       </c>
       <c r="C34" s="3">
@@ -12014,7 +12016,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Called payer - Rep Muthamma - Call ref # 10605826 - TAT 15 days</t>
+          <t xml:space="preserve">Rep Muthamma - TAT 15 days</t>
         </is>
       </c>
       <c r="C35" s="3">
@@ -12170,7 +12172,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Resubmitted to AmeTrust</t>
+          <t xml:space="preserve">Resubmitted to AmeTrust</t>
         </is>
       </c>
       <c r="C36" s="3">
@@ -12328,7 +12330,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Handled by Deanne - Called BCBS AZ - Rep Heather: per the provider's contract the allowed amount is $0.00 (contractual adjustment = billed charges minus the non-covered/denied allowed amount, not a payable allowance) - Case # 10628911 - Rep Mage E: payer canceled the appeal, claim was forwarded to Anthem with zero price and no allowed amount - Pricing issue with local plan - Filed appeal - Request APP-COMM-6695304</t>
+          <t xml:space="preserve">Handled by Deanne - Called BCBS AZ - Rep Heather: per the provider's contract the allowed amount is $0.00 (contractual adjustment = billed charges minus the non-covered/denied allowed amount, not a payable allowance) - Rep Mage E: payer canceled the appeal, claim was forwarded to Anthem with zero price and no allowed amount - Pricing issue with local plan</t>
         </is>
       </c>
       <c r="C37" s="3">
@@ -12484,7 +12486,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Corrected charges for A6219, and resubmitted</t>
+          <t xml:space="preserve">Corrected charges for A6219</t>
         </is>
       </c>
       <c r="C38" s="3">
@@ -12644,8 +12646,10 @@
       <c r="A39" s="2" t="s">
         <v>1121</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>1122</v>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted with no changes</t>
+        </is>
       </c>
       <c r="C39" s="3">
         <v>555599776</v>
@@ -12800,7 +12804,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Changed 99493 to 99492, and resubmitted - Filed recon - Claim 26A635462200 DOS 01/27/26: 99493 denied, no prior CoCM in 6 months; prior 99493 DOS 12/16/25 paid on claim 26A070631100 under old ID 2062477 - Requested reprocess, PRA attached - Added Date of Current Illness, claim note, and resubmitted</t>
+          <t xml:space="preserve">Changed 99493 to 99492 - Claim 26A635462200 DOS 01/27/26: 99493 denied, no prior CoCM in 6 months; prior 99493 DOS 12/16/25 paid on claim 26A070631100 under old ID 2062477 - Requested reprocess, PRA attached - Added Date of Current Illness, claim note</t>
         </is>
       </c>
       <c r="C40" s="3">
@@ -13112,7 +13116,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filed recon with MR - PIQ-92451492 - 93970 denial: sent signed report showing bilateral compression/augmentation - by Jess</t>
+          <t xml:space="preserve">93970 denial: sent signed report showing bilateral compression/augmentation - by Jess</t>
         </is>
       </c>
       <c r="C42" s="3">
@@ -13270,7 +13274,7 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Called payer - Rep Briana - Call ref # 11216220 - Dr. Leathem is not contracted with member's Focus Network</t>
+          <t xml:space="preserve">Rep Briana - Dr. Leathem is not contracted with member's Focus Network</t>
         </is>
       </c>
       <c r="C43" s="3">
@@ -13426,7 +13430,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deanne reviewing - Called payer - Rep Jessie - Claim has a non-anesthesia service but payer lists the rendering provider as an anesthesiologist</t>
+          <t xml:space="preserve">Deanne reviewing - Rep Jessie - Claim has a non-anesthesia service but payer lists the rendering provider as an anesthesiologist</t>
         </is>
       </c>
       <c r="C44" s="3">
@@ -13738,7 +13742,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Resubmitted to AmeTrust</t>
+          <t xml:space="preserve">Resubmitted to AmeTrust</t>
         </is>
       </c>
       <c r="C46" s="3">
@@ -13896,7 +13900,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrected dx to G894, added auth #, and resubmitted - VA doesn't cover BH - Rejected: invalid dx - ASAP Deer Valley NPI missing - Resubmitted</t>
+          <t xml:space="preserve">Corrected dx to G894, added auth # - VA doesn't cover BH - Rejected: invalid dx - ASAP Deer Valley NPI missing</t>
         </is>
       </c>
       <c r="C47" s="3">
@@ -14050,8 +14054,10 @@
       <c r="A48" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>1115</v>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added Date of Current Illness, claim note</t>
+        </is>
       </c>
       <c r="C48" s="3">
         <v>557794433</v>
@@ -14204,7 +14210,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Provider active - Resubmitted</t>
+          <t xml:space="preserve">Provider active</t>
         </is>
       </c>
       <c r="C49" s="3">
@@ -14376,7 +14382,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auth issue - Resubmitted - by Bri - Provider Tax ID/NPI combination not on file with BCBS AZ</t>
+          <t xml:space="preserve">Auth issue - Resubmitted by Bri - Provider Tax ID/NPI combination not on file with BCBS AZ</t>
         </is>
       </c>
       <c r="C50" s="3">
@@ -14538,7 +14544,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99492 paid on DOS 01/27/2026 - Resubmitted - Waiting on claim #556349314 (DOS 01/27/2026) before reprocessing - 99493 denied: non-payable code for required reporting only - Added Date of Current Illness, claim note, and resubmitted</t>
+          <t xml:space="preserve">99492 paid on DOS 01/27/2026 - Waiting on claim #556349314 (DOS 01/27/2026) before reprocessing - 99493 denied: non-payable code for required reporting only - Added Date of Current Illness, claim note</t>
         </is>
       </c>
       <c r="C51" s="3">
@@ -14694,7 +14700,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Called payer - Rep Muthamma - Call ref # 11253575</t>
+          <t xml:space="preserve">Rep Muthamma</t>
         </is>
       </c>
       <c r="C52" s="3">
@@ -14850,7 +14856,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - No auth on file - Checking whether auth is needed on Curo portal # 19801266</t>
+          <t xml:space="preserve">Checking whether auth is needed on Curo portal # 19801266</t>
         </is>
       </c>
       <c r="C53" s="3">
@@ -15004,7 +15010,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Changed 99493 to 99492, and resubmitted</t>
+          <t xml:space="preserve">Changed 99493 to 99492</t>
         </is>
       </c>
       <c r="C54" s="3">
@@ -15156,7 +15162,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Changed 99493 to 99492, and resubmitted - Recon not available on portal because the claim was already adjusted - 99493 paid on claim 26A074466600, DOS 12/12/2025, under prior member ID 1718676 - Current claim billed with active member ID 906162197 - Added Date of Current Illness, claim note, and resubmitted</t>
+          <t xml:space="preserve">Changed 99493 to 99492 - Recon not available on portal because the claim was already adjusted - 99493 paid on claim 26A074466600, DOS 12/12/2025, under prior member ID 1718676 - Current claim billed with active member ID 906162197 - Added Date of Current Illness, claim note</t>
         </is>
       </c>
       <c r="C55" s="3">
@@ -15310,7 +15316,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Claim 568613230 was paid - Removed mod 58, and resubmitted - Added mod 58, and resubmitted</t>
+          <t xml:space="preserve">Claim 568613230 was paid - Removed mod 58 - Added mod 58</t>
         </is>
       </c>
       <c r="C56" s="3">
@@ -15463,7 +15469,7 @@
         <v>1114</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>1136</v>
+        <v>1090</v>
       </c>
       <c r="C57" s="3">
         <v>555067836</v>
@@ -15626,7 +15632,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrected dx order, and resubmitted</t>
+          <t xml:space="preserve">Corrected dx order</t>
         </is>
       </c>
       <c r="C58" s="3">
@@ -15788,7 +15794,7 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrected rendering provider to Timothy Baugher (was Jarrett Leathem), and resubmitted - by Jess</t>
+          <t xml:space="preserve">Corrected rendering provider to Timothy Baugher (was Jarrett Leathem) - by Jess</t>
         </is>
       </c>
       <c r="C59" s="3">
@@ -16104,7 +16110,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Optum had no record of 99492 (billed to UHC, not Optum) - Resubmitted with 99492</t>
+          <t xml:space="preserve">Optum had no record of 99492 (billed to UHC, not Optum) - Resubmitted with 99492</t>
         </is>
       </c>
       <c r="C61" s="3">
@@ -16256,8 +16262,10 @@
       <c r="A62" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>1141</v>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected rendering provider</t>
+        </is>
       </c>
       <c r="C62" s="3">
         <v>551874008</v>
@@ -16408,7 +16416,7 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - OP by secondary - Called payer - Rep Gloria C - Payer started the refund request and sent the claim back for reprocessing - Ticket # SF20260903906271400 - TAT 30 business days</t>
+          <t xml:space="preserve">OP by secondary - Rep Gloria C - Payer started the refund request and sent the claim back for reprocessing - TAT 30 business days</t>
         </is>
       </c>
       <c r="C63" s="3">
@@ -16564,8 +16572,10 @@
       <c r="A64" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>1143</v>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auth only included 62330</t>
+        </is>
       </c>
       <c r="C64" s="3">
         <v>551964467</v>
@@ -16714,7 +16724,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filed appeal on portal with op note - Appeal # Z264AZW09999 - Basis: 63048 is an add-on to auth'd/paid 63047, intraop findings - Medicaid auth tool shows add-on 63048 requires auth - Auth # OP4987640976 didn't include 63048</t>
+          <t xml:space="preserve">Filed appeal on portal with op note - Basis: 63048 is an add-on to auth'd/paid 63047, intraop findings - Medicaid auth tool shows add-on 63048 requires auth - Auth # OP4987640976 didn't include 63048</t>
         </is>
       </c>
       <c r="C65" s="3">
@@ -17486,7 +17496,7 @@
         <v>1091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C70" s="3">
         <v>555351211</v>
@@ -17643,7 +17653,7 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Updated insured's info, and resubmitted</t>
+          <t xml:space="preserve">Updated insured's info</t>
         </is>
       </c>
       <c r="C71" s="3">
@@ -17955,7 +17965,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrected CPT codes, added code 7, and resubmitted</t>
+          <t xml:space="preserve">Corrected CPT codes, added code 7</t>
         </is>
       </c>
       <c r="C73" s="3">
@@ -18115,8 +18125,10 @@
       <c r="A74" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>1115</v>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added Date of Current Illness, claim note</t>
+        </is>
       </c>
       <c r="C74" s="3">
         <v>570350220</v>
@@ -18429,7 +18441,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Resubmitted to Tricare for Life - Claim not found on portal (sent to Tricare West, can't locate it on Availity)</t>
+          <t xml:space="preserve">Resubmitted to Tricare for Life - Claim not found on portal (sent to Tricare West, can't locate it on Availity)</t>
         </is>
       </c>
       <c r="C76" s="3">
@@ -19065,8 +19077,10 @@
       <c r="A80" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>1156</v>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted to the same payer - Active coverage on DOS</t>
+        </is>
       </c>
       <c r="C80" s="3">
         <v>571608266</v>
@@ -19218,7 +19232,7 @@
         <v>1091</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C81" s="3">
         <v>554940052</v>
@@ -19379,7 +19393,7 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Bundled with Claim ID 26F500108500 Line ID 1, DOS 03/24/2026, CPT 64640</t>
+          <t xml:space="preserve">Bundled with Claim ID 26F500108500 Line ID 1, DOS 03/24/2026, CPT 64640</t>
         </is>
       </c>
       <c r="C82" s="3">
@@ -19533,7 +19547,7 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99492 paid - Resubmitted - Reprocess when claim 570543000 is paid</t>
+          <t xml:space="preserve">99492 paid - Reprocess when claim 570543000 is paid</t>
         </is>
       </c>
       <c r="C83" s="3">
@@ -19689,7 +19703,7 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resubmitted - by Jess</t>
+          <t xml:space="preserve">Resubmitted by Jess</t>
         </is>
       </c>
       <c r="C84" s="3">
@@ -19844,7 +19858,7 @@
         <v>1091</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C85" s="3">
         <v>556734047</v>
@@ -20003,7 +20017,7 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uploaded MR per payer request - PIQ-91107053</t>
+          <t xml:space="preserve">Uploaded MR per payer request</t>
         </is>
       </c>
       <c r="C86" s="3">
@@ -20163,7 +20177,7 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Corrected dx codes, and resubmitted</t>
+          <t xml:space="preserve">Corrected dx codes</t>
         </is>
       </c>
       <c r="C87" s="3">
@@ -20473,7 +20487,7 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - 36246 not included in auth - 36248 add-on requires payment of the primary code - 99153 can't be billed with POS 24</t>
+          <t xml:space="preserve">36246 not included in auth - 36248 add-on requires payment of the primary code - 99153 can't be billed with POS 24</t>
         </is>
       </c>
       <c r="C89" s="3">
@@ -20801,8 +20815,10 @@
       <c r="A91" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>1165</v>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added mod XS to 93970 - Anthem Commercial Reimbursement Policy Number: C-23003 - secondary subject to MPPR rules</t>
+        </is>
       </c>
       <c r="C91" s="3">
         <v>572247724</v>
@@ -20961,7 +20977,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denied for timely filing, but this was a resubmission - Resubmitted - Changed 93970 to 93971, and resubmitted</t>
+          <t xml:space="preserve">Denied for timely filing, but this was a resubmission - Changed 93970 to 93971</t>
         </is>
       </c>
       <c r="C92" s="3">
@@ -21116,7 +21132,7 @@
         <v>1091</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C93" s="3">
         <v>558638750</v>
@@ -21591,7 +21607,7 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed - Rep Mark confirmed Integra is the delegated DME vendor for this PT - Provider OON with Devoted</t>
+          <t xml:space="preserve">ABN signed - Rep Mark confirmed Integra is the delegated DME vendor for this PT - Provider OON with Devoted</t>
         </is>
       </c>
       <c r="C96" s="3">
@@ -22073,8 +22089,10 @@
       <c r="A99" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>1115</v>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added Date of Current Illness, claim note</t>
+        </is>
       </c>
       <c r="C99" s="3">
         <v>556413148</v>
@@ -22225,7 +22243,7 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uploaded MR - Removed line 20936, and resubmitted</t>
+          <t xml:space="preserve">Removed line 20936</t>
         </is>
       </c>
       <c r="C100" s="3">
@@ -22391,7 +22409,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uploaded missing MR - PIQ-85007180 - Uploaded POD - by Jess</t>
+          <t xml:space="preserve">Uploaded missing MR - Uploaded POD - by Jess</t>
         </is>
       </c>
       <c r="C101" s="3">
@@ -22707,7 +22725,7 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Submitted to BCBS (BCBS primary, Banner Aetna secondary) - Removed mod 79, added mod 24, and resubmitted - Payer edits only allow 79/78/58 on surgical/procedural codes; 99492 is an E/M - Resubmitted with mod 79 - by Jess</t>
+          <t xml:space="preserve">Submitted to BCBS (BCBS primary, Banner Aetna secondary) - Removed mod 79, added mod 24 - Payer edits only allow 79/78/58 on surgical/procedural codes; 99492 is an E/M - Resubmitted with mod 79 - by Jess</t>
         </is>
       </c>
       <c r="C103" s="3">
@@ -23019,10 +23037,8 @@
       <c r="A105" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Secondary - Primary paid</t>
-        </is>
+      <c r="B105" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C105" s="3">
         <v>553378154</v>
@@ -23329,7 +23345,7 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Added COB info, and resubmitted</t>
+          <t xml:space="preserve">Added COB info</t>
         </is>
       </c>
       <c r="C107" s="3">
@@ -23667,8 +23683,10 @@
       <c r="A109" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>1115</v>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added Date of Current Illness, claim note</t>
+        </is>
       </c>
       <c r="C109" s="3">
         <v>570349832</v>
@@ -23825,7 +23843,7 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uploaded MR per payer request - Request ID 35635409 - All CPT codes denied as not covered</t>
+          <t xml:space="preserve">Uploaded MR per payer request - All CPT codes denied as not covered</t>
         </is>
       </c>
       <c r="C110" s="3">
@@ -24303,8 +24321,10 @@
       <c r="A113" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B113" s="2" t="s">
-        <v>1180</v>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added Date of Current Illness, claim note</t>
+        </is>
       </c>
       <c r="C113" s="3">
         <v>557132196</v>
@@ -24455,7 +24475,7 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filed recon - Decision ID # D600552039 shows NAR</t>
+          <t xml:space="preserve">Decision ID # D600552039 shows NAR</t>
         </is>
       </c>
       <c r="C114" s="3">
@@ -25076,7 +25096,7 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Added SCS referral #, and resubmitted - Not expected to pay: VA doesn't cover BH and we don't have an RFS</t>
+          <t xml:space="preserve">Added SCS referral # - Not expected to pay: VA doesn't cover BH and we don't have an RFS</t>
         </is>
       </c>
       <c r="C118" s="3">
@@ -25224,8 +25244,10 @@
       <c r="A119" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B119" s="2" t="s">
-        <v>1186</v>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added code 7</t>
+        </is>
       </c>
       <c r="C119" s="3">
         <v>571603915</v>
@@ -25864,7 +25886,7 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resubmitted - Aisha reviewed Dr. Adler's status on the AHCCCS portal: active since 2012 - Rendering OON with Medicaid AHCCCS - Confirming with Bri - DOS worked: 05/01/2026</t>
+          <t xml:space="preserve">Aisha reviewed Dr. Adler's status on the AHCCCS portal: active since 2012 - Rendering OON with Medicaid AHCCCS - Confirming with Bri - DOS worked: 05/01/2026</t>
         </is>
       </c>
       <c r="C123" s="3">
@@ -26020,7 +26042,7 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Called payer - Rep Harold C - Call ref # 372182510 - Claim didn't price to the market fee schedule in effect on DOS - Claim sent back for reprocessing - TAT 30 days - ERA shows no allowed amount; payer moved the full billed charge to PT</t>
+          <t xml:space="preserve">Called payer - Rep Harold C - Claim didn't price to the market fee schedule in effect on DOS - TAT 30 days - ERA shows no allowed amount; payer moved the full billed charge to PT</t>
         </is>
       </c>
       <c r="C124" s="3">
@@ -26505,10 +26527,8 @@
       <c r="A127" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Filed dispute with MR - Dispute ID PDX7G8WCG9</t>
-        </is>
+      <c r="B127" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C127" s="3">
         <v>565099868</v>
@@ -26683,7 +26703,7 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - No auth on file - Retro auth not available - Submitted claim on portal with MR</t>
+          <t xml:space="preserve">No auth on file - Retro auth not available - Submitted claim on portal with MR</t>
         </is>
       </c>
       <c r="C128" s="3">
@@ -26991,7 +27011,7 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Corrected mod, and resubmitted</t>
+          <t xml:space="preserve">Corrected mod</t>
         </is>
       </c>
       <c r="C130" s="3">
@@ -27143,8 +27163,10 @@
       <c r="A131" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>1196</v>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added mod 58</t>
+        </is>
       </c>
       <c r="C131" s="3">
         <v>569471711</v>
@@ -27299,7 +27321,7 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resubmitted - Denied for timely filing - Removed line 80307, and resubmitted corrected claim - by Tina</t>
+          <t xml:space="preserve">Denied for timely filing - Removed line 80307, and resubmitted corrected claim - by Tina</t>
         </is>
       </c>
       <c r="C132" s="3">
@@ -27605,7 +27627,7 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Changed 93923 to 93922, and resubmitted - 93923 requires 3 levels; report shows only ankle + toe (2 levels) - Resubmitted by mail - by April - Uploaded MR - by DMinker30A</t>
+          <t xml:space="preserve">Changed 93923 to 93922 - 93923 requires 3 levels; report shows only ankle + toe (2 levels) - Resubmitted by mail - by April - Uploaded MR by DMinker30A</t>
         </is>
       </c>
       <c r="C134" s="3">
@@ -27769,7 +27791,7 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Corrected rendering provider, and resubmitted</t>
+          <t xml:space="preserve">Corrected rendering provider</t>
         </is>
       </c>
       <c r="C135" s="3">
@@ -27923,7 +27945,7 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Added active referral for DOS, and resubmitted - VA doesn't cover BH; separate RFS approval needed for BH coverage</t>
+          <t xml:space="preserve">Added active referral for DOS - VA doesn't cover BH; separate RFS approval needed for BH coverage</t>
         </is>
       </c>
       <c r="C136" s="3">
@@ -28075,8 +28097,10 @@
           <t>Denied</t>
         </is>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>1202</v>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added code 7 - COB was updated by PT as per insurance request</t>
+        </is>
       </c>
       <c r="C137" s="3">
         <v>562420138</v>
@@ -28230,7 +28254,7 @@
         <v>1091</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1203</v>
+        <v>1090</v>
       </c>
       <c r="C138" s="3">
         <v>561729597</v>
@@ -28401,7 +28425,7 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Corrected claim, and resubmitted on 08/03/2026 - by DMinker30A</t>
+          <t xml:space="preserve">Corrected claim, and resubmitted on 08/03/2026 - by DMinker30A</t>
         </is>
       </c>
       <c r="C139" s="3">
@@ -28555,7 +28579,7 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removed line 20936, and resubmitted</t>
+          <t xml:space="preserve">Removed line 20936</t>
         </is>
       </c>
       <c r="C140" s="3">
@@ -28722,7 +28746,7 @@
         <v>1091</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C141" s="3">
         <v>560081393</v>
@@ -28882,7 +28906,7 @@
         <v>1114</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1136</v>
+        <v>1090</v>
       </c>
       <c r="C142" s="3">
         <v>559331282</v>
@@ -29032,7 +29056,7 @@
         <v>1114</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1136</v>
+        <v>1090</v>
       </c>
       <c r="C143" s="3">
         <v>559334288</v>
@@ -29181,8 +29205,10 @@
       <c r="A144" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B144" s="2" t="s">
-        <v>1206</v>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted with 63030+63035 - Rejected: invalid original claim number - Corrected claim number</t>
+        </is>
       </c>
       <c r="C144" s="3">
         <v>559356030</v>
@@ -29335,7 +29361,7 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MR requested - Removed line A6219, and resubmitted</t>
+          <t xml:space="preserve">MR requested - Removed line A6219</t>
         </is>
       </c>
       <c r="C145" s="3">
@@ -29499,8 +29525,10 @@
       <c r="A146" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>1208</v>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On hold - Missing MR</t>
+        </is>
       </c>
       <c r="C146" s="3">
         <v>558887755</v>
@@ -29807,8 +29835,10 @@
       <c r="A148" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B148" s="2" t="s">
-        <v>1210</v>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed rendering, added servicing, changed from professional to DME</t>
+        </is>
       </c>
       <c r="C148" s="3">
         <v>568306831</v>
@@ -29965,7 +29995,7 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filed recon with MR and WC denied auth #910943907 - Unchecked employment box, restored dx order, and resubmitted - Rejected again - Changed employment dx to primary, added dx Y990 and claim note, and resubmitted</t>
+          <t xml:space="preserve">Filed recon with MR and WC denied auth #910943907 - Unchecked employment box, restored dx order - Rejected again - Changed employment dx to primary, added dx Y990 and claim note</t>
         </is>
       </c>
       <c r="C149" s="3">
@@ -30125,7 +30155,7 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Changed service line 1 to 99492, and resubmitted - Processed date 06/16/2026</t>
+          <t xml:space="preserve">Changed service line 1 to 99492 - Processed date 06/16/2026</t>
         </is>
       </c>
       <c r="C150" s="3">
@@ -30279,7 +30309,7 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Changed service line 1 to 99492, and resubmitted - Processed date 06/10/2026</t>
+          <t xml:space="preserve">Changed service line 1 to 99492 - Processed date 06/10/2026</t>
         </is>
       </c>
       <c r="C151" s="3">
@@ -30432,7 +30462,7 @@
         <v>1114</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1136</v>
+        <v>1090</v>
       </c>
       <c r="C152" s="3">
         <v>561246589</v>
@@ -30586,7 +30616,7 @@
         <v>1091</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C153" s="3">
         <v>560710074</v>
@@ -30742,7 +30772,7 @@
         <v>1114</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>1136</v>
+        <v>1090</v>
       </c>
       <c r="C154" s="3">
         <v>560027331</v>
@@ -31030,7 +31060,7 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Corrected dx for 93970, and resubmitted</t>
+          <t xml:space="preserve">Corrected dx for 93970</t>
         </is>
       </c>
       <c r="C156" s="3">
@@ -31182,10 +31212,8 @@
       <c r="A157" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PAID - Filed recon - Decision ID # D606429361</t>
-        </is>
+      <c r="B157" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C157" s="3">
         <v>563202144</v>
@@ -31340,7 +31368,7 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Corrected dx for 93970, removed line 93923, and resubmitted</t>
+          <t xml:space="preserve">Corrected dx for 93970, removed line 93923</t>
         </is>
       </c>
       <c r="C158" s="3">
@@ -31502,7 +31530,7 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uploaded MR - Dispute ID PDXEFY2R66 - Rep Ria U said MR was needed</t>
+          <t xml:space="preserve">Rep Ria U said MR was needed</t>
         </is>
       </c>
       <c r="C159" s="3">
@@ -31816,7 +31844,7 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">99492 paid on DOS 02/20/2026 - Resubmitted</t>
+          <t xml:space="preserve">99492 paid on DOS 02/20/2026</t>
         </is>
       </c>
       <c r="C161" s="3">
@@ -32128,7 +32156,7 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Billed 93923 separately on portal</t>
+          <t xml:space="preserve">Billed 93923 separately on portal</t>
         </is>
       </c>
       <c r="C163" s="3">
@@ -32280,7 +32308,7 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Changed POS from 11 to 24 and location to ASAP Surgery Centers North Valley, and resubmitted</t>
+          <t xml:space="preserve">Changed POS from 11 to 24 and location to ASAP Surgery Centers North Valley</t>
         </is>
       </c>
       <c r="C164" s="3">
@@ -32781,7 +32809,7 @@
         <v>1091</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C167" s="3">
         <v>562557056</v>
@@ -32942,7 +32970,7 @@
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrected dx codes for 93970 (added I83893, R600), and resubmitted</t>
+          <t xml:space="preserve">Corrected dx codes for 93970 (added I83893, R600)</t>
         </is>
       </c>
       <c r="C168" s="3">
@@ -33096,10 +33124,8 @@
       <c r="A169" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Secondary - Primary paid - Waiting on secondary payment</t>
-        </is>
+      <c r="B169" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C169" s="3">
         <v>561646092</v>
@@ -33255,7 +33281,7 @@
         <v>1091</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C170" s="3">
         <v>562559783</v>
@@ -33415,7 +33441,7 @@
         <v>1109</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C171" s="3">
         <v>563023143</v>
@@ -33726,8 +33752,10 @@
       <c r="A173" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B173" s="2" t="s">
-        <v>1227</v>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added mod XU</t>
+        </is>
       </c>
       <c r="C173" s="3">
         <v>569022508</v>
@@ -34060,7 +34088,7 @@
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removed line 20936, and resubmitted</t>
+          <t xml:space="preserve">Removed line 20936</t>
         </is>
       </c>
       <c r="C175" s="3">
@@ -34227,7 +34255,7 @@
         <v>1091</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>1101</v>
+        <v>1090</v>
       </c>
       <c r="C176" s="3">
         <v>573628784</v>
@@ -34389,7 +34417,7 @@
         <v>1091</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C177" s="3">
         <v>565101780</v>
@@ -34564,7 +34592,7 @@
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added mod RT to 36245, corrected dx order, and resubmitted</t>
+          <t xml:space="preserve">Added mod RT to 36245, corrected dx order</t>
         </is>
       </c>
       <c r="C178" s="3">
@@ -35048,8 +35076,10 @@
       <c r="A181" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B181" s="2" t="s">
-        <v>1232</v>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added Date of Current Illness, claim note - Prior CoCM on DOS 03/05/2026</t>
+        </is>
       </c>
       <c r="C181" s="3">
         <v>570976486</v>
@@ -35198,10 +35228,8 @@
       <c r="A182" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PAID - Filed recon with MR</t>
-        </is>
+      <c r="B182" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C182" s="3">
         <v>562698907</v>
@@ -35353,7 +35381,7 @@
         <v>1091</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C183" s="3">
         <v>563060686</v>
@@ -35514,8 +35542,10 @@
       <c r="A184" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B184" s="2" t="s">
-        <v>1234</v>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added mod 24</t>
+        </is>
       </c>
       <c r="C184" s="3">
         <v>571031540</v>
@@ -35978,8 +36008,10 @@
       <c r="A187" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B187" s="2" t="s">
-        <v>1236</v>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added mods 79 and RT</t>
+        </is>
       </c>
       <c r="C187" s="3">
         <v>570992408</v>
@@ -36132,7 +36164,7 @@
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uploaded MR (fax) - by Jess</t>
+          <t xml:space="preserve">Uploaded MR (fax) by Jess</t>
         </is>
       </c>
       <c r="C188" s="3">
@@ -36290,7 +36322,7 @@
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Claim not found on portal - Resubmitted - Asked April to print</t>
+          <t xml:space="preserve">Claim not found on portal - Asked April to print</t>
         </is>
       </c>
       <c r="C189" s="3">
@@ -36444,7 +36476,7 @@
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Uploaded MR - by Jess</t>
+          <t xml:space="preserve">Uploaded MR by Jess</t>
         </is>
       </c>
       <c r="C190" s="3">
@@ -36910,7 +36942,7 @@
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Claim not found on portal - Resubmitted - Asked April to print</t>
+          <t xml:space="preserve">Claim not found on portal - Asked April to print</t>
         </is>
       </c>
       <c r="C193" s="3">
@@ -37068,7 +37100,7 @@
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed - No coverage - Policy MP.009.35</t>
+          <t xml:space="preserve">ABN signed - No coverage - Policy MP.009.35</t>
         </is>
       </c>
       <c r="C194" s="3">
@@ -37374,8 +37406,10 @@
       <c r="A196" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B196" s="2" t="s">
-        <v>1242</v>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Action required on portal</t>
+        </is>
       </c>
       <c r="C196" s="3">
         <v>562803289</v>
@@ -37526,7 +37560,7 @@
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removed line 20930, and resubmitted</t>
+          <t xml:space="preserve">Removed line 20930</t>
         </is>
       </c>
       <c r="C197" s="3">
@@ -37689,7 +37723,7 @@
         <v>1091</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C198" s="3">
         <v>565102380</v>
@@ -37859,7 +37893,7 @@
         <v>1091</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C199" s="3">
         <v>565108599</v>
@@ -38183,7 +38217,7 @@
         <v>1114</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>1136</v>
+        <v>1090</v>
       </c>
       <c r="C201" s="3">
         <v>563029504</v>
@@ -38333,7 +38367,7 @@
         <v>1091</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>1244</v>
+        <v>1090</v>
       </c>
       <c r="C202" s="3">
         <v>564043829</v>
@@ -38487,7 +38521,7 @@
         <v>1091</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C203" s="3">
         <v>563839702</v>
@@ -38644,7 +38678,7 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sent claims inquiry message on portal - ICN 100015364807</t>
+          <t xml:space="preserve">Sent claims inquiry message on portal</t>
         </is>
       </c>
       <c r="C204" s="3">
@@ -38958,7 +38992,7 @@
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Removed dx M5416, and resubmitted</t>
+          <t xml:space="preserve">Removed dx M5416</t>
         </is>
       </c>
       <c r="C206" s="3">
@@ -39115,7 +39149,7 @@
         <v>1109</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C207" s="3">
         <v>564069244</v>
@@ -39271,7 +39305,7 @@
         <v>1109</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C208" s="3">
         <v>563477944</v>
@@ -39426,7 +39460,7 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removed referring provider, and resubmitted - Rejected for invalid EDI. reasons 1. invalid id dataelement text (2), see entity type qualifier at position 2, nmi, nm1dn2insurancexx1356950653</t>
+          <t xml:space="preserve">Removed referring provider - Rejected for invalid EDI. reasons 1. invalid id dataelement text (2), see entity type qualifier at position 2, nmi, nm1dn2insurancexx1356950653</t>
         </is>
       </c>
       <c r="C209" s="3">
@@ -39584,10 +39618,8 @@
       <c r="A210" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B210" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Filed recon - PIQ-91152640</t>
-        </is>
+      <c r="B210" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C210" s="3">
         <v>563854100</v>
@@ -39744,8 +39776,10 @@
       <c r="A211" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B211" s="2" t="s">
-        <v>1249</v>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99492 paid on DOS 01/27/2026 - Awaiting resolution on claim #556349314 (DOS 01/27/2026) before reprocessing</t>
+        </is>
       </c>
       <c r="C211" s="3">
         <v>563454979</v>
@@ -40056,7 +40090,7 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - OP (possible)</t>
+          <t xml:space="preserve">OP (possible)</t>
         </is>
       </c>
       <c r="C213" s="3">
@@ -40213,7 +40247,7 @@
         <v>1091</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>1252</v>
+        <v>1090</v>
       </c>
       <c r="C214" s="3">
         <v>564053524</v>
@@ -40368,8 +40402,10 @@
       <c r="A215" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B215" s="2" t="s">
-        <v>1253</v>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added plan # FEP 105</t>
+        </is>
       </c>
       <c r="C215" s="3">
         <v>572251031</v>
@@ -40520,7 +40556,7 @@
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uploaded MR on portal - by Jess</t>
+          <t xml:space="preserve">Uploaded MR on portal by Jess</t>
         </is>
       </c>
       <c r="C216" s="3">
@@ -40691,7 +40727,7 @@
         <v>1109</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C217" s="3">
         <v>566323995</v>
@@ -40848,10 +40884,8 @@
       <c r="A218" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B218" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Secondary - Primary paid - Waiting on secondary payment</t>
-        </is>
+      <c r="B218" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C218" s="3">
         <v>564070165</v>
@@ -41014,7 +41048,7 @@
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uploaded MR - by Jess</t>
+          <t xml:space="preserve">Uploaded MR by Jess</t>
         </is>
       </c>
       <c r="C219" s="3">
@@ -41170,7 +41204,7 @@
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added auth, and resubmitted - by Tina</t>
+          <t xml:space="preserve">Added auth - by Tina</t>
         </is>
       </c>
       <c r="C220" s="3">
@@ -41326,7 +41360,7 @@
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Removed duplicate PR line, and resubmitted - Rejected: duplicate line-level COB adjustment reason code (PR) not allowed within the same service line (1) adjustment group for insurance sequence (1). X12 Info- 2430-CAS</t>
+          <t xml:space="preserve">Removed duplicate PR line - Rejected: duplicate line-level COB adjustment reason code (PR) not allowed within the same service line (1) adjustment group for insurance sequence (1). X12 Info- 2430-CAS</t>
         </is>
       </c>
       <c r="C221" s="3">
@@ -41484,7 +41518,7 @@
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removed referring provider, added ordering provider, and resubmitted - Referring provider first and last name invalid or missing</t>
+          <t xml:space="preserve">Removed referring provider, added ordering provider - Referring provider first and last name invalid or missing</t>
         </is>
       </c>
       <c r="C222" s="3">
@@ -41638,8 +41672,10 @@
       <c r="A223" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B223" s="2" t="s">
-        <v>1259</v>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added referral #</t>
+        </is>
       </c>
       <c r="C223" s="3">
         <v>573869988</v>
@@ -41796,7 +41832,7 @@
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Added COB info, and sent claim to print</t>
+          <t xml:space="preserve">Added COB info, and sent claim to print</t>
         </is>
       </c>
       <c r="C224" s="3">
@@ -41954,7 +41990,7 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID (payment approved) - Submitted claim on portal with dx M4802 only - Added auth # OP5257461084 - Rejected: invalid diagnosis pointer</t>
+          <t xml:space="preserve">Submitted claim on portal with dx M4802 only - Added auth # OP5257461084 - Rejected: invalid diagnosis pointer</t>
         </is>
       </c>
       <c r="C225" s="3">
@@ -42116,7 +42152,7 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Changed mods to NU+A2, and resubmitted - Changed mod A2 to KX, and resubmitted</t>
+          <t xml:space="preserve">Changed mods to NU+A2 - Changed mod A2 to KX</t>
         </is>
       </c>
       <c r="C226" s="3">
@@ -42436,7 +42472,7 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Removed dx M5116, and resubmitted - Dx M5116 and M5416 can't be billed together</t>
+          <t xml:space="preserve">Removed dx M5116 - Dx M5116 and M5416 can't be billed together</t>
         </is>
       </c>
       <c r="C228" s="3">
@@ -42591,7 +42627,7 @@
         <v>1087</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="C229" s="3">
         <v>564581824</v>
@@ -43226,7 +43262,7 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Changed mods to NU+A2, and resubmitted</t>
+          <t xml:space="preserve">Changed mods to NU+A2</t>
         </is>
       </c>
       <c r="C233" s="3">
@@ -43388,10 +43424,8 @@
       <c r="A234" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Secondary - Primary paid - Waiting on secondary payment</t>
-        </is>
+      <c r="B234" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C234" s="3">
         <v>545752977</v>
@@ -43548,7 +43582,7 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resubmitted - Aisha confirmed Peoria is active from Jan 2026 - Claim sent back for reprocessing - Confirmation # 26119900211</t>
+          <t xml:space="preserve">Aisha confirmed Peoria is active from Jan 2026 - Claim sent back for reprocessing</t>
         </is>
       </c>
       <c r="C235" s="3">
@@ -43706,7 +43740,7 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Added COB info, and resubmitted electronically - Claim not found on portal</t>
+          <t xml:space="preserve">Added COB info - Claim not found on portal</t>
         </is>
       </c>
       <c r="C236" s="3">
@@ -44018,7 +44052,7 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">OP - Secondary - $211.63 - Secondary paid twice; refund to secondary</t>
+          <t xml:space="preserve">Secondary paid twice - Refund $211.63 to secondary</t>
         </is>
       </c>
       <c r="C238" s="3">
@@ -44196,7 +44230,7 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Added COB info, and resubmitted - Claim not found on portal</t>
+          <t xml:space="preserve">Added COB info - Claim not found on portal</t>
         </is>
       </c>
       <c r="C239" s="3">
@@ -44350,10 +44384,8 @@
       <c r="A240" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Claim sent back for reprocessing</t>
-        </is>
+      <c r="B240" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C240" s="3">
         <v>561884409</v>
@@ -44513,7 +44545,7 @@
         <v>1091</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C241" s="3">
         <v>549217692</v>
@@ -44684,7 +44716,7 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Corrected referring provider, and resubmitted</t>
+          <t xml:space="preserve">Corrected referring provider</t>
         </is>
       </c>
       <c r="C242" s="3">
@@ -44846,7 +44878,7 @@
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrected units from 3 to 2 on portal - Confirmation # 4726236494120 - Medicare MUE for 76937 is 2 per DOS</t>
+          <t xml:space="preserve">Corrected units from 3 to 2 on portal - Medicare MUE for 76937 is 2 per DOS</t>
         </is>
       </c>
       <c r="C243" s="3">
@@ -45002,10 +45034,8 @@
       <c r="A244" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Secondary - Primary paid</t>
-        </is>
+      <c r="B244" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C244" s="3">
         <v>553137846</v>
@@ -45162,7 +45192,7 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Corrected referring provider, and resubmitted</t>
+          <t xml:space="preserve">Corrected referring provider</t>
         </is>
       </c>
       <c r="C245" s="3">
@@ -45316,7 +45346,7 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid (Medicare) - Added primary claim ID, and submitted electronically - Resubmitted to Medicare</t>
+          <t xml:space="preserve">Added primary claim ID, and submitted electronically - Resubmitted to Medicare</t>
         </is>
       </c>
       <c r="C246" s="3">
@@ -45476,10 +45506,8 @@
       <c r="A247" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Secondary - Primary paid</t>
-        </is>
+      <c r="B247" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C247" s="3">
         <v>550531610</v>
@@ -45641,7 +45669,7 @@
         <v>1091</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C248" s="3">
         <v>551974048</v>
@@ -45808,7 +45836,7 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Corrected referring provider, and resubmitted</t>
+          <t xml:space="preserve">Corrected referring provider</t>
         </is>
       </c>
       <c r="C249" s="3">
@@ -45960,7 +45988,7 @@
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Corrected referring provider, and resubmitted</t>
+          <t xml:space="preserve">Corrected referring provider</t>
         </is>
       </c>
       <c r="C250" s="3">
@@ -46116,7 +46144,7 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Added primary claim ID, and submitted electronically</t>
+          <t xml:space="preserve">Added primary claim ID, and submitted electronically</t>
         </is>
       </c>
       <c r="C251" s="3">
@@ -46426,8 +46454,10 @@
       <c r="A253" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B253" s="2" t="s">
-        <v>1282</v>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added service line with 63030 - Split bilateral service with mod RT and LT</t>
+        </is>
       </c>
       <c r="C253" s="3">
         <v>563073824</v>
@@ -46592,8 +46622,10 @@
       <c r="A254" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B254" s="2" t="s">
-        <v>1283</v>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected auth # - UTN # required</t>
+        </is>
       </c>
       <c r="C254" s="3">
         <v>571688892</v>
@@ -46748,7 +46780,7 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Claim sent back for reprocessing - Confirmation # 4726257491890 - Rendering provider McCunniff</t>
+          <t xml:space="preserve">Rendering provider McCunniff</t>
         </is>
       </c>
       <c r="C255" s="3">
@@ -46910,8 +46942,10 @@
       <c r="A256" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B256" s="2" t="s">
-        <v>1285</v>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected ordering/referring provider</t>
+        </is>
       </c>
       <c r="C256" s="3">
         <v>571606148</v>
@@ -47068,7 +47102,7 @@
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Updated supplemental insurance info, and resubmitted</t>
+          <t xml:space="preserve">Updated supplemental insurance info</t>
         </is>
       </c>
       <c r="C257" s="3">
@@ -47226,7 +47260,7 @@
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Updated dx to M5416, and resubmitted - by Felipe</t>
+          <t xml:space="preserve">Updated dx to M5416 - by Felipe</t>
         </is>
       </c>
       <c r="C258" s="3">
@@ -47378,7 +47412,7 @@
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Claim sent back for reprocessing - Confirmation # 4726257492330 - Rendering provider McCunniff</t>
+          <t xml:space="preserve">Rendering provider McCunniff</t>
         </is>
       </c>
       <c r="C259" s="3">
@@ -47544,8 +47578,10 @@
       <c r="A260" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B260" s="2" t="s">
-        <v>1289</v>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added UTN</t>
+        </is>
       </c>
       <c r="C260" s="3">
         <v>573820928</v>
@@ -47704,7 +47740,7 @@
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Added COB info, and crossed over electronically</t>
+          <t xml:space="preserve">Added COB info, and crossed over electronically</t>
         </is>
       </c>
       <c r="C261" s="3">
@@ -47856,7 +47892,7 @@
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Added COB info, and resubmitted - Secondary denied for timely filing - Corrected rendering and referring provider, and resubmitted - Invalid rendering provider NPI</t>
+          <t xml:space="preserve">Added COB info - Secondary denied for timely filing - Corrected rendering and referring provider - Invalid rendering provider NPI</t>
         </is>
       </c>
       <c r="C262" s="3">
@@ -48014,7 +48050,7 @@
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Medicare didn't cross over to Mercy Care - Submitted electronically</t>
+          <t xml:space="preserve">Medicare didn't cross over to Mercy Care - Submitted electronically</t>
         </is>
       </c>
       <c r="C263" s="3">
@@ -48168,7 +48204,7 @@
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Added COB info, and crossed over electronically</t>
+          <t xml:space="preserve">Added COB info, and crossed over electronically</t>
         </is>
       </c>
       <c r="C264" s="3">
@@ -48472,8 +48508,10 @@
       <c r="A266" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B266" s="2" t="s">
-        <v>1285</v>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected ordering/referring provider</t>
+        </is>
       </c>
       <c r="C266" s="3">
         <v>571606263</v>
@@ -48630,8 +48668,10 @@
       <c r="A267" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B267" s="2" t="s">
-        <v>1294</v>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted to Humana - HCO/HMO listed Humana</t>
+        </is>
       </c>
       <c r="C267" s="3">
         <v>554943318</v>
@@ -48782,7 +48822,7 @@
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filed appeal on portal with MR - Confirmation # 148586224 - L1851 requires auth; none obtained</t>
+          <t xml:space="preserve">Filed appeal on portal with MR - L1851 requires auth; none obtained</t>
         </is>
       </c>
       <c r="C268" s="3">
@@ -49096,7 +49136,7 @@
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Filed auth on Zyter - Details Overview - OPFOEY0914142230 - No auth request found for 63655</t>
+          <t xml:space="preserve">Filed auth on Zyter - Details Overview - OPFOEY0914142230 - No auth request found for 63655</t>
         </is>
       </c>
       <c r="C270" s="3">
@@ -49250,8 +49290,10 @@
       <c r="A271" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B271" s="2" t="s">
-        <v>1285</v>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected ordering/referring provider</t>
+        </is>
       </c>
       <c r="C271" s="3">
         <v>571585569</v>
@@ -49410,10 +49452,8 @@
       <c r="A272" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B272" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Secondary - Primary paid</t>
-        </is>
+      <c r="B272" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C272" s="3">
         <v>556803684</v>
@@ -49571,7 +49611,7 @@
         <v>1091</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C273" s="3">
         <v>558686302</v>
@@ -50054,7 +50094,7 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Primary paid - Removed mod RT, and resubmitted - by Deanne</t>
+          <t xml:space="preserve">Removed mod RT - by Deanne</t>
         </is>
       </c>
       <c r="C276" s="3">
@@ -50206,7 +50246,7 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Corrected COB info, and resubmitted</t>
+          <t xml:space="preserve">Corrected COB info</t>
         </is>
       </c>
       <c r="C277" s="3">
@@ -50366,7 +50406,7 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MBI updated on chart, and resubmitted</t>
+          <t xml:space="preserve">MBI updated on chart</t>
         </is>
       </c>
       <c r="C278" s="3">
@@ -50522,7 +50562,7 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Crossed over to secondary</t>
+          <t xml:space="preserve">Crossed over to secondary</t>
         </is>
       </c>
       <c r="C279" s="3">
@@ -50688,7 +50728,7 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Sent on 06/08/2026 - None of the secondary claims are paid</t>
+          <t xml:space="preserve">Sent on 06/08/2026 - None of the secondary claims are paid</t>
         </is>
       </c>
       <c r="C280" s="3">
@@ -50846,7 +50886,7 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Crossed over to secondary</t>
+          <t xml:space="preserve">Crossed over to secondary</t>
         </is>
       </c>
       <c r="C281" s="3">
@@ -51000,8 +51040,10 @@
       <c r="A282" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B282" s="2" t="s">
-        <v>1305</v>
+      <c r="B282" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBI updated on chart</t>
+        </is>
       </c>
       <c r="C282" s="3">
         <v>571616270</v>
@@ -51158,8 +51200,10 @@
       <c r="A283" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B283" s="2" t="s">
-        <v>1305</v>
+      <c r="B283" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBI updated on chart</t>
+        </is>
       </c>
       <c r="C283" s="3">
         <v>571616337</v>
@@ -51314,8 +51358,10 @@
       <c r="A284" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B284" s="2" t="s">
-        <v>1285</v>
+      <c r="B284" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected ordering/referring provider</t>
+        </is>
       </c>
       <c r="C284" s="3">
         <v>571585850</v>
@@ -51472,8 +51518,10 @@
       <c r="A285" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B285" s="2" t="s">
-        <v>1285</v>
+      <c r="B285" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected ordering/referring provider</t>
+        </is>
       </c>
       <c r="C285" s="3">
         <v>571585903</v>
@@ -51626,8 +51674,10 @@
       <c r="A286" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B286" s="2" t="s">
-        <v>1306</v>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrected ordering/referring provider</t>
+        </is>
       </c>
       <c r="C286" s="3">
         <v>558247000</v>
@@ -51778,7 +51828,7 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Added rendering NPI 1518261023 to box 24J and COB info, and resubmitted</t>
+          <t xml:space="preserve">Added rendering NPI 1518261023 to box 24J and COB info</t>
         </is>
       </c>
       <c r="C287" s="3">
@@ -51940,7 +51990,7 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Removed mod, and resubmitted - by Deanne</t>
+          <t xml:space="preserve">Removed mod - by Deanne</t>
         </is>
       </c>
       <c r="C288" s="3">
@@ -52090,8 +52140,10 @@
       <c r="A289" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B289" s="2" t="s">
-        <v>1309</v>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBI updated on chart - MBI End Date 04/14/2026</t>
+        </is>
       </c>
       <c r="C289" s="3">
         <v>558264075</v>
@@ -52242,7 +52294,7 @@
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - Added adjustments, and resubmitted to secondary after rejection - Resubmitted 63663 with 1 unit instead of 2 - by Tina - Denied for frequency - MBI updated on chart, and resubmitted</t>
+          <t xml:space="preserve">Added adjustments, and resubmitted to secondary after rejection - Resubmitted 63663 with 1 unit instead of 2 - by Tina - Denied for frequency - MBI updated on chart</t>
         </is>
       </c>
       <c r="C290" s="3">
@@ -52400,10 +52452,8 @@
       <c r="A291" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B291" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Secondary - Primary paid - Waiting on secondary payment</t>
-        </is>
+      <c r="B291" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C291" s="3">
         <v>558264882</v>
@@ -52560,7 +52610,7 @@
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MBI updated on chart, and resubmitted - MBI End Date 04/14/2026</t>
+          <t xml:space="preserve">MBI updated on chart - MBI End Date 04/14/2026</t>
         </is>
       </c>
       <c r="C292" s="3">
@@ -52716,7 +52766,7 @@
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrected referring provider, and resubmitted</t>
+          <t xml:space="preserve">Corrected referring provider</t>
         </is>
       </c>
       <c r="C293" s="3">
@@ -52880,7 +52930,7 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Pending posting</t>
+          <t xml:space="preserve">Pending posting</t>
         </is>
       </c>
       <c r="C294" s="3">
@@ -53038,7 +53088,7 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - MBI updated on chart, and resubmitted - MBI End Date 04/14/2026</t>
+          <t xml:space="preserve">MBI updated on chart - MBI End Date 04/14/2026</t>
         </is>
       </c>
       <c r="C295" s="3">
@@ -53190,7 +53240,7 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MBI updated on chart, and resubmitted - MBI End Date 04/14/2026</t>
+          <t xml:space="preserve">MBI updated on chart - MBI End Date 04/14/2026</t>
         </is>
       </c>
       <c r="C296" s="3">
@@ -53350,10 +53400,8 @@
       <c r="A297" s="2" t="s">
         <v>1087</v>
       </c>
-      <c r="B297" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Secondary - Primary paid - Waiting on secondary payment</t>
-        </is>
+      <c r="B297" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C297" s="3">
         <v>559008757</v>
@@ -53512,7 +53560,7 @@
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - MBI updated on chart (typo corrected), and resubmitted</t>
+          <t xml:space="preserve">MBI updated on chart (typo corrected)</t>
         </is>
       </c>
       <c r="C298" s="3">
@@ -53684,7 +53732,7 @@
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filed appeal for 63685 - Confirmation # 2686931212 - TAT 60 days - Filed auth on Zyter - No auth found</t>
+          <t xml:space="preserve">Filed appeal for 63685 - TAT 60 days - Filed auth on Zyter - No auth found</t>
         </is>
       </c>
       <c r="C299" s="3">
@@ -53838,7 +53886,7 @@
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Corrected service line 1 on portal: billed 93970 instead of 93923, and reopened claim - Confirmation # 4726237493100 - 93923 was billed on 2 separate lines and 93970 was missed</t>
+          <t xml:space="preserve">Corrected service line 1 on portal: billed 93970 instead of 93923, and reopened claim - 93923 was billed on 2 separate lines and 93970 was missed</t>
         </is>
       </c>
       <c r="C300" s="3">
@@ -53986,10 +54034,8 @@
       <c r="A301" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B301" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Secondary - Primary paid - Waiting on secondary payment</t>
-        </is>
+      <c r="B301" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C301" s="3">
         <v>559107561</v>
@@ -54146,7 +54192,7 @@
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added mod 79 on portal, and reopened claim - Confirmation # 4726237491810</t>
+          <t xml:space="preserve">Added mod 79 on portal, and reopened claim</t>
         </is>
       </c>
       <c r="C302" s="3">
@@ -54298,7 +54344,7 @@
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed - Requested void of claim 569311834 per Medicare recoup - Home Health Scottsdale is the delegated DME vendor on DOS</t>
+          <t xml:space="preserve">ABN signed - Requested void of claim 569311834 per Medicare recoup - Home Health Scottsdale is the delegated DME vendor on DOS</t>
         </is>
       </c>
       <c r="C303" s="3">
@@ -54456,10 +54502,8 @@
       <c r="A304" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B304" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Secondary - Primary paid - Waiting on secondary payment</t>
-        </is>
+      <c r="B304" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C304" s="3">
         <v>559368713</v>
@@ -54614,8 +54658,10 @@
       <c r="A305" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B305" s="2" t="s">
-        <v>1305</v>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBI updated on chart</t>
+        </is>
       </c>
       <c r="C305" s="3">
         <v>569723919</v>
@@ -54773,7 +54819,7 @@
         <v>1114</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="C306" s="3">
         <v>561726685</v>
@@ -54946,7 +54992,7 @@
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Corrected referring provider, and resubmitted</t>
+          <t xml:space="preserve">Corrected referring provider</t>
         </is>
       </c>
       <c r="C307" s="3">
@@ -55104,7 +55150,7 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Corrected referring and ordering providers, and resubmitted</t>
+          <t xml:space="preserve">Corrected referring and ordering providers</t>
         </is>
       </c>
       <c r="C308" s="3">
@@ -55252,10 +55298,8 @@
       <c r="A309" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B309" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PAID</t>
-        </is>
+      <c r="B309" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C309" s="3">
         <v>561853521</v>
@@ -55408,7 +55452,7 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Pending posting</t>
+          <t xml:space="preserve">Pending posting</t>
         </is>
       </c>
       <c r="C310" s="3">
@@ -55564,10 +55608,8 @@
       <c r="A311" s="2" t="s">
         <v>1109</v>
       </c>
-      <c r="B311" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Secondary - Primary paid - Waiting on secondary payment</t>
-        </is>
+      <c r="B311" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C311" s="3">
         <v>560682170</v>
@@ -55722,7 +55764,7 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Added dx M25562 (only knee dx on order encounter notes), and resubmitted</t>
+          <t xml:space="preserve">Added dx M25562 (only knee dx on order encounter notes)</t>
         </is>
       </c>
       <c r="C312" s="3">
@@ -55886,7 +55928,7 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Added Medicare ICN, and crossed over electronically</t>
+          <t xml:space="preserve">Added Medicare ICN, and crossed over electronically</t>
         </is>
       </c>
       <c r="C313" s="3">
@@ -56039,7 +56081,7 @@
         <v>1091</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C314" s="3">
         <v>562932709</v>
@@ -56214,7 +56256,7 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">MBI updated on chart, and resubmitted - by QRobertson30</t>
+          <t xml:space="preserve">MBI updated on chart - by QRobertson30</t>
         </is>
       </c>
       <c r="C315" s="3">
@@ -56368,8 +56410,10 @@
       <c r="A316" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B316" s="2" t="s">
-        <v>1326</v>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBI updated on chart - Missing/incomplete/invalid patient identifier</t>
+        </is>
       </c>
       <c r="C316" s="3">
         <v>574464619</v>
@@ -56528,7 +56572,7 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Pending posting</t>
+          <t xml:space="preserve">Pending posting</t>
         </is>
       </c>
       <c r="C317" s="3">
@@ -56684,8 +56728,10 @@
       <c r="A318" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B318" s="2" t="s">
-        <v>1305</v>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBI updated on chart</t>
+        </is>
       </c>
       <c r="C318" s="3">
         <v>574479854</v>
@@ -57002,7 +57048,7 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Resubmitted with Medicare COB claim info - Secondary payment appears to have been recouped due to a duplicate error</t>
+          <t xml:space="preserve">Resubmitted with Medicare COB claim info - Secondary payment appears to have been recouped due to a duplicate error</t>
         </is>
       </c>
       <c r="C320" s="3">
@@ -57306,8 +57352,10 @@
       <c r="A322" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B322" s="2" t="s">
-        <v>1305</v>
+      <c r="B322" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBI updated on chart</t>
+        </is>
       </c>
       <c r="C322" s="3">
         <v>574481102</v>
@@ -57460,8 +57508,10 @@
       <c r="A323" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B323" s="2" t="s">
-        <v>1305</v>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBI updated on chart</t>
+        </is>
       </c>
       <c r="C323" s="3">
         <v>574481188</v>
@@ -57614,8 +57664,10 @@
       <c r="A324" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B324" s="2" t="s">
-        <v>1330</v>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Added UTN for 63655 approval</t>
+        </is>
       </c>
       <c r="C324" s="3">
         <v>574466870</v>
@@ -57768,8 +57820,10 @@
       <c r="A325" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B325" s="2" t="s">
-        <v>1331</v>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed referring provider</t>
+        </is>
       </c>
       <c r="C325" s="3">
         <v>574464654</v>
@@ -57926,8 +57980,10 @@
       <c r="A326" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B326" s="2" t="s">
-        <v>1331</v>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removed referring provider</t>
+        </is>
       </c>
       <c r="C326" s="3">
         <v>574464671</v>
@@ -58082,8 +58138,10 @@
       <c r="A327" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B327" s="2" t="s">
-        <v>1305</v>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBI updated on chart</t>
+        </is>
       </c>
       <c r="C327" s="3">
         <v>574466946</v>
@@ -58236,8 +58294,10 @@
       <c r="A328" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B328" s="2" t="s">
-        <v>1305</v>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBI updated on chart</t>
+        </is>
       </c>
       <c r="C328" s="3">
         <v>574481284</v>
@@ -58390,8 +58450,10 @@
       <c r="A329" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B329" s="2" t="s">
-        <v>1305</v>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MBI updated on chart</t>
+        </is>
       </c>
       <c r="C329" s="3">
         <v>574479803</v>
@@ -58862,8 +58924,10 @@
       <c r="A332" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B332" s="2" t="s">
-        <v>1333</v>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edited billing provider, added COB claim info</t>
+        </is>
       </c>
       <c r="C332" s="3">
         <v>564117213</v>
@@ -59020,7 +59084,7 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filed appeal for 75774 - Confirmation # 2718022455 - TAT 60 days</t>
+          <t xml:space="preserve">Filed appeal for 75774 - TAT 60 days</t>
         </is>
       </c>
       <c r="C333" s="3">
@@ -59475,7 +59539,7 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Checking tax code on UMR records - Waiting on email response</t>
+          <t xml:space="preserve">Checking tax code on UMR records - Waiting on email response</t>
         </is>
       </c>
       <c r="C336" s="3">
@@ -59788,7 +59852,7 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Called payer - Rep Keran - Call ref # REQ0679770 - Claim escalated - TAT 30 days</t>
+          <t xml:space="preserve">Rep Keran - Claim escalated - TAT 30 days</t>
         </is>
       </c>
       <c r="C338" s="3">
@@ -59927,7 +59991,7 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Called payer - Rep Keran - Call ref # REQ0679770 - Charges issue under review on claim 553079628</t>
+          <t xml:space="preserve">Rep Keran - Charges issue under review on claim 553079628</t>
         </is>
       </c>
       <c r="C339" s="3">
@@ -60064,7 +60128,7 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Called payer - Rep Keran - Call ref # REQ0679770 - Charges issue under review on claim 553079628</t>
+          <t xml:space="preserve">Rep Keran - Charges issue under review on claim 553079628</t>
         </is>
       </c>
       <c r="C340" s="3">
@@ -60203,7 +60267,7 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network) - Call ref # 0800645 - Rejected: Member not found (X12 2010BA-NM1)</t>
+          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network) - Rejected: Member not found (X12 2010BA-NM1)</t>
         </is>
       </c>
       <c r="C341" s="3">
@@ -60359,7 +60423,7 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network) - Call ref # 0800645</t>
+          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network)</t>
         </is>
       </c>
       <c r="C342" s="3">
@@ -60515,7 +60579,7 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network) - Call ref # 0800645 - Rejected: Member not found (X12 2010BA-NM1)</t>
+          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network) - Rejected: Member not found (X12 2010BA-NM1)</t>
         </is>
       </c>
       <c r="C343" s="3">
@@ -60673,7 +60737,7 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network) - Call ref # 0800645</t>
+          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network)</t>
         </is>
       </c>
       <c r="C344" s="3">
@@ -60829,7 +60893,7 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network) - Call ref # 0800645 - Rejected: Member not found (X12 2010BA-NM1)</t>
+          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network) - Rejected: Member not found (X12 2010BA-NM1)</t>
         </is>
       </c>
       <c r="C345" s="3">
@@ -60985,7 +61049,7 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Adjusted allowed amount per secondary EOB</t>
+          <t xml:space="preserve">Adjusted allowed amount per secondary EOB</t>
         </is>
       </c>
       <c r="C346" s="3">
@@ -61124,7 +61188,7 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Uploaded MR (Message Center) - Payer: no MR received - Uploaded MR on PCH portal - AA0019803260980101003 - MR was requested</t>
+          <t xml:space="preserve">MR sent via Message Center, then PCH portal - Payer had no MR on file - MR was requested</t>
         </is>
       </c>
       <c r="C347" s="3">
@@ -61429,7 +61493,7 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resubmitted with MR - by Tina - Uploaded MR on portal</t>
+          <t xml:space="preserve">Resubmitted with MR - by Tina</t>
         </is>
       </c>
       <c r="C349" s="3">
@@ -61847,7 +61911,7 @@
         <v>1114</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="C352" s="3">
         <v>556723206</v>
@@ -62261,10 +62325,8 @@
       <c r="A355" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B355" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Uploaded MR on portal - Case ID# 18150</t>
-        </is>
+      <c r="B355" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C355" s="3">
         <v>557575573</v>
@@ -62393,8 +62455,10 @@
       <c r="BB355" s="2" t="s">
         <v>1453</v>
       </c>
-      <c r="BC355" s="2" t="s">
-        <v>1090</v>
+      <c r="BC355" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Case ID# 18150</t>
+        </is>
       </c>
       <c r="BD355" s="4">
         <v>46341</v>
@@ -63405,7 +63469,7 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rep Arvin-CFR replied: MR under review - Document review # 208075035 - TAT 30 days - Uploaded MR (Message Center)</t>
+          <t xml:space="preserve">Rep Arvin-CFR replied: MR under review - TAT 30 days</t>
         </is>
       </c>
       <c r="C363" s="3">
@@ -63827,10 +63891,8 @@
       <c r="A366" s="2" t="s">
         <v>1091</v>
       </c>
-      <c r="B366" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Uploaded MR on portal - Case ID# 17527</t>
-        </is>
+      <c r="B366" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C366" s="3">
         <v>569719928</v>
@@ -63971,7 +64033,7 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rep Vin M: MR under review - Document handle # 208203095 - Open inquiry on portal Message Center</t>
+          <t xml:space="preserve">Rep Vin M: MR under review - Open inquiry on portal Message Center</t>
         </is>
       </c>
       <c r="C367" s="3">
@@ -64099,8 +64161,10 @@
       <c r="BB367" s="2" t="s">
         <v>1754</v>
       </c>
-      <c r="BC367" s="2" t="s">
-        <v>1090</v>
+      <c r="BC367" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Document handle # 208203095</t>
+        </is>
       </c>
       <c r="BD367" s="4">
         <v>46337</v>
@@ -64115,7 +64179,7 @@
       </c>
       <c r="B368" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network) - Call ref # 0800645</t>
+          <t xml:space="preserve">Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network)</t>
         </is>
       </c>
       <c r="C368" s="3">
@@ -64534,7 +64598,7 @@
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resubmitted for printing - Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network) - Call ref # 0800645</t>
+          <t xml:space="preserve">Resubmitted for printing - Resubmitted to Optum (payer ID OCN01) - Alignment rep Puja S: claims should be mailed to Optum PO Box 6099, Torrance, CA 90504 (address belongs to HealthCare Partners, now part of Optum Care Network)</t>
         </is>
       </c>
       <c r="C371" s="3">
@@ -64671,7 +64735,7 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Member ID updated on chart, and resubmitted - Rejected: Member not found on payer member table. X12 Info- 2010BA-NM109A3-21. Claim rejected as unprocessable: missing or invalid information - member not found</t>
+          <t xml:space="preserve">Member ID updated on chart - Rejected: Member not found on payer member table. X12 Info- 2010BA-NM109A3-21. Claim rejected as unprocessable: missing or invalid information - member not found</t>
         </is>
       </c>
       <c r="C372" s="3">
@@ -64808,7 +64872,7 @@
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Pending posting</t>
+          <t xml:space="preserve">Pending posting</t>
         </is>
       </c>
       <c r="C373" s="3">
@@ -64951,7 +65015,7 @@
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - Humana considers GAE experimental or not medically necessary for chronic pain - Humana Medicare Advantage Medical Coverage Policy: Injections for Chronic Pain Conditions - Uploaded MR - by DMinker30A</t>
+          <t xml:space="preserve">Humana considers GAE experimental or not medically necessary for chronic pain - Humana Medicare Advantage Medical Coverage Policy: Injections for Chronic Pain Conditions - Uploaded MR by DMinker30A</t>
         </is>
       </c>
       <c r="C374" s="3">
@@ -65115,7 +65179,7 @@
       </c>
       <c r="B375" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - Humana considers GAE experimental or not medically necessary for chronic pain - Humana Medicare Advantage Medical Coverage Policy: Injections for Chronic Pain Conditions - Uploaded MR - by DMinker30A</t>
+          <t xml:space="preserve">Humana considers GAE experimental or not medically necessary for chronic pain - Humana Medicare Advantage Medical Coverage Policy: Injections for Chronic Pain Conditions - Uploaded MR by DMinker30A</t>
         </is>
       </c>
       <c r="C375" s="3">
@@ -65432,7 +65496,7 @@
         <v>1114</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>1358</v>
+        <v>1090</v>
       </c>
       <c r="C377" s="3">
         <v>546049607</v>
@@ -65587,7 +65651,7 @@
       </c>
       <c r="B378" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - Called payer - Rep Heather - Case # 12323141 - Provider wasn't participating with this plan until 04/01/2026 - Dr. Mayuran is INN for commercial lines but OON for Medicare</t>
+          <t xml:space="preserve">Called payer - Rep Heather - Provider wasn't participating with this plan until 04/01/2026 - Dr. Mayuran is INN for commercial lines but OON for Medicare</t>
         </is>
       </c>
       <c r="C378" s="3">
@@ -65888,7 +65952,7 @@
         <v>1114</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>1329</v>
+        <v>1090</v>
       </c>
       <c r="C380" s="3">
         <v>547275123</v>
@@ -66045,7 +66109,7 @@
       </c>
       <c r="B381" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - Humana considers GAE experimental or not medically necessary for chronic pain - Humana Medicare Advantage Medical Coverage Policy: Injections for Chronic Pain Conditions - Uploaded MR - by DMinker30A</t>
+          <t xml:space="preserve">Humana considers GAE experimental or not medically necessary for chronic pain - Humana Medicare Advantage Medical Coverage Policy: Injections for Chronic Pain Conditions - Uploaded MR by DMinker30A</t>
         </is>
       </c>
       <c r="C381" s="3">
@@ -66209,7 +66273,7 @@
       </c>
       <c r="B382" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - GAE (37242) experimental per Aetna policy 0856 (Embolization: Selected Procedures)</t>
+          <t xml:space="preserve">GAE (37242) experimental per Aetna policy 0856 (Embolization: Selected Procedures)</t>
         </is>
       </c>
       <c r="C382" s="3">
@@ -66527,7 +66591,7 @@
       </c>
       <c r="B384" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - Filed recon - Request ID TT2646380 - Auth 19816932 denied</t>
+          <t xml:space="preserve">Auth 19816932 denied</t>
         </is>
       </c>
       <c r="C384" s="3">
@@ -67349,7 +67413,7 @@
       </c>
       <c r="B389" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - 37242-53 not supported: embolization discontinued, procedure stopped at arterial access - Resubmitted with 37242 - by QNavarro30</t>
+          <t xml:space="preserve">37242-53 not supported: embolization discontinued, procedure stopped at arterial access - Resubmitted with 37242 - by QNavarro30</t>
         </is>
       </c>
       <c r="C389" s="3">
@@ -67683,8 +67747,10 @@
       <c r="A391" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B391" s="2" t="s">
-        <v>1364</v>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ABN signed - PT was an inpatient at hospital COBALT REHABILITATION HOSPITAL (NPI 1679954002) from 06/04/2026 to 06/15/2026</t>
+        </is>
       </c>
       <c r="C391" s="3">
         <v>564672683</v>
@@ -67838,7 +67904,7 @@
         <v>1114</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>1358</v>
+        <v>1090</v>
       </c>
       <c r="C392" s="3">
         <v>562699568</v>
@@ -67987,8 +68053,10 @@
       <c r="A393" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B393" s="2" t="s">
-        <v>1365</v>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance</t>
+        </is>
       </c>
       <c r="C393" s="3">
         <v>563177256</v>
@@ -68141,8 +68209,10 @@
       <c r="A394" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B394" s="2" t="s">
-        <v>1365</v>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance</t>
+        </is>
       </c>
       <c r="C394" s="3">
         <v>563164453</v>
@@ -68298,7 +68368,7 @@
         <v>1114</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>1358</v>
+        <v>1090</v>
       </c>
       <c r="C395" s="3">
         <v>563203416</v>
@@ -68447,8 +68517,10 @@
       <c r="A396" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B396" s="2" t="s">
-        <v>1365</v>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance</t>
+        </is>
       </c>
       <c r="C396" s="3">
         <v>563163093</v>
@@ -68605,7 +68677,7 @@
       </c>
       <c r="B397" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Shifted to PT - Plan termed 04/30/2026</t>
+          <t xml:space="preserve">Shifted to PT - Plan termed 04/30/2026</t>
         </is>
       </c>
       <c r="C397" s="3">
@@ -68757,7 +68829,7 @@
       </c>
       <c r="B398" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed for $400.00 - Bundled with L0637 claim on DOS 12/04/2023 - Supplier SonoSpine Arizona LLC - Member ID updated on chart, and resubmitted - by Bri</t>
+          <t xml:space="preserve">ABN signed for $400.00 - Bundled with L0637 claim on DOS 12/04/2023 - Supplier SonoSpine Arizona LLC - Member ID updated on chart - by Bri</t>
         </is>
       </c>
       <c r="C398" s="3">
@@ -68912,7 +68984,7 @@
         <v>1114</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>1111</v>
+        <v>1090</v>
       </c>
       <c r="C399" s="3">
         <v>551321878</v>
@@ -69227,7 +69299,7 @@
       </c>
       <c r="B401" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - Dr. Krause OON - Approved by Optum Medicare Advantage on 04/08/2026</t>
+          <t xml:space="preserve">Dr. Krause OON - Approved by Optum Medicare Advantage on 04/08/2026</t>
         </is>
       </c>
       <c r="C401" s="3">
@@ -69381,7 +69453,7 @@
       </c>
       <c r="B402" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removed mod 79, added mod 24, and resubmitted - Added mod 79, and resubmitted</t>
+          <t xml:space="preserve">Removed mod 79, added mod 24 - Added mod 79</t>
         </is>
       </c>
       <c r="C402" s="3">
@@ -69535,7 +69607,7 @@
       </c>
       <c r="B403" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - by Amanda</t>
+          <t xml:space="preserve">Adjusted balance by Amanda</t>
         </is>
       </c>
       <c r="C403" s="3">
@@ -69845,7 +69917,7 @@
       </c>
       <c r="B405" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Payer approved correction - Corrected dx order (I83811 as primary), and resubmitted</t>
+          <t xml:space="preserve">Payer approved correction - Corrected dx order (I83811 as primary)</t>
         </is>
       </c>
       <c r="C405" s="3">
@@ -70151,7 +70223,7 @@
       </c>
       <c r="B407" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - Removed dx M5416, and resubmitted on portal - Dx M5116 and M5416 can't be reported together - Claim downloaded</t>
+          <t xml:space="preserve">Removed dx M5416, and resubmitted on portal - Dx M5116 and M5416 can't be reported together - Claim downloaded</t>
         </is>
       </c>
       <c r="C407" s="3">
@@ -70307,7 +70379,7 @@
       </c>
       <c r="B408" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - No auth on file (required for 63047)</t>
+          <t xml:space="preserve">No auth on file (required for 63047)</t>
         </is>
       </c>
       <c r="C408" s="3">
@@ -70459,8 +70531,10 @@
       <c r="A409" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B409" s="2" t="s">
-        <v>1376</v>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93923 bundled with 93925</t>
+        </is>
       </c>
       <c r="C409" s="3">
         <v>553810379</v>
@@ -70610,7 +70684,7 @@
         <v>1114</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>1329</v>
+        <v>1090</v>
       </c>
       <c r="C410" s="3">
         <v>556692374</v>
@@ -70759,7 +70833,7 @@
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - No auth on file - Collagen dressings</t>
+          <t xml:space="preserve">No auth for collagen dressings</t>
         </is>
       </c>
       <c r="C411" s="3">
@@ -70913,7 +70987,7 @@
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - No auth on file - Collagen dressings</t>
+          <t xml:space="preserve">No auth for collagen dressings</t>
         </is>
       </c>
       <c r="C412" s="3">
@@ -71067,7 +71141,7 @@
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - No auth on file - Collagen dressings</t>
+          <t xml:space="preserve">No auth for collagen dressings</t>
         </is>
       </c>
       <c r="C413" s="3">
@@ -71221,7 +71295,7 @@
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - Auth only included 63045</t>
+          <t xml:space="preserve">Auth only included 63045</t>
         </is>
       </c>
       <c r="C414" s="3">
@@ -71525,7 +71599,7 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed - No coverage - Policy MP.009.35</t>
+          <t xml:space="preserve">ABN signed - No coverage - Policy MP.009.35</t>
         </is>
       </c>
       <c r="C416" s="3">
@@ -71679,7 +71753,7 @@
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed - No coverage - Policy MP.009.35</t>
+          <t xml:space="preserve">ABN signed - No coverage - Policy MP.009.35</t>
         </is>
       </c>
       <c r="C417" s="3">
@@ -71832,7 +71906,7 @@
         <v>1114</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>1329</v>
+        <v>1090</v>
       </c>
       <c r="C418" s="3">
         <v>562510509</v>
@@ -71983,8 +72057,10 @@
       <c r="A419" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B419" s="2" t="s">
-        <v>1376</v>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93923 bundled with 93925</t>
+        </is>
       </c>
       <c r="C419" s="3">
         <v>555438747</v>
@@ -72135,7 +72211,7 @@
       </c>
       <c r="B420" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed - PCP is the delegated DME vendor</t>
+          <t xml:space="preserve">ABN signed - PCP is the delegated DME vendor</t>
         </is>
       </c>
       <c r="C420" s="3">
@@ -72285,8 +72361,10 @@
       <c r="A421" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B421" s="2" t="s">
-        <v>1382</v>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No ABN signed - PCP is the delegated DME vendor</t>
+        </is>
       </c>
       <c r="C421" s="3">
         <v>559737254</v>
@@ -72443,7 +72521,7 @@
       </c>
       <c r="B422" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed - No auth on file</t>
+          <t xml:space="preserve">ABN signed</t>
         </is>
       </c>
       <c r="C422" s="3">
@@ -72595,8 +72673,10 @@
       <c r="A423" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B423" s="2" t="s">
-        <v>1384</v>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auth was requested to Medicare and not Humana</t>
+        </is>
       </c>
       <c r="C423" s="3">
         <v>561728234</v>
@@ -72755,7 +72835,7 @@
       </c>
       <c r="B424" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - Adjusted insurance balance - Provider OON - Audit # WY03MQKV - Provider inquiry</t>
+          <t xml:space="preserve">Shifted to PT - Adjusted insurance balance - Provider OON - Provider inquiry</t>
         </is>
       </c>
       <c r="C424" s="3">
@@ -72911,7 +72991,7 @@
       </c>
       <c r="B425" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removed line 93923 (bundled), and resubmitted - 93923 billed on claim 568263929</t>
+          <t xml:space="preserve">Removed line 93923 (bundled) - 93923 billed on claim 568263929</t>
         </is>
       </c>
       <c r="C425" s="3">
@@ -73071,7 +73151,7 @@
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - 93923 bundled with 93925 and 93970 - 93923 billed on claim 568254615</t>
+          <t xml:space="preserve">93923 bundled with 93925 and 93970 - 93923 billed on claim 568254615</t>
         </is>
       </c>
       <c r="C426" s="3">
@@ -73377,7 +73457,7 @@
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - Auth only included 63650 (63685 adjusted)</t>
+          <t xml:space="preserve">Auth only included 63650 (63685 adjusted)</t>
         </is>
       </c>
       <c r="C428" s="3">
@@ -73531,7 +73611,7 @@
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed (charges per ABN)</t>
+          <t xml:space="preserve">ABN signed (charges per ABN)</t>
         </is>
       </c>
       <c r="C429" s="3">
@@ -73685,7 +73765,7 @@
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - Ordering provider Dr. Krause notified of the dx issue</t>
+          <t xml:space="preserve">Ordering provider Dr. Krause notified of the dx issue</t>
         </is>
       </c>
       <c r="C430" s="3">
@@ -73839,10 +73919,8 @@
       <c r="A431" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B431" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Adjusted balance - No auth on file</t>
-        </is>
+      <c r="B431" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C431" s="3">
         <v>561851402</v>
@@ -73995,7 +74073,7 @@
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Member ID updated on chart, and resubmitted - by Jess</t>
+          <t xml:space="preserve">Member ID updated on chart - by Jess</t>
         </is>
       </c>
       <c r="C432" s="3">
@@ -74147,7 +74225,7 @@
       </c>
       <c r="B433" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed - No coverage</t>
+          <t xml:space="preserve">ABN signed - No coverage</t>
         </is>
       </c>
       <c r="C433" s="3">
@@ -74303,7 +74381,7 @@
       </c>
       <c r="B434" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Jess asked our team to post payment</t>
+          <t xml:space="preserve">Jess asked our team to post payment</t>
         </is>
       </c>
       <c r="C434" s="3">
@@ -74457,7 +74535,7 @@
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - A-codes not included in auth/referral</t>
+          <t xml:space="preserve">A-codes not included in auth/referral</t>
         </is>
       </c>
       <c r="C435" s="3">
@@ -74761,10 +74839,8 @@
       <c r="A437" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B437" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Adjusted balance - No auth on file</t>
-        </is>
+      <c r="B437" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C437" s="3">
         <v>563985783</v>
@@ -74917,7 +74993,7 @@
       </c>
       <c r="B438" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - A-codes not covered under BCBS M2K plan</t>
+          <t xml:space="preserve">A-codes not covered under BCBS M2K plan</t>
         </is>
       </c>
       <c r="C438" s="3">
@@ -75071,7 +75147,7 @@
       </c>
       <c r="B439" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed - No auth on file</t>
+          <t xml:space="preserve">ABN signed</t>
         </is>
       </c>
       <c r="C439" s="3">
@@ -75216,7 +75292,7 @@
       </c>
       <c r="B440" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - GAE (37242) experimental per Aetna for knee pain</t>
+          <t xml:space="preserve">GAE (37242) experimental per Aetna for knee pain</t>
         </is>
       </c>
       <c r="C440" s="3">
@@ -75379,7 +75455,7 @@
         <v>1114</v>
       </c>
       <c r="B441" s="2" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="C441" s="3">
         <v>563010537</v>
@@ -75680,7 +75756,7 @@
       </c>
       <c r="B443" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Primary paid - VA doesn't cover BH</t>
+          <t xml:space="preserve">VA doesn't cover BH</t>
         </is>
       </c>
       <c r="C443" s="3">
@@ -75982,8 +76058,10 @@
       <c r="A445" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B445" s="2" t="s">
-        <v>1405</v>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Certificate Number 260506159813 was cancelled and it didn't say auth was not required - Auth for procedure 63030 and 63047 is required</t>
+        </is>
       </c>
       <c r="C445" s="3">
         <v>559152456</v>
@@ -76142,7 +76220,7 @@
       </c>
       <c r="B446" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Updated insured's info, and resubmitted</t>
+          <t xml:space="preserve">Updated insured's info</t>
         </is>
       </c>
       <c r="C446" s="3">
@@ -76458,7 +76536,7 @@
       </c>
       <c r="B448" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - Should have been billed to Optum; past the 90-day filing limit</t>
+          <t xml:space="preserve">Should have been billed to Optum; past the 90-day filing limit</t>
         </is>
       </c>
       <c r="C448" s="3">
@@ -76610,7 +76688,7 @@
       </c>
       <c r="B449" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed - A-codes not covered</t>
+          <t xml:space="preserve">ABN signed - A-codes not covered</t>
         </is>
       </c>
       <c r="C449" s="3">
@@ -76762,7 +76840,7 @@
       </c>
       <c r="B450" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Resubmitted to Optum - First submitted to SCAN Health Plan and denied</t>
+          <t xml:space="preserve">Resubmitted to Optum - First submitted to SCAN Health Plan and denied</t>
         </is>
       </c>
       <c r="C450" s="3">
@@ -76916,7 +76994,7 @@
       </c>
       <c r="B451" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removed dx I872, and resubmitted</t>
+          <t xml:space="preserve">Removed dx I872</t>
         </is>
       </c>
       <c r="C451" s="3">
@@ -77068,7 +77146,7 @@
       </c>
       <c r="B452" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Updated insured's info, and resubmitted</t>
+          <t xml:space="preserve">Updated insured's info</t>
         </is>
       </c>
       <c r="C452" s="3">
@@ -77220,7 +77298,7 @@
       </c>
       <c r="B453" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed - No coverage - Policy MP.009.35</t>
+          <t xml:space="preserve">ABN signed - No coverage - Policy MP.009.35</t>
         </is>
       </c>
       <c r="C453" s="3">
@@ -77374,10 +77452,8 @@
       <c r="A454" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B454" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Adjusted balance - No auth on file</t>
-        </is>
+      <c r="B454" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C454" s="3">
         <v>563166125</v>
@@ -77530,7 +77606,7 @@
       </c>
       <c r="B455" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - A-codes not covered under BCBS M2K plan</t>
+          <t xml:space="preserve">A-codes not covered under BCBS M2K plan</t>
         </is>
       </c>
       <c r="C455" s="3">
@@ -77834,7 +77910,7 @@
       </c>
       <c r="B457" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - A-codes not covered under BCBS M2K plan</t>
+          <t xml:space="preserve">A-codes not covered under BCBS M2K plan</t>
         </is>
       </c>
       <c r="C457" s="3">
@@ -77986,8 +78062,10 @@
       <c r="A458" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B458" s="2" t="s">
-        <v>1416</v>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No BH documentation found for those 20+ mins</t>
+        </is>
       </c>
       <c r="C458" s="3">
         <v>560608599</v>
@@ -78144,7 +78222,7 @@
       </c>
       <c r="B459" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed - No coverage - Policy MP.009.35</t>
+          <t xml:space="preserve">ABN signed - No coverage - Policy MP.009.35</t>
         </is>
       </c>
       <c r="C459" s="3">
@@ -78296,7 +78374,7 @@
       </c>
       <c r="B460" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed - Removed referring provider, and resubmitted - Rejected: invalid EDI</t>
+          <t xml:space="preserve">ABN signed - Removed referring provider - Rejected: invalid EDI</t>
         </is>
       </c>
       <c r="C460" s="3">
@@ -78448,7 +78526,7 @@
       </c>
       <c r="B461" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - VA doesn't cover BH</t>
+          <t xml:space="preserve">VA doesn't cover BH</t>
         </is>
       </c>
       <c r="C461" s="3">
@@ -78600,7 +78678,7 @@
       </c>
       <c r="B462" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - GAE (37242) experimental per Aetna policy 0856 (Embolization: Selected Procedures) - If 37242 doesn't pay, neither does 36245 - 99153 not covered due to POS</t>
+          <t xml:space="preserve">GAE (37242) experimental per Aetna policy 0856 (Embolization: Selected Procedures) - If 37242 doesn't pay, neither does 36245 - 99153 not covered due to POS</t>
         </is>
       </c>
       <c r="C462" s="3">
@@ -78772,7 +78850,7 @@
       </c>
       <c r="B463" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - GAE (37242) experimental per Aetna policy 0856 (Embolization: Selected Procedures) - If 37242 doesn't pay, neither does 36245 - 99153 not covered due to POS</t>
+          <t xml:space="preserve">GAE (37242) experimental per Aetna policy 0856 (Embolization: Selected Procedures) - If 37242 doesn't pay, neither does 36245 - 99153 not covered due to POS</t>
         </is>
       </c>
       <c r="C463" s="3">
@@ -78942,8 +79020,10 @@
       <c r="A464" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B464" s="2" t="s">
-        <v>1402</v>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The ABI and TBI are not a standalone study. They're embedded inside the Arterial Duplex Lower Extremity report</t>
+        </is>
       </c>
       <c r="C464" s="3">
         <v>563071059</v>
@@ -79090,10 +79170,8 @@
       <c r="A465" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B465" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Adjusted balance - 75710, 75774, 36245</t>
-        </is>
+      <c r="B465" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C465" s="3">
         <v>558686908</v>
@@ -79255,7 +79333,7 @@
         <v>1114</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>1358</v>
+        <v>1090</v>
       </c>
       <c r="C466" s="3">
         <v>563945778</v>
@@ -79406,7 +79484,7 @@
       </c>
       <c r="B467" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - GAE (37242) experimental per Aetna policy 0856 (Embolization: Selected Procedures) - If 37242 doesn't pay, neither does 36245 - 99153 not covered due to POS</t>
+          <t xml:space="preserve">GAE (37242) experimental per Aetna policy 0856 (Embolization: Selected Procedures) - If 37242 doesn't pay, neither does 36245 - 99153 not covered due to POS</t>
         </is>
       </c>
       <c r="C467" s="3">
@@ -79574,7 +79652,7 @@
       </c>
       <c r="B468" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - Auth only included 63650 - Auth # A273499577</t>
+          <t xml:space="preserve">Auth only included 63650 - Auth # A273499577</t>
         </is>
       </c>
       <c r="C468" s="3">
@@ -80177,7 +80255,7 @@
         <v>1114</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>1329</v>
+        <v>1090</v>
       </c>
       <c r="C472" s="3">
         <v>553677900</v>
@@ -80328,7 +80406,7 @@
       </c>
       <c r="B473" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PAID - Payment on hold</t>
+          <t xml:space="preserve">Payment on hold</t>
         </is>
       </c>
       <c r="C473" s="3">
@@ -80484,7 +80562,7 @@
       </c>
       <c r="B474" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed - Same/similar: L0637 dispensed 01/16/2023 by Arizona Spine and Pain Specialists LLC</t>
+          <t xml:space="preserve">ABN signed - Same/similar: L0637 dispensed 01/16/2023 by Arizona Spine and Pain Specialists LLC</t>
         </is>
       </c>
       <c r="C474" s="3">
@@ -80790,10 +80868,8 @@
       <c r="A476" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B476" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Adjusted balance - No auth on file</t>
-        </is>
+      <c r="B476" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C476" s="3">
         <v>551735634</v>
@@ -81400,10 +81476,8 @@
       <c r="A480" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B480" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Adjusted balance - No auth on file</t>
-        </is>
+      <c r="B480" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C480" s="3">
         <v>553103783</v>
@@ -81554,8 +81628,10 @@
       <c r="A481" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B481" s="2" t="s">
-        <v>1427</v>
+      <c r="B481" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Surgical Dressing: not separately payable if incident to a physician's service - Palmetto GBA July 2026 DMEPOS_Jurisdiction_List article</t>
+        </is>
       </c>
       <c r="C481" s="3">
         <v>556757813</v>
@@ -81708,7 +81784,7 @@
       </c>
       <c r="B482" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed - Same/similar: another L0650 dispensed in the last 5 years</t>
+          <t xml:space="preserve">ABN signed - Same/similar: another L0650 dispensed in the last 5 years</t>
         </is>
       </c>
       <c r="C482" s="3">
@@ -81866,8 +81942,10 @@
       <c r="A483" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B483" s="2" t="s">
-        <v>1429</v>
+      <c r="B483" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only 1 incision performed - 20 units of each were ordered - We dispensed 40 units of each per POD</t>
+        </is>
       </c>
       <c r="C483" s="3">
         <v>556771003</v>
@@ -82018,7 +82096,7 @@
       </c>
       <c r="B484" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed - Same/similar: another L0650 dispensed 04/25/2022 by SonoSpine Arizona LLC</t>
+          <t xml:space="preserve">ABN signed - Same/similar: another L0650 dispensed 04/25/2022 by SonoSpine Arizona LLC</t>
         </is>
       </c>
       <c r="C484" s="3">
@@ -82174,7 +82252,7 @@
       </c>
       <c r="B485" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adjusted balance - No ABN signed - Same/similar: another L0650 dispensed 04/25/2022 by SonoSpine Arizona LLC</t>
+          <t xml:space="preserve">No ABN signed - Same/similar: another L0650 dispensed 04/25/2022 by SonoSpine Arizona LLC</t>
         </is>
       </c>
       <c r="C485" s="3">
@@ -82326,7 +82404,7 @@
       </c>
       <c r="B486" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrected rendering and referring provider, and resubmitted</t>
+          <t xml:space="preserve">Corrected rendering and referring provider</t>
         </is>
       </c>
       <c r="C486" s="3">
@@ -82478,7 +82556,7 @@
       </c>
       <c r="B487" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Added COB info, and crossed over electronically</t>
+          <t xml:space="preserve">Added COB info, and crossed over electronically</t>
         </is>
       </c>
       <c r="C487" s="3">
@@ -82632,7 +82710,7 @@
       </c>
       <c r="B488" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary - Adjusted balance - Plan termed 04/30/2026</t>
+          <t xml:space="preserve">Plan termed 04/30/2026</t>
         </is>
       </c>
       <c r="C488" s="3">
@@ -82784,10 +82862,8 @@
       <c r="A489" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B489" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Secondary - PAID</t>
-        </is>
+      <c r="B489" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C489" s="3">
         <v>560072534</v>
@@ -82942,7 +83018,7 @@
       </c>
       <c r="B490" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shifted to PT - ABN signed - No auth on file</t>
+          <t xml:space="preserve">ABN signed</t>
         </is>
       </c>
       <c r="C490" s="3">
@@ -83098,10 +83174,8 @@
       <c r="A491" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B491" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Adjusted balance - No auth on file</t>
-        </is>
+      <c r="B491" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C491" s="3">
         <v>559739970</v>
@@ -83250,10 +83324,8 @@
       <c r="A492" s="2" t="s">
         <v>1114</v>
       </c>
-      <c r="B492" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Adjusted balance - No auth on file</t>
-        </is>
+      <c r="B492" s="2" t="s">
+        <v>1090</v>
       </c>
       <c r="C492" s="3">
         <v>559735530</v>
@@ -83408,7 +83480,7 @@
       </c>
       <c r="B493" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrected ordering provider, and resubmitted</t>
+          <t xml:space="preserve">Corrected ordering provider</t>
         </is>
       </c>
       <c r="C493" s="3">

--- a/Master Updates.xlsx
+++ b/Master Updates.xlsx
@@ -6993,8 +6993,10 @@
       <c r="AZ2" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA2" s="2" t="s">
-        <v>1090</v>
+      <c r="BA2" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB2" s="2" t="s">
         <v>1090</v>
@@ -9966,8 +9968,10 @@
       <c r="AZ21" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA21" s="2" t="s">
-        <v>1090</v>
+      <c r="BA21" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB21" s="2" t="s">
         <v>1090</v>
@@ -10128,8 +10132,10 @@
       <c r="AZ22" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA22" s="2" t="s">
-        <v>1090</v>
+      <c r="BA22" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB22" s="2" t="s">
         <v>1090</v>
@@ -11068,8 +11074,10 @@
       <c r="AZ28" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA28" s="2" t="s">
-        <v>1090</v>
+      <c r="BA28" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB28" s="2" t="s">
         <v>1090</v>
@@ -11532,8 +11540,10 @@
       <c r="AZ31" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA31" s="2" t="s">
-        <v>1090</v>
+      <c r="BA31" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB31" s="2" t="s">
         <v>1090</v>
@@ -11684,8 +11694,10 @@
       <c r="AZ32" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA32" s="2" t="s">
-        <v>1090</v>
+      <c r="BA32" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB32" s="2" t="s">
         <v>1090</v>
@@ -12150,8 +12162,10 @@
       <c r="AZ35" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA35" s="2" t="s">
-        <v>1090</v>
+      <c r="BA35" s="2" t="inlineStr">
+        <is>
+          <t>Credentialing / out of network</t>
+        </is>
       </c>
       <c r="BB35" s="2" t="s">
         <v>1090</v>
@@ -12308,8 +12322,10 @@
       <c r="AZ36" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA36" s="2" t="s">
-        <v>1090</v>
+      <c r="BA36" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB36" s="2" t="s">
         <v>1497</v>
@@ -12782,8 +12798,10 @@
       <c r="AZ39" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA39" s="2" t="s">
-        <v>1090</v>
+      <c r="BA39" s="2" t="inlineStr">
+        <is>
+          <t>Claim not found</t>
+        </is>
       </c>
       <c r="BB39" s="2" t="s">
         <v>1090</v>
@@ -13878,8 +13896,10 @@
       <c r="AZ46" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA46" s="2" t="s">
-        <v>1090</v>
+      <c r="BA46" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB46" s="2" t="s">
         <v>1497</v>
@@ -14834,8 +14854,10 @@
       <c r="AZ52" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA52" s="2" t="s">
-        <v>1090</v>
+      <c r="BA52" s="2" t="inlineStr">
+        <is>
+          <t>Credentialing / out of network</t>
+        </is>
       </c>
       <c r="BB52" s="2" t="s">
         <v>1090</v>
@@ -16552,8 +16574,10 @@
       <c r="AZ63" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA63" s="2" t="s">
-        <v>1090</v>
+      <c r="BA63" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB63" s="2" t="s">
         <v>1090</v>
@@ -17018,8 +17042,10 @@
       <c r="AZ66" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA66" s="2" t="s">
-        <v>1090</v>
+      <c r="BA66" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB66" s="2" t="s">
         <v>1090</v>
@@ -18897,8 +18923,10 @@
       <c r="AZ78" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA78" s="2" t="s">
-        <v>1090</v>
+      <c r="BA78" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB78" s="2" t="s">
         <v>1090</v>
@@ -19837,8 +19865,10 @@
       <c r="AZ84" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA84" s="2" t="s">
-        <v>1090</v>
+      <c r="BA84" s="2" t="inlineStr">
+        <is>
+          <t>Credentialing / out of network</t>
+        </is>
       </c>
       <c r="BB84" s="2" t="s">
         <v>1090</v>
@@ -23169,8 +23199,10 @@
       <c r="AZ105" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA105" s="2" t="s">
-        <v>1090</v>
+      <c r="BA105" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB105" s="2" t="s">
         <v>1090</v>
@@ -24301,8 +24333,10 @@
       <c r="AZ112" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA112" s="2" t="s">
-        <v>1090</v>
+      <c r="BA112" s="2" t="inlineStr">
+        <is>
+          <t>Medical records needed</t>
+        </is>
       </c>
       <c r="BB112" s="2" t="s">
         <v>1090</v>
@@ -25382,8 +25416,10 @@
       <c r="AZ119" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA119" s="2" t="s">
-        <v>1090</v>
+      <c r="BA119" s="2" t="inlineStr">
+        <is>
+          <t>Duplicate claim</t>
+        </is>
       </c>
       <c r="BB119" s="2" t="s">
         <v>1090</v>
@@ -25540,8 +25576,10 @@
       <c r="AZ120" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA120" s="2" t="s">
-        <v>1090</v>
+      <c r="BA120" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB120" s="2" t="s">
         <v>1090</v>
@@ -26681,8 +26719,10 @@
       <c r="AZ127" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA127" s="2" t="s">
-        <v>1090</v>
+      <c r="BA127" s="2" t="inlineStr">
+        <is>
+          <t>Medical records needed</t>
+        </is>
       </c>
       <c r="BB127" s="2" t="s">
         <v>1090</v>
@@ -32612,8 +32652,10 @@
       <c r="AZ165" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA165" s="2" t="s">
-        <v>1090</v>
+      <c r="BA165" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB165" s="2" t="s">
         <v>1090</v>
@@ -34898,8 +34940,10 @@
       <c r="AZ179" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA179" s="2" t="s">
-        <v>1090</v>
+      <c r="BA179" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB179" s="2" t="s">
         <v>1090</v>
@@ -35056,8 +35100,10 @@
       <c r="AZ180" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA180" s="2" t="s">
-        <v>1090</v>
+      <c r="BA180" s="2" t="inlineStr">
+        <is>
+          <t>Medical records needed</t>
+        </is>
       </c>
       <c r="BB180" s="2" t="s">
         <v>1090</v>
@@ -35988,8 +36034,10 @@
       <c r="AZ186" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA186" s="2" t="s">
-        <v>1090</v>
+      <c r="BA186" s="2" t="inlineStr">
+        <is>
+          <t>Medical records needed</t>
+        </is>
       </c>
       <c r="BB186" s="2" t="s">
         <v>1090</v>
@@ -36458,8 +36506,10 @@
       <c r="AZ189" s="2" t="s">
         <v>1443</v>
       </c>
-      <c r="BA189" s="2" t="s">
-        <v>1643</v>
+      <c r="BA189" s="2" t="inlineStr">
+        <is>
+          <t>Claim not found</t>
+        </is>
       </c>
       <c r="BB189" s="2" t="s">
         <v>1090</v>
@@ -37078,8 +37128,10 @@
       <c r="AZ193" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA193" s="2" t="s">
-        <v>1090</v>
+      <c r="BA193" s="2" t="inlineStr">
+        <is>
+          <t>Claim not found</t>
+        </is>
       </c>
       <c r="BB193" s="2" t="s">
         <v>1090</v>
@@ -41026,8 +41078,10 @@
       <c r="AZ218" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA218" s="2" t="s">
-        <v>1090</v>
+      <c r="BA218" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB218" s="2" t="s">
         <v>1090</v>
@@ -42760,8 +42814,10 @@
       <c r="AZ229" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA229" s="2" t="s">
-        <v>1090</v>
+      <c r="BA229" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB229" s="2" t="s">
         <v>1090</v>
@@ -43560,8 +43616,10 @@
       <c r="AZ234" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA234" s="2" t="s">
-        <v>1090</v>
+      <c r="BA234" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB234" s="2" t="s">
         <v>1090</v>
@@ -43874,8 +43932,10 @@
       <c r="AZ236" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA236" s="2" t="s">
-        <v>1090</v>
+      <c r="BA236" s="2" t="inlineStr">
+        <is>
+          <t>Claim not found</t>
+        </is>
       </c>
       <c r="BB236" s="2" t="s">
         <v>1090</v>
@@ -44208,8 +44268,10 @@
       <c r="AZ238" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA238" s="2" t="s">
-        <v>1090</v>
+      <c r="BA238" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB238" s="2" t="s">
         <v>1090</v>
@@ -44364,8 +44426,10 @@
       <c r="AZ239" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA239" s="2" t="s">
-        <v>1090</v>
+      <c r="BA239" s="2" t="inlineStr">
+        <is>
+          <t>Claim not found</t>
+        </is>
       </c>
       <c r="BB239" s="2" t="s">
         <v>1090</v>
@@ -45170,8 +45234,10 @@
       <c r="AZ244" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA244" s="2" t="s">
-        <v>1090</v>
+      <c r="BA244" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB244" s="2" t="s">
         <v>1090</v>
@@ -45486,8 +45552,10 @@
       <c r="AZ246" s="2" t="s">
         <v>1443</v>
       </c>
-      <c r="BA246" s="2" t="s">
-        <v>1090</v>
+      <c r="BA246" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB246" s="2" t="s">
         <v>1090</v>
@@ -45648,8 +45716,10 @@
       <c r="AZ247" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA247" s="2" t="s">
-        <v>1090</v>
+      <c r="BA247" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB247" s="2" t="s">
         <v>1090</v>
@@ -49590,8 +49660,10 @@
       <c r="AZ272" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA272" s="2" t="s">
-        <v>1090</v>
+      <c r="BA272" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB272" s="2" t="s">
         <v>1090</v>
@@ -50706,8 +50778,10 @@
       <c r="AZ279" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA279" s="2" t="s">
-        <v>1090</v>
+      <c r="BA279" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB279" s="2" t="s">
         <v>1090</v>
@@ -50864,8 +50938,10 @@
       <c r="AZ280" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA280" s="2" t="s">
-        <v>1090</v>
+      <c r="BA280" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB280" s="2" t="s">
         <v>1090</v>
@@ -52588,8 +52664,10 @@
       <c r="AZ291" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA291" s="2" t="s">
-        <v>1090</v>
+      <c r="BA291" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB291" s="2" t="s">
         <v>1090</v>
@@ -53066,8 +53144,10 @@
       <c r="AZ294" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA294" s="2" t="s">
-        <v>1090</v>
+      <c r="BA294" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB294" s="2" t="s">
         <v>1090</v>
@@ -53538,8 +53618,10 @@
       <c r="AZ297" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA297" s="2" t="s">
-        <v>1090</v>
+      <c r="BA297" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB297" s="2" t="s">
         <v>1090</v>
@@ -54170,8 +54252,10 @@
       <c r="AZ301" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA301" s="2" t="s">
-        <v>1090</v>
+      <c r="BA301" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB301" s="2" t="s">
         <v>1090</v>
@@ -54638,8 +54722,10 @@
       <c r="AZ304" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA304" s="2" t="s">
-        <v>1090</v>
+      <c r="BA304" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB304" s="2" t="s">
         <v>1090</v>
@@ -55588,8 +55674,10 @@
       <c r="AZ310" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA310" s="2" t="s">
-        <v>1090</v>
+      <c r="BA310" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB310" s="2" t="s">
         <v>1090</v>
@@ -55742,8 +55830,10 @@
       <c r="AZ311" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA311" s="2" t="s">
-        <v>1090</v>
+      <c r="BA311" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB311" s="2" t="s">
         <v>1090</v>
@@ -58748,8 +58838,10 @@
       <c r="AZ330" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA330" s="2" t="s">
-        <v>1090</v>
+      <c r="BA330" s="2" t="inlineStr">
+        <is>
+          <t>Claim not found</t>
+        </is>
       </c>
       <c r="BB330" s="2" t="s">
         <v>1090</v>
@@ -59830,8 +59922,10 @@
       <c r="AZ337" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA337" s="2" t="s">
-        <v>1090</v>
+      <c r="BA337" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB337" s="2" t="s">
         <v>1497</v>
@@ -61166,8 +61260,10 @@
       <c r="AZ346" s="2" t="s">
         <v>1329</v>
       </c>
-      <c r="BA346" s="2" t="s">
-        <v>1090</v>
+      <c r="BA346" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB346" s="2" t="s">
         <v>1090</v>
@@ -62031,8 +62127,10 @@
       <c r="AZ352" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA352" s="2" t="s">
-        <v>1090</v>
+      <c r="BA352" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB352" s="2" t="s">
         <v>1090</v>
@@ -62723,8 +62821,10 @@
       <c r="AZ357" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA357" s="2" t="s">
-        <v>1090</v>
+      <c r="BA357" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB357" s="2" t="s">
         <v>1090</v>
@@ -64993,8 +65093,10 @@
       <c r="AZ373" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA373" s="2" t="s">
-        <v>1090</v>
+      <c r="BA373" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB373" s="2" t="s">
         <v>1090</v>
@@ -65935,8 +66037,10 @@
       <c r="AZ379" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA379" s="2" t="s">
-        <v>1090</v>
+      <c r="BA379" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB379" s="2" t="s">
         <v>1090</v>
@@ -66897,8 +67001,10 @@
       <c r="AZ385" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA385" s="2" t="s">
-        <v>1090</v>
+      <c r="BA385" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB385" s="2" t="s">
         <v>1090</v>
@@ -67051,8 +67157,10 @@
       <c r="AZ386" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA386" s="2" t="s">
-        <v>1090</v>
+      <c r="BA386" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB386" s="2" t="s">
         <v>1090</v>
@@ -67223,8 +67331,10 @@
       <c r="AZ387" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA387" s="2" t="s">
-        <v>1090</v>
+      <c r="BA387" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB387" s="2" t="s">
         <v>1090</v>
@@ -67395,8 +67505,10 @@
       <c r="AZ388" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA388" s="2" t="s">
-        <v>1090</v>
+      <c r="BA388" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB388" s="2" t="s">
         <v>1090</v>
@@ -67731,8 +67843,10 @@
       <c r="AZ390" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA390" s="2" t="s">
-        <v>1090</v>
+      <c r="BA390" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB390" s="2" t="s">
         <v>1090</v>
@@ -68193,8 +68307,10 @@
       <c r="AZ393" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA393" s="2" t="s">
-        <v>1090</v>
+      <c r="BA393" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB393" s="2" t="s">
         <v>1090</v>
@@ -68351,8 +68467,10 @@
       <c r="AZ394" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA394" s="2" t="s">
-        <v>1090</v>
+      <c r="BA394" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB394" s="2" t="s">
         <v>1090</v>
@@ -68659,8 +68777,10 @@
       <c r="AZ396" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA396" s="2" t="s">
-        <v>1090</v>
+      <c r="BA396" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB396" s="2" t="s">
         <v>1090</v>
@@ -73439,8 +73559,10 @@
       <c r="AZ427" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA427" s="2" t="s">
-        <v>1090</v>
+      <c r="BA427" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB427" s="2" t="s">
         <v>1090</v>
@@ -74517,8 +74639,10 @@
       <c r="AZ434" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA434" s="2" t="s">
-        <v>1090</v>
+      <c r="BA434" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB434" s="2" t="s">
         <v>1090</v>
@@ -75590,8 +75714,10 @@
       <c r="AZ441" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA441" s="2" t="s">
-        <v>1090</v>
+      <c r="BA441" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB441" s="2" t="s">
         <v>1090</v>
@@ -80852,8 +80978,10 @@
       <c r="AZ475" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA475" s="2" t="s">
-        <v>1090</v>
+      <c r="BA475" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB475" s="2" t="s">
         <v>1090</v>
@@ -81154,8 +81282,10 @@
       <c r="AZ477" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA477" s="2" t="s">
-        <v>1090</v>
+      <c r="BA477" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB477" s="2" t="s">
         <v>1090</v>
@@ -81306,8 +81436,10 @@
       <c r="AZ478" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA478" s="2" t="s">
-        <v>1090</v>
+      <c r="BA478" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB478" s="2" t="s">
         <v>1090</v>
@@ -82692,8 +82824,10 @@
       <c r="AZ487" s="2" t="s">
         <v>1443</v>
       </c>
-      <c r="BA487" s="2" t="s">
-        <v>1090</v>
+      <c r="BA487" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB487" s="2" t="s">
         <v>1090</v>
@@ -83000,8 +83134,10 @@
       <c r="AZ489" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA489" s="2" t="s">
-        <v>1090</v>
+      <c r="BA489" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB489" s="2" t="s">
         <v>1090</v>
@@ -83753,8 +83889,10 @@
       <c r="AZ494" s="2" t="s">
         <v>1443</v>
       </c>
-      <c r="BA494" s="2" t="s">
-        <v>1090</v>
+      <c r="BA494" s="2" t="inlineStr">
+        <is>
+          <t>NO DENIAL</t>
+        </is>
       </c>
       <c r="BB494" s="2" t="s">
         <v>1090</v>
@@ -85875,8 +86013,10 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>1643</v>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Claim not found</t>
+        </is>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">

--- a/Master Updates.xlsx
+++ b/Master Updates.xlsx
@@ -66195,8 +66195,10 @@
       <c r="AZ380" s="2" t="s">
         <v>1090</v>
       </c>
-      <c r="BA380" s="2" t="s">
-        <v>1090</v>
+      <c r="BA380" s="2" t="inlineStr">
+        <is>
+          <t>PR deductible/coinsurance</t>
+        </is>
       </c>
       <c r="BB380" s="2" t="s">
         <v>1497</v>
@@ -84031,11 +84033,15 @@
       <c r="B2" t="s">
         <v>1843</v>
       </c>
-      <c r="C2" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1827</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PR deductible/coinsurance</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bill the patient for the deductible/coinsurance/copay amount shown on the EOB.</t>
+        </is>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -84045,11 +84051,15 @@
       <c r="B3" t="s">
         <v>1843</v>
       </c>
-      <c r="C3" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1827</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PR deductible/coinsurance</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bill the patient for the deductible/coinsurance/copay amount shown on the EOB.</t>
+        </is>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -84059,11 +84069,15 @@
       <c r="B4" t="s">
         <v>1843</v>
       </c>
-      <c r="C4" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1827</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PR deductible/coinsurance</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bill the patient for the deductible/coinsurance/copay amount shown on the EOB.</t>
+        </is>
       </c>
       <c r="E4">
         <v>1</v>
@@ -85771,7 +85785,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BABA8923-288C-4E24-811F-D4A4F3011519}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -86027,6 +86041,18 @@
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1499</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PR deductible/coinsurance</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bill the patient for the deductible/coinsurance/copay amount shown on the EOB.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Master Updates.xlsx
+++ b/Master Updates.xlsx
@@ -8080,8 +8080,10 @@
       <c r="BD9" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE9" s="2" t="s">
-        <v>1098</v>
+      <c r="BE9" s="2" t="inlineStr">
+        <is>
+          <t>Get MR from Juan</t>
+        </is>
       </c>
     </row>
     <row r="10" spans="1:57" x14ac:dyDescent="0.25">
@@ -8238,8 +8240,10 @@
       <c r="BD10" s="4">
         <v>46341</v>
       </c>
-      <c r="BE10" s="2" t="s">
-        <v>1461</v>
+      <c r="BE10" s="2" t="inlineStr">
+        <is>
+          <t>Bill PT once full recoup posts</t>
+        </is>
       </c>
     </row>
     <row r="11" spans="1:57" x14ac:dyDescent="0.25">
@@ -9170,8 +9174,10 @@
       <c r="BD16" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE16" s="2" t="s">
-        <v>1461</v>
+      <c r="BE16" s="2" t="inlineStr">
+        <is>
+          <t>Bill PT once full recoup posts</t>
+        </is>
       </c>
     </row>
     <row r="17" spans="1:57" x14ac:dyDescent="0.25">
@@ -9332,8 +9338,10 @@
       <c r="BD17" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE17" s="2" t="s">
-        <v>1818</v>
+      <c r="BE17" s="2" t="inlineStr">
+        <is>
+          <t>Follow up with D - Invalid/missing modifier</t>
+        </is>
       </c>
     </row>
     <row r="18" spans="1:57" x14ac:dyDescent="0.25">
@@ -9494,8 +9502,10 @@
       <c r="BD18" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE18" s="2" t="s">
-        <v>1818</v>
+      <c r="BE18" s="2" t="inlineStr">
+        <is>
+          <t>Follow up with D - Invalid/missing modifier</t>
+        </is>
       </c>
     </row>
     <row r="19" spans="1:57" x14ac:dyDescent="0.25">
@@ -9658,8 +9668,10 @@
       <c r="BD19" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE19" s="2" t="s">
-        <v>1818</v>
+      <c r="BE19" s="2" t="inlineStr">
+        <is>
+          <t>Follow up with D - Adjust, or ask scribe to correct notes</t>
+        </is>
       </c>
     </row>
     <row r="20" spans="1:57" x14ac:dyDescent="0.25">
@@ -9822,8 +9834,10 @@
       <c r="BD20" s="4">
         <v>46310</v>
       </c>
-      <c r="BE20" s="2" t="s">
-        <v>1473</v>
+      <c r="BE20" s="2" t="inlineStr">
+        <is>
+          <t>Follow up with D - Adjust 99204 or change encounter notes (if resubmitting as 99214, bill POS 11 and remove mod 95)</t>
+        </is>
       </c>
     </row>
     <row r="21" spans="1:57" x14ac:dyDescent="0.25">
@@ -9982,8 +9996,10 @@
       <c r="BD21" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE21" s="2" t="s">
-        <v>1474</v>
+      <c r="BE21" s="2" t="inlineStr">
+        <is>
+          <t>Refund overpayment to BCBS</t>
+        </is>
       </c>
     </row>
     <row r="22" spans="1:57" x14ac:dyDescent="0.25">
@@ -10146,8 +10162,10 @@
       <c r="BD22" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE22" s="2" t="s">
-        <v>1474</v>
+      <c r="BE22" s="2" t="inlineStr">
+        <is>
+          <t>Refund overpayment to BCBS</t>
+        </is>
       </c>
     </row>
     <row r="23" spans="1:57" x14ac:dyDescent="0.25">
@@ -10622,8 +10640,10 @@
       <c r="BD25" s="4">
         <v>46171</v>
       </c>
-      <c r="BE25" s="2" t="s">
-        <v>1481</v>
+      <c r="BE25" s="2" t="inlineStr">
+        <is>
+          <t>Confirm secondary received the claim</t>
+        </is>
       </c>
     </row>
     <row r="26" spans="1:57" x14ac:dyDescent="0.25">
@@ -10930,8 +10950,10 @@
       <c r="BD27" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE27" s="2" t="s">
-        <v>1484</v>
+      <c r="BE27" s="2" t="inlineStr">
+        <is>
+          <t>Locate active plan on DOS with Tricare</t>
+        </is>
       </c>
     </row>
     <row r="28" spans="1:57" x14ac:dyDescent="0.25">
@@ -11088,8 +11110,10 @@
       <c r="BD28" s="4">
         <v>46243</v>
       </c>
-      <c r="BE28" s="2" t="s">
-        <v>1485</v>
+      <c r="BE28" s="2" t="inlineStr">
+        <is>
+          <t>Void original claim 547459229</t>
+        </is>
       </c>
     </row>
     <row r="29" spans="1:57" x14ac:dyDescent="0.25">
@@ -11708,8 +11732,10 @@
       <c r="BD32" s="4">
         <v>46107</v>
       </c>
-      <c r="BE32" s="2" t="s">
-        <v>1491</v>
+      <c r="BE32" s="2" t="inlineStr">
+        <is>
+          <t>Void original claim 547855520</t>
+        </is>
       </c>
     </row>
     <row r="33" spans="1:57" x14ac:dyDescent="0.25">
@@ -12654,8 +12680,10 @@
       <c r="BD38" s="4">
         <v>46166</v>
       </c>
-      <c r="BE38" s="2" t="s">
-        <v>1481</v>
+      <c r="BE38" s="2" t="inlineStr">
+        <is>
+          <t>Cross over to secondary once primary payment is posted</t>
+        </is>
       </c>
     </row>
     <row r="39" spans="1:57" x14ac:dyDescent="0.25">
@@ -13124,8 +13152,10 @@
       <c r="BD41" s="4">
         <v>46276</v>
       </c>
-      <c r="BE41" s="2" t="s">
-        <v>1506</v>
+      <c r="BE41" s="2" t="inlineStr">
+        <is>
+          <t>Call PT - Confirm COB questionnaire (IQ) was updated, then ask payer to reprocess</t>
+        </is>
       </c>
     </row>
     <row r="42" spans="1:57" x14ac:dyDescent="0.25">
@@ -16588,8 +16618,10 @@
       <c r="BD63" s="4">
         <v>46298</v>
       </c>
-      <c r="BE63" s="2" t="s">
-        <v>1526</v>
+      <c r="BE63" s="2" t="inlineStr">
+        <is>
+          <t>Follow up on refund/reprocessing ticket</t>
+        </is>
       </c>
     </row>
     <row r="64" spans="1:57" x14ac:dyDescent="0.25">
@@ -18777,8 +18809,10 @@
       <c r="BD77" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE77" s="2" t="s">
-        <v>1540</v>
+      <c r="BE77" s="2" t="inlineStr">
+        <is>
+          <t>Get MR from Juan</t>
+        </is>
       </c>
     </row>
     <row r="78" spans="1:57" x14ac:dyDescent="0.25">
@@ -18937,8 +18971,10 @@
       <c r="BD78" s="4">
         <v>46296</v>
       </c>
-      <c r="BE78" s="2" t="s">
-        <v>1541</v>
+      <c r="BE78" s="2" t="inlineStr">
+        <is>
+          <t>Follow up with posting team - Possible duplicate payment</t>
+        </is>
       </c>
     </row>
     <row r="79" spans="1:57" x14ac:dyDescent="0.25">
@@ -20507,8 +20543,10 @@
       <c r="BD88" s="4">
         <v>46331</v>
       </c>
-      <c r="BE88" s="2" t="s">
-        <v>1548</v>
+      <c r="BE88" s="2" t="inlineStr">
+        <is>
+          <t>Confirm April faxed the appeal</t>
+        </is>
       </c>
     </row>
     <row r="89" spans="1:57" x14ac:dyDescent="0.25">
@@ -20837,8 +20875,10 @@
       <c r="BD90" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE90" s="2" t="s">
-        <v>1551</v>
+      <c r="BE90" s="2" t="inlineStr">
+        <is>
+          <t>Call payer - Bundling denial (auth on file)</t>
+        </is>
       </c>
     </row>
     <row r="91" spans="1:57" x14ac:dyDescent="0.25">
@@ -21469,8 +21509,10 @@
       <c r="BD94" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE94" s="2" t="s">
-        <v>1554</v>
+      <c r="BE94" s="2" t="inlineStr">
+        <is>
+          <t>Bill Preferred Homecare (delegated vendor) - call 800-636-2123 to confirm</t>
+        </is>
       </c>
     </row>
     <row r="95" spans="1:57" x14ac:dyDescent="0.25">
@@ -21627,8 +21669,10 @@
       <c r="BD95" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE95" s="2" t="s">
-        <v>1554</v>
+      <c r="BE95" s="2" t="inlineStr">
+        <is>
+          <t>Bill Preferred Homecare (delegated vendor) - call 800-636-2123 to confirm</t>
+        </is>
       </c>
     </row>
     <row r="96" spans="1:57" x14ac:dyDescent="0.25">
@@ -21943,8 +21987,10 @@
       <c r="BD97" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE97" s="2" t="s">
-        <v>1556</v>
+      <c r="BE97" s="2" t="inlineStr">
+        <is>
+          <t>Follow up with Bri - Dr. Sarkar OON status</t>
+        </is>
       </c>
     </row>
     <row r="98" spans="1:57" x14ac:dyDescent="0.25">
@@ -22745,8 +22791,10 @@
       <c r="BD102" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE102" s="2" t="s">
-        <v>1554</v>
+      <c r="BE102" s="2" t="inlineStr">
+        <is>
+          <t>Bill Preferred Homecare (delegated vendor) - call 800-636-2123 to confirm</t>
+        </is>
       </c>
     </row>
     <row r="103" spans="1:57" x14ac:dyDescent="0.25">
@@ -23059,8 +23107,10 @@
       <c r="BD104" s="4">
         <v>46278</v>
       </c>
-      <c r="BE104" s="2" t="s">
-        <v>1562</v>
+      <c r="BE104" s="2" t="inlineStr">
+        <is>
+          <t>Confirm Linda W. faxed MR</t>
+        </is>
       </c>
     </row>
     <row r="105" spans="1:57" x14ac:dyDescent="0.25">
@@ -23367,8 +23417,10 @@
       <c r="BD106" s="4">
         <v>46306</v>
       </c>
-      <c r="BE106" s="2" t="s">
-        <v>1564</v>
+      <c r="BE106" s="2" t="inlineStr">
+        <is>
+          <t>Follow up with credentialing team - Dr. Sarkar OON status</t>
+        </is>
       </c>
     </row>
     <row r="107" spans="1:57" x14ac:dyDescent="0.25">
@@ -23707,8 +23759,10 @@
       <c r="BD108" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE108" s="2" t="s">
-        <v>1554</v>
+      <c r="BE108" s="2" t="inlineStr">
+        <is>
+          <t>Bill Preferred Homecare (delegated vendor) - call 800-636-2123 to confirm</t>
+        </is>
       </c>
     </row>
     <row r="109" spans="1:57" x14ac:dyDescent="0.25">
@@ -24187,8 +24241,10 @@
       <c r="BD111" s="4">
         <v>46319</v>
       </c>
-      <c r="BE111" s="2" t="s">
-        <v>1567</v>
+      <c r="BE111" s="2" t="inlineStr">
+        <is>
+          <t>Follow up with Tina - PT eligibility on DOS</t>
+        </is>
       </c>
     </row>
     <row r="112" spans="1:57" x14ac:dyDescent="0.25">
@@ -24347,8 +24403,10 @@
       <c r="BD112" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE112" s="2" t="s">
-        <v>1568</v>
+      <c r="BE112" s="2" t="inlineStr">
+        <is>
+          <t>Chat on portal - Ask for PIQ review status</t>
+        </is>
       </c>
     </row>
     <row r="113" spans="1:57" x14ac:dyDescent="0.25">
@@ -25590,8 +25648,10 @@
       <c r="BD120" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE120" s="2" t="s">
-        <v>1571</v>
+      <c r="BE120" s="2" t="inlineStr">
+        <is>
+          <t>Check COB on Noridian - If nothing there, follow up with April</t>
+        </is>
       </c>
     </row>
     <row r="121" spans="1:57" x14ac:dyDescent="0.25">
@@ -25750,8 +25810,10 @@
       <c r="BD121" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE121" s="2" t="s">
-        <v>1554</v>
+      <c r="BE121" s="2" t="inlineStr">
+        <is>
+          <t>Bill Preferred Homecare (delegated vendor) - call 800-636-2123 to confirm</t>
+        </is>
       </c>
     </row>
     <row r="122" spans="1:57" x14ac:dyDescent="0.25">
@@ -25914,8 +25976,10 @@
       <c r="BD122" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE122" s="2" t="s">
-        <v>1572</v>
+      <c r="BE122" s="2" t="inlineStr">
+        <is>
+          <t>Chat on portal - Confirm Anthem received MR</t>
+        </is>
       </c>
     </row>
     <row r="123" spans="1:57" x14ac:dyDescent="0.25">
@@ -26070,8 +26134,10 @@
       <c r="BD123" s="4">
         <v>46331</v>
       </c>
-      <c r="BE123" s="2" t="s">
-        <v>1573</v>
+      <c r="BE123" s="2" t="inlineStr">
+        <is>
+          <t>Follow up with Bri - Rendering OON with AHCCCS</t>
+        </is>
       </c>
     </row>
     <row r="124" spans="1:57" x14ac:dyDescent="0.25">
@@ -26397,8 +26463,10 @@
       <c r="BD125" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE125" s="2" t="s">
-        <v>1577</v>
+      <c r="BE125" s="2" t="inlineStr">
+        <is>
+          <t>Send pending message to Bri</t>
+        </is>
       </c>
     </row>
     <row r="126" spans="1:57" x14ac:dyDescent="0.25">
@@ -29557,8 +29625,10 @@
       <c r="BD145" s="4">
         <v>46275</v>
       </c>
-      <c r="BE145" s="2" t="s">
-        <v>1596</v>
+      <c r="BE145" s="2" t="inlineStr">
+        <is>
+          <t>Get MR request letter</t>
+        </is>
       </c>
     </row>
     <row r="146" spans="1:57" x14ac:dyDescent="0.25">
@@ -33786,8 +33856,10 @@
       <c r="BD172" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE172" s="2" t="s">
-        <v>1623</v>
+      <c r="BE172" s="2" t="inlineStr">
+        <is>
+          <t>Send MR to payer</t>
+        </is>
       </c>
     </row>
     <row r="173" spans="1:57" x14ac:dyDescent="0.25">
@@ -35114,8 +35186,10 @@
       <c r="BD180" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE180" s="2" t="s">
-        <v>1636</v>
+      <c r="BE180" s="2" t="inlineStr">
+        <is>
+          <t>Call payer - Bar code letter (if needed) and denial details</t>
+        </is>
       </c>
     </row>
     <row r="181" spans="1:57" x14ac:dyDescent="0.25">
@@ -36048,8 +36122,10 @@
       <c r="BD186" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE186" s="2" t="s">
-        <v>1636</v>
+      <c r="BE186" s="2" t="inlineStr">
+        <is>
+          <t>Call payer - Bar code letter (if needed) and denial details</t>
+        </is>
       </c>
     </row>
     <row r="187" spans="1:57" x14ac:dyDescent="0.25">
@@ -36360,8 +36436,10 @@
       <c r="BD188" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE188" s="2" t="s">
-        <v>1641</v>
+      <c r="BE188" s="2" t="inlineStr">
+        <is>
+          <t>Check BCBS Alabama portal once access is active</t>
+        </is>
       </c>
     </row>
     <row r="189" spans="1:57" x14ac:dyDescent="0.25">
@@ -36824,8 +36902,10 @@
       <c r="BD191" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE191" s="2" t="s">
-        <v>1645</v>
+      <c r="BE191" s="2" t="inlineStr">
+        <is>
+          <t>Chat on UHC portal - Rendering provider status</t>
+        </is>
       </c>
     </row>
     <row r="192" spans="1:57" x14ac:dyDescent="0.25">
@@ -36982,8 +37062,10 @@
       <c r="BD192" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE192" s="2" t="s">
-        <v>1646</v>
+      <c r="BE192" s="2" t="inlineStr">
+        <is>
+          <t>Call payer - Provider status on DOS</t>
+        </is>
       </c>
     </row>
     <row r="193" spans="1:57" x14ac:dyDescent="0.25">
@@ -38260,8 +38342,10 @@
       <c r="BD200" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE200" s="2" t="s">
-        <v>1656</v>
+      <c r="BE200" s="2" t="inlineStr">
+        <is>
+          <t>Bill Preferred Homecare (delegated vendor) - call 800-636-2123 to confirm</t>
+        </is>
       </c>
     </row>
     <row r="201" spans="1:57" x14ac:dyDescent="0.25">
@@ -38876,8 +38960,10 @@
       <c r="BD204" s="4">
         <v>46314</v>
       </c>
-      <c r="BE204" s="2" t="s">
-        <v>1662</v>
+      <c r="BE204" s="2" t="inlineStr">
+        <is>
+          <t>Follow up on claims inquiry</t>
+        </is>
       </c>
     </row>
     <row r="205" spans="1:57" x14ac:dyDescent="0.25">
@@ -39034,8 +39120,10 @@
       <c r="BD205" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE205" s="2" t="s">
-        <v>1656</v>
+      <c r="BE205" s="2" t="inlineStr">
+        <is>
+          <t>Bill Preferred Homecare (delegated vendor) - call 800-636-2123 to confirm</t>
+        </is>
       </c>
     </row>
     <row r="206" spans="1:57" x14ac:dyDescent="0.25">
@@ -39348,8 +39436,10 @@
       <c r="BD207" s="4">
         <v>46303</v>
       </c>
-      <c r="BE207" s="2" t="s">
-        <v>1666</v>
+      <c r="BE207" s="2" t="inlineStr">
+        <is>
+          <t>Follow up on MR review</t>
+        </is>
       </c>
     </row>
     <row r="208" spans="1:57" x14ac:dyDescent="0.25">
@@ -40132,8 +40222,10 @@
       <c r="BD212" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE212" s="2" t="s">
-        <v>1669</v>
+      <c r="BE212" s="2" t="inlineStr">
+        <is>
+          <t>Call PT - Get current coverage (Aetna termed 03/31/2026)</t>
+        </is>
       </c>
     </row>
     <row r="213" spans="1:57" x14ac:dyDescent="0.25">
@@ -42196,8 +42288,10 @@
       <c r="BD225" s="4">
         <v>46331</v>
       </c>
-      <c r="BE225" s="2" t="s">
-        <v>1635</v>
+      <c r="BE225" s="2" t="inlineStr">
+        <is>
+          <t>Confirm payment is posted</t>
+        </is>
       </c>
     </row>
     <row r="226" spans="1:57" x14ac:dyDescent="0.25">
@@ -42516,8 +42610,10 @@
       <c r="BD227" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE227" s="2" t="s">
-        <v>1680</v>
+      <c r="BE227" s="2" t="inlineStr">
+        <is>
+          <t>Call payer - MUE denial</t>
+        </is>
       </c>
     </row>
     <row r="228" spans="1:57" x14ac:dyDescent="0.25">
@@ -43630,8 +43726,10 @@
       <c r="BD234" s="4">
         <v>46159</v>
       </c>
-      <c r="BE234" s="2" t="s">
-        <v>1685</v>
+      <c r="BE234" s="2" t="inlineStr">
+        <is>
+          <t>Confirm secondary payment is posted</t>
+        </is>
       </c>
     </row>
     <row r="235" spans="1:57" x14ac:dyDescent="0.25">
@@ -44282,8 +44380,10 @@
       <c r="BD238" s="4">
         <v>46290</v>
       </c>
-      <c r="BE238" s="2" t="s">
-        <v>1689</v>
+      <c r="BE238" s="2" t="inlineStr">
+        <is>
+          <t>Refund $211.63 overpayment to secondary</t>
+        </is>
       </c>
     </row>
     <row r="239" spans="1:57" x14ac:dyDescent="0.25">
@@ -44600,8 +44700,10 @@
       <c r="BD240" s="4">
         <v>46331</v>
       </c>
-      <c r="BE240" s="2" t="s">
-        <v>1691</v>
+      <c r="BE240" s="2" t="inlineStr">
+        <is>
+          <t>Follow up on reprocessing</t>
+        </is>
       </c>
     </row>
     <row r="241" spans="1:57" x14ac:dyDescent="0.25">
@@ -45090,8 +45192,10 @@
       <c r="BD243" s="4">
         <v>46289</v>
       </c>
-      <c r="BE243" s="2" t="s">
-        <v>1695</v>
+      <c r="BE243" s="2" t="inlineStr">
+        <is>
+          <t>Correct secondary claim once primary payment is posted</t>
+        </is>
       </c>
     </row>
     <row r="244" spans="1:57" x14ac:dyDescent="0.25">
@@ -45730,8 +45834,10 @@
       <c r="BD247" s="4">
         <v>46331</v>
       </c>
-      <c r="BE247" s="2" t="s">
-        <v>1697</v>
+      <c r="BE247" s="2" t="inlineStr">
+        <is>
+          <t>Confirm secondary received the claim</t>
+        </is>
       </c>
     </row>
     <row r="248" spans="1:57" x14ac:dyDescent="0.25">
@@ -52520,8 +52626,10 @@
       <c r="BD290" s="4">
         <v>46314</v>
       </c>
-      <c r="BE290" s="2" t="s">
-        <v>1719</v>
+      <c r="BE290" s="2" t="inlineStr">
+        <is>
+          <t>Confirm claim was accepted (no rejection)</t>
+        </is>
       </c>
     </row>
     <row r="291" spans="1:57" x14ac:dyDescent="0.25">
@@ -56810,8 +56918,10 @@
       <c r="BD317" s="4">
         <v>46317</v>
       </c>
-      <c r="BE317" s="2" t="s">
-        <v>1327</v>
+      <c r="BE317" s="2" t="inlineStr">
+        <is>
+          <t>Confirm payment is posted</t>
+        </is>
       </c>
     </row>
     <row r="318" spans="1:57" x14ac:dyDescent="0.25">
@@ -57128,8 +57238,10 @@
       <c r="BD319" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE319" s="2" t="s">
-        <v>1730</v>
+      <c r="BE319" s="2" t="inlineStr">
+        <is>
+          <t>Call PT - Get MBI</t>
+        </is>
       </c>
     </row>
     <row r="320" spans="1:57" x14ac:dyDescent="0.25">
@@ -58852,8 +58964,10 @@
       <c r="BD330" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE330" s="2" t="s">
-        <v>1733</v>
+      <c r="BE330" s="2" t="inlineStr">
+        <is>
+          <t>Check Tricare for Life portal once access is active - Confirm crossover went through</t>
+        </is>
       </c>
     </row>
     <row r="331" spans="1:57" x14ac:dyDescent="0.25">
@@ -59008,8 +59122,10 @@
       <c r="BD331" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE331" s="2" t="s">
-        <v>1734</v>
+      <c r="BE331" s="2" t="inlineStr">
+        <is>
+          <t>Call PT - Get new MBI</t>
+        </is>
       </c>
     </row>
     <row r="332" spans="1:57" x14ac:dyDescent="0.25">
@@ -63559,8 +63675,10 @@
       <c r="BD362" s="4" t="s">
         <v>1090</v>
       </c>
-      <c r="BE362" s="2" t="s">
-        <v>1751</v>
+      <c r="BE362" s="2" t="inlineStr">
+        <is>
+          <t>Check payer portal once access is active - Confirm COB (payer says it is secondary)</t>
+        </is>
       </c>
     </row>
     <row r="363" spans="1:57" x14ac:dyDescent="0.25">
@@ -65107,8 +65225,10 @@
       <c r="BD373" s="4">
         <v>46336</v>
       </c>
-      <c r="BE373" s="2" t="s">
-        <v>1635</v>
+      <c r="BE373" s="2" t="inlineStr">
+        <is>
+          <t>Confirm payment is posted</t>
+        </is>
       </c>
     </row>
     <row r="374" spans="1:57" x14ac:dyDescent="0.25">

--- a/Master Updates.xlsx
+++ b/Master Updates.xlsx
@@ -15,11 +15,14 @@
   <sheets>
     <sheet name="All Claims - Draft" sheetId="2" r:id="rId1"/>
     <sheet name="Denial Codes" sheetId="4" r:id="rId2"/>
-    <sheet name="Lists" sheetId="3" r:id="rId3"/>
+    <sheet name="Denial Reason" sheetId="3" r:id="rId3"/>
+    <sheet name="Last and Prior Action" sheetId="4" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Claims - Draft'!$A$1:$BE$494</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Denial Codes'!$A$1:$E$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Denial Codes'!$A$1:$E$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Denial Reason'!$A$1:$C$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Last and Prior Action'!$A$1:$C$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -84119,7 +84122,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FC7D6F-C120-45E5-84CC-94E654397439}">
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="95" customWidth="1"/>
@@ -84129,2053 +84132,3650 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>1839</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>1840</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>1819</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>1841</v>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denial Code (pick or type)</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denial Reason</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What usually fixes it</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claims with this code (all months)</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1842</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1843</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR_1 - Deductible amount</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>PR deductible/coinsurance</t>
+          <t xml:space="preserve">PR deductible/coinsurance</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Bill the patient for the deductible/coinsurance/copay amount shown on the EOB.</t>
+          <t xml:space="preserve">Bill the patient for the deductible/coinsurance/copay amount shown on the EOB.</t>
         </is>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1844</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1843</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR_2 - Coinsurance amount</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>PR deductible/coinsurance</t>
+          <t xml:space="preserve">PR deductible/coinsurance</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bill the patient for the deductible/coinsurance/copay amount shown on the EOB.</t>
+          <t xml:space="preserve">Bill the patient for the deductible/coinsurance/copay amount shown on the EOB.</t>
         </is>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1785</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1843</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR_3 - Co-payment amount</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PR deductible/coinsurance</t>
+          <t xml:space="preserve">PR deductible/coinsurance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bill the patient for the deductible/coinsurance/copay amount shown on the EOB.</t>
+          <t xml:space="preserve">Bill the patient for the deductible/coinsurance/copay amount shown on the EOB.</t>
         </is>
       </c>
       <c r="E4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>1476</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1444</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1824</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_4 - The procedure code is inconsistent with the modifier used, or a required modifier is missing</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modifier issue</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Correct or add the modifier (e.g. NU/RR, KX, RT/LT, 25) and resubmit.</t>
+        </is>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>1521</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1487</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1836</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_5 - The procedure code/type of bill is inconsistent with the place of service</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Place of service</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify the place of service (inpatient/outpatient) and correct the claim.</t>
+        </is>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>1845</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1826</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_6 - The procedure/revenue code is inconsistent with the patient's age</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coding / billing error</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix the code, units, charge or other claim data and resubmit as a corrected claim.</t>
+        </is>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>1846</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1826</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_7 - The procedure/revenue code is inconsistent with the patient's gender</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coding / billing error</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix the code, units, charge or other claim data and resubmit as a corrected claim.</t>
+        </is>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>1847</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1510</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1825</v>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR_8 - The procedure code is inconsistent with the provider type/specialty (taxonomy)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Credentialing / out of network</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check provider enrollment, NPI/TIN and network status; appeal once credentialing is confirmed.</t>
+        </is>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>1848</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1513</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1820</v>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_11 - The diagnosis is inconsistent with the procedure</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diagnosis issue</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review the diagnosis codes and pointers with the chart; correct and resubmit.</t>
+        </is>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>1849</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D11" t="s">
-        <v>1826</v>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_15 - The authorization number is missing, invalid, or does not apply to the billed services or provider</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No authorization</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the portal for an auth; request a retro-auth or file an appeal with the auth number, then resubmit.</t>
+        </is>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>1445</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1458</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1838</v>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_16 - Claim/service lacks information or has submission/billing error(s)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coding / billing error</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix the code, units, charge or other claim data and resubmit as a corrected claim.</t>
+        </is>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>1850</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C13" t="s">
-        <v>1599</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1837</v>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_18 - Exact duplicate claim/service</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duplicate claim</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the status of the original claim; no resubmission needed if it was processed.</t>
+        </is>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>1451</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1450</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1831</v>
-      </c>
-      <c r="E14">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_19 - Work-related injury/illness - liability of the Workers' Compensation carrier</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accident / work related</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get the accident details or workers' comp carrier from the patient; update the claim or bill the WC carrier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OA_22 - This care may be covered by another payer per coordination of benefits</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other insurance / COB</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get the other insurance and primary EOB, update COB with the payer and bill primary first.</t>
+        </is>
+      </c>
+      <c r="E15">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>1851</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1450</v>
-      </c>
-      <c r="D15" t="s">
-        <v>1831</v>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OA_23 - The impact of prior payer(s) adjudication including payments and/or adjustments</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other insurance / COB</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get the other insurance and primary EOB, update COB with the payer and bill primary first.</t>
+        </is>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>1705</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C16" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1830</v>
-      </c>
-      <c r="E16">
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_24 - Charges are covered under a capitation agreement/managed care plan</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wrong payer / vendor</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bill the correct payer, delegated vendor or capitated group/IPA (e.g. Optum Behavioral, Preferred Homecare).</t>
+        </is>
+      </c>
+      <c r="E17">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>1852</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1483</v>
-      </c>
-      <c r="D17" t="s">
-        <v>1832</v>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_26 - Expenses incurred prior to coverage</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility / member ID</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify eligibility; correct the member ID/MBI, name or DOB and resubmit.</t>
+        </is>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>1853</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C18" t="s">
-        <v>1483</v>
-      </c>
-      <c r="D18" t="s">
-        <v>1832</v>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR_26 - Expenses incurred prior to coverage</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility / member ID</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify eligibility; correct the member ID/MBI, name or DOB and resubmit.</t>
+        </is>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>1854</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C19" t="s">
-        <v>1483</v>
-      </c>
-      <c r="D19" t="s">
-        <v>1832</v>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_27 - Expenses incurred after coverage terminated</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility / member ID</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify eligibility; correct the member ID/MBI, name or DOB and resubmit.</t>
+        </is>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>1537</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1536</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1821</v>
-      </c>
-      <c r="E20">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_29 - The time limit for filing has expired</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Timely filing</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Find proof of timely filing (clearinghouse acceptance or earlier submission) and appeal with it; if none, adjust the balance.</t>
+        </is>
+      </c>
+      <c r="E21">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>1855</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C21" t="s">
-        <v>1483</v>
-      </c>
-      <c r="D21" t="s">
-        <v>1832</v>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_31 - Patient cannot be identified as our insured</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility / member ID</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify eligibility; correct the member ID/MBI, name or DOB and resubmit.</t>
+        </is>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>1527</v>
-      </c>
-      <c r="B22" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C22" t="s">
-        <v>1513</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1820</v>
-      </c>
-      <c r="E22">
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_39 - Services denied at the time authorization/pre-certification was requested</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No authorization</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the portal for an auth; request a retro-auth or file an appeal with the auth number, then resubmit.</t>
+        </is>
+      </c>
+      <c r="E23">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>1497</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1499</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1856</v>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_45 - Charge exceeds fee schedule/maximum allowable or contracted/legislated fee arrangement</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO DENIAL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No action needed - the claim paid, or the code is a payment reduction/informational. Review the ERA only if the allowed amount looks wrong.</t>
+        </is>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>1857</v>
-      </c>
-      <c r="B24" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D24" t="s">
-        <v>1827</v>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_49 - Non-covered: routine/preventive exam or a diagnostic/screening procedure done with one</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not covered by plan</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm benefits; bill the patient if an ABN/waiver is on file, otherwise appeal or adjust.</t>
+        </is>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>1464</v>
-      </c>
-      <c r="B25" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C25" t="s">
-        <v>1470</v>
-      </c>
-      <c r="D25" t="s">
-        <v>1828</v>
-      </c>
-      <c r="E25">
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_50 - Non-covered services because this is not deemed a 'medical necessity' by the payer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medical necessity / frequency</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Appeal with medical records and a letter of medical necessity; check LCD/MUE limits.</t>
+        </is>
+      </c>
+      <c r="E26">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>1809</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D26" t="s">
-        <v>1827</v>
-      </c>
-      <c r="E26">
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_55 - Procedure/treatment/drug is deemed experimental/investigational by the payer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not covered by plan</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm benefits; bill the patient if an ABN/waiver is on file, otherwise appeal or adjust.</t>
+        </is>
+      </c>
+      <c r="E27">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>1858</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1499</v>
-      </c>
-      <c r="D27" t="s">
-        <v>1856</v>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_59 - Processed based on multiple or concurrent procedure rules</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO DENIAL</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No action needed - the claim paid, or the code is a payment reduction/informational. Review the ERA only if the allowed amount looks wrong.</t>
+        </is>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>1789</v>
-      </c>
-      <c r="B28" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C28" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D28" t="s">
-        <v>1827</v>
-      </c>
-      <c r="E28">
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_96 - Non-covered charge(s)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not covered by plan</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm benefits; bill the patient if an ABN/waiver is on file, otherwise appeal or adjust.</t>
+        </is>
+      </c>
+      <c r="E29">
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>1465</v>
-      </c>
-      <c r="B29" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C29" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D29" t="s">
-        <v>1827</v>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR_96 - Non-covered charge(s)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not covered by plan</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm benefits; bill the patient if an ABN/waiver is on file, otherwise appeal or adjust.</t>
+        </is>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>1457</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D30" t="s">
-        <v>1823</v>
-      </c>
-      <c r="E30">
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_97 - The benefit for this service is included in the payment/allowance for another service/procedure already adjudicated</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bundled / NCCI edit</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the NCCI pair; if the service was distinct, add 59/XU (or XS) and resubmit; otherwise adjust.</t>
+        </is>
+      </c>
+      <c r="E31">
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>1788</v>
-      </c>
-      <c r="B31" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C31" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D31" t="s">
-        <v>1823</v>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PI_97 - The benefit for this service is included in the payment/allowance for another service/procedure that has already been adjudicated</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bundled / NCCI edit</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the NCCI pair; if the service was distinct, add 59/XU (or XS) and resubmit; otherwise adjust.</t>
+        </is>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>1859</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C32" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D32" t="s">
-        <v>1826</v>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_107 - The related or qualifying claim/service was not identified on this claim</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coding / billing error</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix the code, units, charge or other claim data and resubmit as a corrected claim.</t>
+        </is>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>1736</v>
-      </c>
-      <c r="B33" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C33" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D33" t="s">
-        <v>1830</v>
-      </c>
-      <c r="E33">
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_109 - Claim/service not covered by this payer/contractor - send to the correct payer/contractor</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wrong payer / vendor</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bill the correct payer, delegated vendor or capitated group/IPA (e.g. Optum Behavioral, Preferred Homecare).</t>
+        </is>
+      </c>
+      <c r="E34">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>1860</v>
-      </c>
-      <c r="B34" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C34" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D34" t="s">
-        <v>1827</v>
-      </c>
-      <c r="E34">
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_119 - Benefit maximum for this time period or occurrence has been reached</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not covered by plan</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm benefits; bill the patient if an ABN/waiver is on file, otherwise appeal or adjust.</t>
+        </is>
+      </c>
+      <c r="E35">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>1861</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D35" t="s">
-        <v>1826</v>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR_119 - Benefit maximum for this time period or occurrence has been reached</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not covered by plan</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm benefits; bill the patient if an ABN/waiver is on file, otherwise appeal or adjust.</t>
+        </is>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>1862</v>
-      </c>
-      <c r="B36" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1483</v>
-      </c>
-      <c r="D36" t="s">
-        <v>1832</v>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_129 - Prior processing information appears incorrect</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coding / billing error</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix the code, units, charge or other claim data and resubmit as a corrected claim.</t>
+        </is>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>1863</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1499</v>
-      </c>
-      <c r="D37" t="s">
-        <v>1856</v>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_131 - Claim specific negotiated discount</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO DENIAL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No action needed - the claim paid, or the code is a payment reduction/informational. Review the ERA only if the allowed amount looks wrong.</t>
+        </is>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>1588</v>
-      </c>
-      <c r="B38" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C38" t="s">
-        <v>1510</v>
-      </c>
-      <c r="D38" t="s">
-        <v>1825</v>
-      </c>
-      <c r="E38">
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_140 - Patient/insured health identification number and name do not match</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility / member ID</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify eligibility; correct the member ID/MBI, name or DOB and resubmit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_144 - Incentive adjustment, e.g. preferred product/service</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO DENIAL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No action needed - the claim paid, or the code is a payment reduction/informational. Review the ERA only if the allowed amount looks wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_146 - Diagnosis was invalid for the date(s) of service reported</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diagnosis issue</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review the diagnosis codes and pointers with the chart; correct and resubmit.</t>
+        </is>
+      </c>
+      <c r="E41">
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>1552</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C39" t="s">
-        <v>1470</v>
-      </c>
-      <c r="D39" t="s">
-        <v>1828</v>
-      </c>
-      <c r="E39">
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_150 - Payer deems the information submitted does not support this level of service</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medical necessity / frequency</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Appeal with medical records and a letter of medical necessity; check LCD/MUE limits.</t>
+        </is>
+      </c>
+      <c r="E42">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>1738</v>
-      </c>
-      <c r="B40" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C40" t="s">
-        <v>1470</v>
-      </c>
-      <c r="D40" t="s">
-        <v>1828</v>
-      </c>
-      <c r="E40">
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_151 - Payer deems the information submitted does not support this many/frequency of services</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medical necessity / frequency</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Appeal with medical records and a letter of medical necessity; check LCD/MUE limits.</t>
+        </is>
+      </c>
+      <c r="E43">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>1622</v>
-      </c>
-      <c r="B41" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C41" t="s">
-        <v>1452</v>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_164 - Attachment/other documentation referenced on the claim was not received in a timely fashion</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medical records needed</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Upload the MR on the payer portal, note the PIQ/reference number and set a review date.</t>
+        </is>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>1815</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C42" t="s">
-        <v>1483</v>
-      </c>
-      <c r="D42" t="s">
-        <v>1832</v>
-      </c>
-      <c r="E42">
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_166 - Submitted after this payer's responsibility for processing claims under this plan ended</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility / member ID</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify eligibility; correct the member ID/MBI, name or DOB and resubmit.</t>
+        </is>
+      </c>
+      <c r="E45">
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>1864</v>
-      </c>
-      <c r="B43" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C43" t="s">
-        <v>1510</v>
-      </c>
-      <c r="D43" t="s">
-        <v>1825</v>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_167 - This (these) diagnosis(es) is (are) not covered</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diagnosis issue</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review the diagnosis codes and pointers with the chart; correct and resubmit.</t>
+        </is>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>1865</v>
-      </c>
-      <c r="B44" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C44" t="s">
-        <v>1447</v>
-      </c>
-      <c r="D44" t="s">
-        <v>1833</v>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_170 - Payment is denied when performed/billed by this type of provider</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Credentialing / out of network</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check provider enrollment, NPI/TIN and network status; appeal once credentialing is confirmed.</t>
+        </is>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>1866</v>
-      </c>
-      <c r="B45" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C45" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D45" t="s">
-        <v>1826</v>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_181 - Procedure code was invalid on the date of service</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coding / billing error</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix the code, units, charge or other claim data and resubmit as a corrected claim.</t>
+        </is>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>1867</v>
-      </c>
-      <c r="B46" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C46" t="s">
-        <v>1444</v>
-      </c>
-      <c r="D46" t="s">
-        <v>1824</v>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_182 - Procedure modifier was invalid on the date of service</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modifier issue</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Correct or add the modifier (e.g. NU/RR, KX, RT/LT, 25) and resubmit.</t>
+        </is>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>1467</v>
-      </c>
-      <c r="B47" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C47" t="s">
-        <v>1466</v>
-      </c>
-      <c r="D47" t="s">
-        <v>1834</v>
-      </c>
-      <c r="E47">
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_183 - The referring provider is not eligible to refer the service billed</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referral / referring provider</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get a valid referral or correct the referring provider, then resubmit.</t>
+        </is>
+      </c>
+      <c r="E50">
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>1868</v>
-      </c>
-      <c r="B48" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C48" t="s">
-        <v>1447</v>
-      </c>
-      <c r="D48" t="s">
-        <v>1833</v>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_185 - The rendering provider is not eligible to perform the service billed</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Credentialing / out of network</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check provider enrollment, NPI/TIN and network status; appeal once credentialing is confirmed.</t>
+        </is>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>1869</v>
-      </c>
-      <c r="B49" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C49" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D49" t="s">
-        <v>1826</v>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_189 - 'Not otherwise classified' or 'unlisted' procedure code billed when a specific code exists</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coding / billing error</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix the code, units, charge or other claim data and resubmit as a corrected claim.</t>
+        </is>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>1512</v>
-      </c>
-      <c r="B50" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C50" t="s">
-        <v>1513</v>
-      </c>
-      <c r="D50" t="s">
-        <v>1820</v>
-      </c>
-      <c r="E50">
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_197 - Precertification/authorization/notification/pre-treatment absent</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No authorization</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the portal for an auth; request a retro-auth or file an appeal with the auth number, then resubmit.</t>
+        </is>
+      </c>
+      <c r="E53">
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>1798</v>
-      </c>
-      <c r="B51" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C51" t="s">
-        <v>1513</v>
-      </c>
-      <c r="D51" t="s">
-        <v>1820</v>
-      </c>
-      <c r="E51">
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_198 - Precertification/notification/authorization/pre-treatment exceeded</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No authorization</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the portal for an auth; request a retro-auth or file an appeal with the auth number, then resubmit.</t>
+        </is>
+      </c>
+      <c r="E54">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>1870</v>
-      </c>
-      <c r="B52" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C52" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D52" t="s">
-        <v>1826</v>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_199 - Revenue code and procedure code do not match</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coding / billing error</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix the code, units, charge or other claim data and resubmit as a corrected claim.</t>
+        </is>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>1648</v>
-      </c>
-      <c r="B53" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C53" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D53" t="s">
-        <v>1827</v>
-      </c>
-      <c r="E53">
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR_204 - This service/equipment/drug is not covered under the patient's current benefit plan</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not covered by plan</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm benefits; bill the patient if an ABN/waiver is on file, otherwise appeal or adjust.</t>
+        </is>
+      </c>
+      <c r="E56">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>1871</v>
-      </c>
-      <c r="B54" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C54" t="s">
-        <v>1452</v>
-      </c>
-      <c r="D54" t="s">
-        <v>1822</v>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_226 - Information requested from the billing/rendering provider was not provided, not timely or incomplete</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medical records needed</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Upload the MR on the payer portal, note the PIQ/reference number and set a review date.</t>
+        </is>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>1872</v>
-      </c>
-      <c r="B55" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C55" t="s">
-        <v>1599</v>
-      </c>
-      <c r="D55" t="s">
-        <v>1837</v>
-      </c>
-      <c r="E55">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>1783</v>
-      </c>
-      <c r="B56" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C56" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D56" t="s">
-        <v>1823</v>
-      </c>
-      <c r="E56">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>1873</v>
-      </c>
-      <c r="B57" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C57" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D57" t="s">
-        <v>1823</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>1874</v>
-      </c>
-      <c r="B58" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C58" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D58" t="s">
-        <v>1823</v>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR_227 - Information requested from the patient/insured/responsible party was not provided or was incomplete</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accident / work related</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get the accident details or workers' comp carrier from the patient; update the claim or bill the WC carrier.</t>
+        </is>
       </c>
       <c r="E58">
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>1875</v>
-      </c>
-      <c r="B59" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C59" t="s">
-        <v>1447</v>
-      </c>
-      <c r="D59" t="s">
-        <v>1833</v>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_231 - Mutually exclusive procedures cannot be done in the same day/setting</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bundled / NCCI edit</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the NCCI pair; if the service was distinct, add 59/XU (or XS) and resubmit; otherwise adjust.</t>
+        </is>
+      </c>
+      <c r="E59">
+        <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>1876</v>
-      </c>
-      <c r="B60" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C60" t="s">
-        <v>1466</v>
-      </c>
-      <c r="D60" t="s">
-        <v>1834</v>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_234 - This procedure is not paid separately</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bundled / NCCI edit</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the NCCI pair; if the service was distinct, add 59/XU (or XS) and resubmit; otherwise adjust.</t>
+        </is>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>1493</v>
-      </c>
-      <c r="B61" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C61" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D61" t="s">
-        <v>1826</v>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_236 - Procedure or procedure/modifier combination not compatible with another procedure on the same day (NCCI)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bundled / NCCI edit</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the NCCI pair; if the service was distinct, add 59/XU (or XS) and resubmit; otherwise adjust.</t>
+        </is>
       </c>
       <c r="E61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_242 - Services not provided by network/primary care providers</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Credentialing / out of network</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check provider enrollment, NPI/TIN and network status; appeal once credentialing is confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_243 - Services not authorized by network/primary care providers</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referral / referring provider</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get a valid referral or correct the referring provider, then resubmit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OA_246 - This non-payable code is for required reporting only</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coding / billing error</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix the code, units, charge or other claim data and resubmit as a corrected claim.</t>
+        </is>
+      </c>
+      <c r="E64">
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>1877</v>
-      </c>
-      <c r="B62" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C62" t="s">
-        <v>1452</v>
-      </c>
-      <c r="D62" t="s">
-        <v>1822</v>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_251 - The attachment/other documentation received was incomplete or deficient</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medical records needed</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Upload the MR on the payer portal, note the PIQ/reference number and set a review date.</t>
+        </is>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>1453</v>
-      </c>
-      <c r="B63" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C63" t="s">
-        <v>1452</v>
-      </c>
-      <c r="D63" t="s">
-        <v>1822</v>
-      </c>
-      <c r="E63">
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_252 - An attachment/other documentation is required to adjudicate this claim/service</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medical records needed</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Upload the MR on the payer portal, note the PIQ/reference number and set a review date.</t>
+        </is>
+      </c>
+      <c r="E66">
         <v>42</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>1878</v>
-      </c>
-      <c r="B64" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C64" t="s">
-        <v>1499</v>
-      </c>
-      <c r="D64" t="s">
-        <v>1856</v>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_253 - Sequestration - reduction in federal payment</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO DENIAL</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No action needed - the claim paid, or the code is a payment reduction/informational. Review the ERA only if the allowed amount looks wrong.</t>
+        </is>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>1784</v>
-      </c>
-      <c r="B65" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C65" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D65" t="s">
-        <v>1827</v>
-      </c>
-      <c r="E65">
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_273 - Coverage/program guidelines were exceeded</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not covered by plan</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm benefits; bill the patient if an ABN/waiver is on file, otherwise appeal or adjust.</t>
+        </is>
+      </c>
+      <c r="E68">
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>1879</v>
-      </c>
-      <c r="B66" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C66" t="s">
-        <v>1513</v>
-      </c>
-      <c r="D66" t="s">
-        <v>1820</v>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_284 - Precertification/authorization number may be valid but does not apply to the billed services</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No authorization</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the portal for an auth; request a retro-auth or file an appeal with the auth number, then resubmit.</t>
+        </is>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>1583</v>
-      </c>
-      <c r="B67" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C67" t="s">
-        <v>1466</v>
-      </c>
-      <c r="D67" t="s">
-        <v>1834</v>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_288 - Referral absent</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referral / referring provider</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get a valid referral or correct the referring provider, then resubmit.</t>
+        </is>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>1807</v>
-      </c>
-      <c r="B68" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C68" t="s">
-        <v>1499</v>
-      </c>
-      <c r="D68" t="s">
-        <v>1856</v>
-      </c>
-      <c r="E68">
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_A1 - Claim/service denied</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usually informational or a payment reduction rather than a denial; review the ERA if the balance looks wrong.</t>
+        </is>
+      </c>
+      <c r="E71">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>1524</v>
-      </c>
-      <c r="B69" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C69" t="s">
-        <v>1447</v>
-      </c>
-      <c r="D69" t="s">
-        <v>1833</v>
-      </c>
-      <c r="E69">
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_B7 - This provider was not certified/eligible to be paid for this procedure/service on this date of service</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Credentialing / out of network</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check provider enrollment, NPI/TIN and network status; appeal once credentialing is confirmed.</t>
+        </is>
+      </c>
+      <c r="E72">
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>1880</v>
-      </c>
-      <c r="B70" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C70" t="s">
-        <v>1483</v>
-      </c>
-      <c r="D70" t="s">
-        <v>1832</v>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_B9 - Patient is enrolled in a hospice</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility / member ID</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify eligibility; correct the member ID/MBI, name or DOB and resubmit.</t>
+        </is>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>1881</v>
-      </c>
-      <c r="B71" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C71" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D71" t="s">
-        <v>1823</v>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_B10 - Allowed amount reduced because a component of the basic procedure/test was paid</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bundled / NCCI edit</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the NCCI pair; if the service was distinct, add 59/XU (or XS) and resubmit; otherwise adjust.</t>
+        </is>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>1793</v>
-      </c>
-      <c r="B72" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C72" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D72" t="s">
-        <v>1830</v>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_B11 - The claim/service has been transferred to the proper payer/processor for processing</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wrong payer / vendor</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bill the correct payer, delegated vendor or capitated group/IPA (e.g. Optum Behavioral, Preferred Homecare).</t>
+        </is>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>1549</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C73" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D73" t="s">
-        <v>1823</v>
-      </c>
-      <c r="E73">
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_B15 - This service/procedure requires that a qualifying service/procedure be received and covered</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bundled / NCCI edit</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the NCCI pair; if the service was distinct, add 59/XU (or XS) and resubmit; otherwise adjust.</t>
+        </is>
+      </c>
+      <c r="E76">
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>1882</v>
-      </c>
-      <c r="B74" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C74" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D74" t="s">
-        <v>1826</v>
-      </c>
-      <c r="E74">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>1883</v>
-      </c>
-      <c r="B75" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C75" t="s">
-        <v>1499</v>
-      </c>
-      <c r="D75" t="s">
-        <v>1856</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>1884</v>
-      </c>
-      <c r="B76" t="s">
-        <v>1843</v>
-      </c>
-      <c r="C76" t="s">
-        <v>1599</v>
-      </c>
-      <c r="D76" t="s">
-        <v>1837</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>1775</v>
-      </c>
-      <c r="B77" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C77" t="s">
-        <v>1487</v>
-      </c>
-      <c r="D77" t="s">
-        <v>1836</v>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_B16 - 'New patient' qualifications were not met</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coding / billing error</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix the code, units, charge or other claim data and resubmit as a corrected claim.</t>
+        </is>
       </c>
       <c r="E77">
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>1813</v>
-      </c>
-      <c r="B78" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C78" t="s">
-        <v>1778</v>
-      </c>
-      <c r="D78" t="s">
-        <v>1835</v>
-      </c>
-      <c r="E78">
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_B20 - Procedure/service was partially or fully furnished by another provider</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Usually informational or a payment reduction rather than a denial; review the ERA if the balance looks wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_P12 - Workers' compensation jurisdictional fee schedule adjustment</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accident / work related</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get the accident details or workers' comp carrier from the patient; update the claim or bill the WC carrier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M2 - Not paid separately when the patient is an inpatient</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Place of service</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify the place of service (inpatient/outpatient) and correct the claim.</t>
+        </is>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M3 - Equipment is the same or similar to equipment already being used</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same or similar equipment (DME)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm the prior supplier and date; if an ABN was signed, shift to the patient, otherwise adjust.</t>
+        </is>
+      </c>
+      <c r="E81">
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>1607</v>
-      </c>
-      <c r="B79" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C79" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D79" t="s">
-        <v>1823</v>
-      </c>
-      <c r="E79">
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M15 - Separately billed services/tests have been bundled as components of the same procedure</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bundled / NCCI edit</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the NCCI pair; if the service was distinct, add 59/XU (or XS) and resubmit; otherwise adjust.</t>
+        </is>
+      </c>
+      <c r="E82">
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>1886</v>
-      </c>
-      <c r="B80" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C80" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D80" t="s">
-        <v>1826</v>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M20 - Missing/incomplete/invalid HCPCS</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coding / billing error</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix the code, units, charge or other claim data and resubmit as a corrected claim.</t>
+        </is>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>1494</v>
-      </c>
-      <c r="B81" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C81" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D81" t="s">
-        <v>1826</v>
-      </c>
-      <c r="E81">
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M50 - Missing/incomplete/invalid revenue code(s)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coding / billing error</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix the code, units, charge or other claim data and resubmit as a corrected claim.</t>
+        </is>
+      </c>
+      <c r="E84">
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>1609</v>
-      </c>
-      <c r="B82" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C82" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D82" t="s">
-        <v>1826</v>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M51 - Missing/incomplete/invalid procedure code(s)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coding / billing error</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix the code, units, charge or other claim data and resubmit as a corrected claim.</t>
+        </is>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>1547</v>
-      </c>
-      <c r="B83" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C83" t="s">
-        <v>1510</v>
-      </c>
-      <c r="D83" t="s">
-        <v>1825</v>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M76 - Missing/incomplete/invalid diagnosis or condition</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diagnosis issue</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review the diagnosis codes and pointers with the chart; correct and resubmit.</t>
+        </is>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>1887</v>
-      </c>
-      <c r="B84" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C84" t="s">
-        <v>1487</v>
-      </c>
-      <c r="D84" t="s">
-        <v>1836</v>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M77 - Missing/incomplete/invalid/inappropriate place of service</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Place of service</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify the place of service (inpatient/outpatient) and correct the claim.</t>
+        </is>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>1888</v>
-      </c>
-      <c r="B85" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C85" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D85" t="s">
-        <v>1823</v>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M80 - Not covered when performed during the same session/date as a previously processed service for the patient</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bundled / NCCI edit</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the NCCI pair; if the service was distinct, add 59/XU (or XS) and resubmit; otherwise adjust.</t>
+        </is>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>1889</v>
-      </c>
-      <c r="B86" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C86" t="s">
-        <v>1470</v>
-      </c>
-      <c r="D86" t="s">
-        <v>1828</v>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M86 - Service denied because payment already made for same/similar procedure within set time frame</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medical necessity / frequency</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Appeal with medical records and a letter of medical necessity; check LCD/MUE limits.</t>
+        </is>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>1681</v>
-      </c>
-      <c r="B87" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C87" t="s">
-        <v>1450</v>
-      </c>
-      <c r="D87" t="s">
-        <v>1831</v>
-      </c>
-      <c r="E87">
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MA04 - Secondary payment cannot be considered without the identity of or payment information from the primary payer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other insurance / COB</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get the other insurance and primary EOB, update COB with the payer and bill primary first.</t>
+        </is>
+      </c>
+      <c r="E90">
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>1890</v>
-      </c>
-      <c r="B88" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C88" t="s">
-        <v>1450</v>
-      </c>
-      <c r="D88" t="s">
-        <v>1831</v>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MA18 - Alert: the claim information is also being forwarded to the patient's supplemental insurer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other insurance / COB</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get the other insurance and primary EOB, update COB with the payer and bill primary first.</t>
+        </is>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>1891</v>
-      </c>
-      <c r="B89" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C89" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D89" t="s">
-        <v>1826</v>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MA130 - Claim contains incomplete and/or invalid information; no appeal rights because the claim is unprocessable</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coding / billing error</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix the code, units, charge or other claim data and resubmit as a corrected claim.</t>
+        </is>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B90" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C90" t="s">
-        <v>1450</v>
-      </c>
-      <c r="D90" t="s">
-        <v>1831</v>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N4 - Missing/incomplete/invalid prior insurance carrier EOB</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other insurance / COB</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get the other insurance and primary EOB, update COB with the payer and bill primary first.</t>
+        </is>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>1893</v>
-      </c>
-      <c r="B91" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C91" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D91" t="s">
-        <v>1823</v>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N19 - Procedure code incidental to primary procedure</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bundled / NCCI edit</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the NCCI pair; if the service was distinct, add 59/XU (or XS) and resubmit; otherwise adjust.</t>
+        </is>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>1894</v>
-      </c>
-      <c r="B92" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C92" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D92" t="s">
-        <v>1823</v>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N20 - Service not payable with other service rendered on the same date</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bundled / NCCI edit</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the NCCI pair; if the service was distinct, add 59/XU (or XS) and resubmit; otherwise adjust.</t>
+        </is>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>1895</v>
-      </c>
-      <c r="B93" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C93" t="s">
-        <v>1483</v>
-      </c>
-      <c r="D93" t="s">
-        <v>1832</v>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N30 - Patient ineligible for this service</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility / member ID</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify eligibility; correct the member ID/MBI, name or DOB and resubmit.</t>
+        </is>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>1896</v>
-      </c>
-      <c r="B94" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C94" t="s">
-        <v>1492</v>
-      </c>
-      <c r="D94" t="s">
-        <v>1826</v>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N56 - Procedure code billed is not correct/valid for the services billed or the date of service billed</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coding / billing error</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix the code, units, charge or other claim data and resubmit as a corrected claim.</t>
+        </is>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>1714</v>
-      </c>
-      <c r="B95" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C95" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D95" t="s">
-        <v>1830</v>
-      </c>
-      <c r="E95">
-        <v>1</v>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N88 - Alert: Payment made conditionally - PT is under a Home Health (HHA) episode of care; payment may be recouped</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bundled / NCCI edit</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check whether the PT had an active HHA episode on the DOS; if so, expect a recoup and bill the HHA or the PT per ABN.</t>
+        </is>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>1897</v>
-      </c>
-      <c r="B96" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C96" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D96" t="s">
-        <v>1827</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>1898</v>
-      </c>
-      <c r="B97" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C97" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D97" t="s">
-        <v>1827</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>1899</v>
-      </c>
-      <c r="B98" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C98" t="s">
-        <v>1452</v>
-      </c>
-      <c r="D98" t="s">
-        <v>1822</v>
-      </c>
-      <c r="E98">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>1900</v>
-      </c>
-      <c r="B99" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C99" t="s">
-        <v>1599</v>
-      </c>
-      <c r="D99" t="s">
-        <v>1837</v>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N104 - This claim/service is not payable under our claims jurisdiction area</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wrong payer / vendor</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bill the correct payer, delegated vendor or capitated group/IPA (e.g. Optum Behavioral, Preferred Homecare).</t>
+        </is>
       </c>
       <c r="E99">
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>1655</v>
-      </c>
-      <c r="B100" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C100" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D100" t="s">
-        <v>1827</v>
-      </c>
-      <c r="E100">
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N115 - This decision was based on a Local Coverage Determination (LCD)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not covered by plan</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm benefits; bill the patient if an ABN/waiver is on file, otherwise appeal or adjust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N130 - Consult plan benefit documents/guidelines for information about restrictions for this service</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not covered by plan</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm benefits; bill the patient if an ABN/waiver is on file, otherwise appeal or adjust.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N163 - Medical record does not support code billed per the code definition</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medical records needed</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Upload the MR on the payer portal, note the PIQ/reference number and set a review date.</t>
+        </is>
+      </c>
+      <c r="E102">
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>1672</v>
-      </c>
-      <c r="B101" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C101" t="s">
-        <v>1450</v>
-      </c>
-      <c r="D101" t="s">
-        <v>1831</v>
-      </c>
-      <c r="E101">
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N179 - Additional information has been requested from the member</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accident / work related</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get the accident details or workers' comp carrier from the patient; update the claim or bill the WC carrier.</t>
+        </is>
+      </c>
+      <c r="E103">
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>1901</v>
-      </c>
-      <c r="B102" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C102" t="s">
-        <v>1466</v>
-      </c>
-      <c r="D102" t="s">
-        <v>1834</v>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N216 - We do not offer coverage for this type of service or the patient is not enrolled in this portion of our benefit package</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not covered by plan</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm benefits; bill the patient if an ABN/waiver is on file, otherwise appeal or adjust.</t>
+        </is>
+      </c>
+      <c r="E104">
+        <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>1448</v>
-      </c>
-      <c r="B103" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C103" t="s">
-        <v>1447</v>
-      </c>
-      <c r="D103" t="s">
-        <v>1833</v>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N245 - Incomplete/invalid plan information for other insurance</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other insurance / COB</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get the other insurance and primary EOB, update COB with the payer and bill primary first.</t>
+        </is>
+      </c>
+      <c r="E105">
+        <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>1718</v>
-      </c>
-      <c r="B104" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C104" t="s">
-        <v>1483</v>
-      </c>
-      <c r="D104" t="s">
-        <v>1832</v>
-      </c>
-      <c r="E104">
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N257 - Missing/incomplete/invalid billing provider/supplier primary identifier</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coding / billing error</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix the code, units, charge or other claim data and resubmit as a corrected claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N286 - Missing/incomplete/invalid referring provider primary identifier</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referral / referring provider</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get a valid referral or correct the referring provider, then resubmit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N290 - Missing/incomplete/invalid rendering provider primary identifier</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Credentialing / out of network</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check provider enrollment, NPI/TIN and network status; appeal once credentialing is confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N314 - Missing/incomplete/invalid diagnosis date</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diagnosis issue</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review the diagnosis codes and pointers with the chart; correct and resubmit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N382 - Missing/incomplete/invalid patient identifier</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility / member ID</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify eligibility; correct the member ID/MBI, name or DOB and resubmit.</t>
+        </is>
+      </c>
+      <c r="E110">
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>1902</v>
-      </c>
-      <c r="B105" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C105" t="s">
-        <v>1563</v>
-      </c>
-      <c r="D105" t="s">
-        <v>1827</v>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N386 - This decision was based on a National Coverage Determination (NCD)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not covered by plan</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm benefits; bill the patient if an ABN/waiver is on file, otherwise appeal or adjust.</t>
+        </is>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>1750</v>
-      </c>
-      <c r="B106" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C106" t="s">
-        <v>1444</v>
-      </c>
-      <c r="D106" t="s">
-        <v>1824</v>
-      </c>
-      <c r="E106">
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N519 - Invalid combination of HCPCS modifiers</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modifier issue</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Correct or add the modifier (e.g. NU/RR, KX, RT/LT, 25) and resubmit.</t>
+        </is>
+      </c>
+      <c r="E112">
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B107" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C107" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D107" t="s">
-        <v>1823</v>
-      </c>
-      <c r="E107">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>1742</v>
-      </c>
-      <c r="B108" t="s">
-        <v>1885</v>
-      </c>
-      <c r="C108" t="s">
-        <v>1447</v>
-      </c>
-      <c r="D108" t="s">
-        <v>1833</v>
-      </c>
-      <c r="E108">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>1471</v>
-      </c>
-      <c r="B109" t="s">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>1903</v>
-      </c>
-      <c r="B110" t="s">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>1460</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>1904</v>
-      </c>
-      <c r="B112" t="s">
-        <v>1905</v>
-      </c>
-      <c r="C112" t="s">
-        <v>1479</v>
-      </c>
-      <c r="D112" t="s">
-        <v>1830</v>
-      </c>
-      <c r="E112">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>1678</v>
-      </c>
-      <c r="B113" t="s">
-        <v>1905</v>
-      </c>
-      <c r="C113" t="s">
-        <v>1466</v>
-      </c>
-      <c r="D113" t="s">
-        <v>1834</v>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N525 - These services are not covered when performed within the global period of another service</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bundled / NCCI edit</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the NCCI pair; if the service was distinct, add 59/XU (or XS) and resubmit; otherwise adjust.</t>
+        </is>
       </c>
       <c r="E113">
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>1683</v>
-      </c>
-      <c r="B114" t="s">
-        <v>1905</v>
-      </c>
-      <c r="C114" t="s">
-        <v>1456</v>
-      </c>
-      <c r="D114" t="s">
-        <v>1823</v>
-      </c>
-      <c r="E114">
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N575 - Mismatch between the submitted ordering/referring provider name and the ordering/referring provider name stored in our records</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referral / referring provider</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get a valid referral or correct the referring provider, then resubmit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N665 - Services by an unlicensed provider are not reimbursable</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Credentialing / out of network</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check provider enrollment, NPI/TIN and network status; appeal once credentialing is confirmed.</t>
+        </is>
+      </c>
+      <c r="E115">
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>1660</v>
-      </c>
-      <c r="B115" t="s">
-        <v>1843</v>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N674 - Not covered unless a pre-requisite procedure/service has been provided</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bundled / NCCI edit</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the NCCI pair; if the service was distinct, add 59/XU (or XS) and resubmit; otherwise adjust.</t>
+        </is>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>1906</v>
-      </c>
-      <c r="B116" t="s">
-        <v>1885</v>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N776 - This service is not a covered Telehealth service</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not covered by plan</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm benefits; bill the patient if an ABN/waiver is on file, otherwise appeal or adjust.</t>
+        </is>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>1731</v>
-      </c>
-      <c r="B117" t="s">
-        <v>1885</v>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">N822 - Missing procedure modifier(s)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remark</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modifier issue</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Correct or add the modifier (e.g. NU/RR, KX, RT/LT, 25) and resubmit.</t>
+        </is>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>1899</v>
-      </c>
-      <c r="B118" t="s">
-        <v>1885</v>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R10 - Optum: Optum Behavioral Health responsibility</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Payer-specific</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wrong payer / vendor</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bill the correct payer, delegated vendor or capitated group/IPA (e.g. Optum Behavioral, Preferred Homecare).</t>
+        </is>
+      </c>
+      <c r="E119">
+        <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>1471</v>
-      </c>
-      <c r="B119" t="s">
-        <v>1885</v>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">R1PRF - Invalid referral format</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Payer-specific</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referral / referring provider</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get a valid referral or correct the referring provider, then resubmit.</t>
+        </is>
+      </c>
+      <c r="E120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CL41-CVCUN - National Correct Coding Initiative denial for Column I/Column II procedures</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Payer-specific</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bundled / NCCI edit</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the NCCI pair; if the service was distinct, add 59/XU (or XS) and resubmit; otherwise adjust.</t>
+        </is>
+      </c>
+      <c r="E121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_2346 - Not a standard reason code (no description in NGO)</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Payer-specific</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read the ERA remark codes; call the payer if the reason isn't clear, then pick a more specific reason.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E114" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
+  <autoFilter ref="A1:E122" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BABA8923-288C-4E24-811F-D4A4F3011519}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="90" customWidth="1"/>
-    <col min="3" max="3" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="95" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B1" s="9" t="s">
-        <v>1819</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>50</v>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denial Reason</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What usually fixes it</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denial codes that map here</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1513</v>
-      </c>
-      <c r="B2" t="s">
-        <v>1820</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1443</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accident / work related</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get the accident details or workers' comp carrier from the patient; update the claim or bill the WC carrier.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_19, PR_227, CO_P12, N179</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1536</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1821</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1486</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bundled / NCCI edit</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the NCCI pair; if the service was distinct, add 59/XU (or XS) and resubmit; otherwise adjust.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_97, PI_97, CO_231, CO_234, CO_236, CO_B10, CO_B15, M15, M80, N19, N20, N88, N525, N674, CL41-CVCUN</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1452</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1822</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1528</v>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coding / billing error</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fix the code, units, charge or other claim data and resubmit as a corrected claim.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_6, CO_7, CO_16, CO_107, CO_129, CO_181, CO_189, CO_199, OA_246, CO_B16, M20, M50, M51, MA130, N56, N257</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>1456</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1823</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1477</v>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Credentialing / out of network</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check provider enrollment, NPI/TIN and network status; appeal once credentialing is confirmed.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR_8, CO_170, CO_185, CO_242, CO_B7, N290, N665</t>
+        </is>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>1444</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1824</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1580</v>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diagnosis issue</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Review the diagnosis codes and pointers with the chart; correct and resubmit.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_11, CO_146, CO_167, M76, N314</t>
+        </is>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>1510</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1825</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1111</v>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Duplicate claim</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the status of the original claim; no resubmission needed if it was processed.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_18</t>
+        </is>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>1492</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1826</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1329</v>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eligibility / member ID</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify eligibility; correct the member ID/MBI, name or DOB and resubmit.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_26, PR_26, CO_27, CO_31, CO_140, CO_166, CO_B9, N30, N382</t>
+        </is>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>1563</v>
-      </c>
-      <c r="B9" t="s">
-        <v>1827</v>
-      </c>
-      <c r="C9" t="s">
-        <v>1505</v>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medical necessity / frequency</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Appeal with medical records and a letter of medical necessity; check LCD/MUE limits.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_50, CO_150, CO_151, M86</t>
+        </is>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>1792</v>
-      </c>
-      <c r="C10" t="s">
-        <v>1459</v>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medical records needed</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Upload the MR on the payer portal, note the PIQ/reference number and set a review date.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_164, CO_226, CO_251, CO_252, N163</t>
+        </is>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>1470</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1828</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1829</v>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modifier issue</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Correct or add the modifier (e.g. NU/RR, KX, RT/LT, 25) and resubmit.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_4, CO_182, N519, N822</t>
+        </is>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>1479</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1830</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1490</v>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No authorization</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the portal for an auth; request a retro-auth or file an appeal with the auth number, then resubmit.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_15, CO_39, CO_197, CO_198, CO_284</t>
+        </is>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>1450</v>
-      </c>
-      <c r="B13" t="s">
-        <v>1831</v>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not covered by plan</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm benefits; bill the patient if an ABN/waiver is on file, otherwise appeal or adjust.</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Billed secondary / Crossed over to secondary</t>
+          <t xml:space="preserve">CO_49, CO_55, CO_96, PR_96, CO_119, PR_119, PR_204, CO_273, N115, N130, N216, N386, N776</t>
         </is>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>1483</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1832</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Billed correct payer</t>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not covered by secondary</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm the secondary's benefits; if the service isn't covered, bill the patient or adjust per the plan.</t>
         </is>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>1447</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1833</v>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other insurance / COB</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get the other insurance and primary EOB, update COB with the payer and bill primary first.</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Contacted patient</t>
+          <t xml:space="preserve">OA_22, OA_23, MA04, MA18, N4, N245</t>
         </is>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>1466</v>
-      </c>
-      <c r="B16" t="s">
-        <v>1834</v>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Place of service</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verify the place of service (inpatient/outpatient) and correct the claim.</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Reprocessing requested</t>
+          <t xml:space="preserve">CO_5, M2, M77</t>
         </is>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>1778</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1835</v>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PR deductible/coinsurance</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bill the patient for the deductible/coinsurance/copay amount shown on the EOB.</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Checking with internal team</t>
+          <t xml:space="preserve">PR_1, PR_2, PR_3</t>
         </is>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>1487</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1836</v>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Referral / referring provider</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Get a valid referral or correct the referring provider, then resubmit.</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Overpayment identified / Refund sent</t>
+          <t xml:space="preserve">CO_183, CO_243, CO_288, N286, N575, R1PRF</t>
         </is>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>1599</v>
-      </c>
-      <c r="B19" t="s">
-        <v>1837</v>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Same or similar equipment (DME)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm the prior supplier and date; if an ABN was signed, shift to the patient, otherwise adjust.</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Waiting on recoupment</t>
+          <t xml:space="preserve">M3</t>
         </is>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>1458</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1838</v>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Timely filing</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Find proof of timely filing (clearinghouse acceptance or earlier submission) and appeal with it; if none, adjust the balance.</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Under Review</t>
+          <t xml:space="preserve">CO_29</t>
         </is>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Claim not found</t>
+          <t xml:space="preserve">Wrong payer / vendor</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bill the correct payer, delegated vendor or capitated group/IPA (e.g. Optum Behavioral, Preferred Homecare).</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_24, CO_109, CO_B11, N104, R10</t>
         </is>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>1618</v>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claim not found</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confirm the payer ID/mailing address and eligibility, resubmit, and keep proof of timely filing.</t>
+        </is>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>1499</v>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NO DENIAL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No action needed - the claim paid, or the code is a payment reduction/informational. Review the ERA only if the allowed amount looks wrong.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_45, CO_59, CO_131, CO_144, CO_253</t>
+        </is>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PR deductible/coinsurance</t>
+          <t xml:space="preserve">Other</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bill the patient for the deductible/coinsurance/copay amount shown on the EOB.</t>
+          <t xml:space="preserve">Read the ERA remark codes; call the payer if the reason isn't clear, then pick a more specific reason.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CO_A1, CO_B20, CO_2346</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C24"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="44" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="80" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Action</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">When to use it</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resubmitted</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Submit</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sent a corrected or new claim to the same payer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Billed correct payer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Submit</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sent the claim to a different payer or delegated vendor after a wrong-payer denial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Billed secondary / Crossed over to secondary</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Submit</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sent the claim to the secondary after the primary paid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reprocessing requested</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Submit</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Asked the payer to reprocess the claim (call, ticket or portal) without sending a new claim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auth requested</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Submit</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Requested an authorization or retro-auth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uploaded MR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Appeal</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sent medical records (portal, fax or Message Center).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon filed</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Appeal</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed a reconsideration or dispute (first-level appeal).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Appeal filed</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Appeal</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Filed a formal appeal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contacted payer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contact</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Called, chatted with or emailed the payer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contacted patient</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contact</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Called or messaged the patient (coverage, MBI, COB).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Checking with internal team</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contact</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waiting on someone in-house: provider, credentialing, auth or posting team.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Under Review</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waiting</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Use when the Claim Status is Under Review.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waiting on payer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waiting</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claim is in process; nothing to do until the payer responds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary payment pending</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waiting</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secondary was billed; waiting on its payment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waiting on recoupment</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waiting</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Waiting for the payer to recoup a payment before the next step.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Payment posted</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Closed</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Payment received and posted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted balance</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Closed</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balance written off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adjusted secondary balance</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Closed</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balance left after the secondary written off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted to patient</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Closed</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balance moved to patient responsibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Shifted secondary balance to patient</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Closed</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balance left after the secondary moved to patient responsibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Overpayment identified / Refund sent</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Closed</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Overpayment found; refund, void or offset requested or sent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prior Actions: pick from the same list. List earlier actions newest first, separated by "; " (e.g. Recon filed; Resubmitted).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:C22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
